--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4849210000000</v>
+        <v>4861030000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5260790000000</v>
+        <v>5084140000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4123000000000</v>
+        <v>4249100000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3680320000000</v>
+        <v>3752940000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2769710000000</v>
+        <v>2734760000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,37 +636,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2246990000000</v>
+        <v>2168000000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1728010000000</v>
+        <v>1695620000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1650860000000</v>
+        <v>1645570000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,37 +681,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1443320000000</v>
+        <v>1417770000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Lilly(Eli) &amp; Co</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1101450000000</v>
+        <v>1071530000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lilly(Eli) &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1050270000000</v>
+        <v>1043590000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>982670000000</v>
+        <v>991490000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>946930000000</v>
+        <v>930710000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>850100000000</v>
+        <v>865410000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>842570000000</v>
+        <v>805480000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>691650000000</v>
+        <v>700670000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,37 +801,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>682540000000</v>
+        <v>678790000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>654560000000</v>
+        <v>641800000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>640020000000</v>
+        <v>607090000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>498620000000</v>
+        <v>503200000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>454360000000</v>
+        <v>462580000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>442080000000</v>
+        <v>433920000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>438380000000</v>
+        <v>419200000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,37 +906,37 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>432880000000</v>
+        <v>417060000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>422930000000</v>
+        <v>416480000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>401870000000</v>
+        <v>415860000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>401250000000</v>
+        <v>407520000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>379870000000</v>
+        <v>384430000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,112 +981,112 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>376280000000</v>
+        <v>360390000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>373170000000</v>
+        <v>357370000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>362270000000</v>
+        <v>344270000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>360690000000</v>
+        <v>342220000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>355100000000</v>
+        <v>339700000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>340270000000</v>
+        <v>339410000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>337410000000</v>
+        <v>336650000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>336700000000</v>
+        <v>334450000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>335820000000</v>
+        <v>329490000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>322290000000</v>
+        <v>324450000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>308030000000</v>
+        <v>310150000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>299670000000</v>
+        <v>305880000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,22 +1161,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>297790000000</v>
+        <v>303710000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>282800000000</v>
+        <v>287810000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,187 +1191,187 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>277190000000</v>
+        <v>276200000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>273040000000</v>
+        <v>271510000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>271680000000</v>
+        <v>268260000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>270470000000</v>
+        <v>263270000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>266420000000</v>
+        <v>255260000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>254950000000</v>
+        <v>254430000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>251080000000</v>
+        <v>254000000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>248410000000</v>
+        <v>251940000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>245390000000</v>
+        <v>241010000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>239150000000</v>
+        <v>240570000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>238180000000</v>
+        <v>234680000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>236010000000</v>
+        <v>233950000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>234700000000</v>
+        <v>232980000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,22 +1386,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>232860000000</v>
+        <v>228430000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>229210000000</v>
+        <v>227240000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>225480000000</v>
+        <v>226880000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,67 +1431,67 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>219270000000</v>
+        <v>221350000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>214920000000</v>
+        <v>220920000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>211690000000</v>
+        <v>214080000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>210270000000</v>
+        <v>213510000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>204380000000</v>
+        <v>213100000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,22 +1506,22 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>204010000000</v>
+        <v>206250000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>203870000000</v>
+        <v>202710000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>195580000000</v>
+        <v>196190000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,52 +1551,52 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>191110000000</v>
+        <v>189200000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>186060000000</v>
+        <v>187500000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>185470000000</v>
+        <v>186090000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>183980000000</v>
+        <v>185580000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>182200000000</v>
+        <v>183740000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>178700000000</v>
+        <v>182210000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>178570000000</v>
+        <v>181660000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>178210000000</v>
+        <v>181540000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>176410000000</v>
+        <v>178390000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,82 +1686,82 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>175420000000</v>
+        <v>173130000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>171700000000</v>
+        <v>172270000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>166330000000</v>
+        <v>170280000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>165710000000</v>
+        <v>166190000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>161230000000</v>
+        <v>159320000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>159590000000</v>
+        <v>153930000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>146390000000</v>
+        <v>148350000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,52 +1791,52 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>144110000000</v>
+        <v>145380000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>143340000000</v>
+        <v>142880000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140700000000</v>
+        <v>133520000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131270000000</v>
+        <v>131890000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,67 +1851,67 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>130680000000</v>
+        <v>131750000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>130500000000</v>
+        <v>130940000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>130410000000</v>
+        <v>130730000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>130000000000</v>
+        <v>128430000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>126460000000</v>
+        <v>123700000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>121080000000</v>
+        <v>123390000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120980000000</v>
+        <v>122180000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,22 +1956,22 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>116350000000</v>
+        <v>119980000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>116070000000</v>
+        <v>119330000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,82 +1986,82 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>115180000000</v>
+        <v>117900000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>112560000000</v>
+        <v>117630000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>112540000000</v>
+        <v>117250000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>110750000000</v>
+        <v>114530000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>110430000000</v>
+        <v>112990000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>109150000000</v>
+        <v>112940000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,22 +2076,22 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>108410000000</v>
+        <v>111850000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>108240000000</v>
+        <v>111180000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>106570000000</v>
+        <v>109890000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>102390000000</v>
+        <v>105580000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,127 +2136,127 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>101910000000</v>
+        <v>102180000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>100260000000</v>
+        <v>98550000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>98970000000</v>
+        <v>97660000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>97910000000</v>
+        <v>96340000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>96190000000</v>
+        <v>92120000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92430000000</v>
+        <v>92000000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>90810000000</v>
+        <v>91390000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88360000000</v>
+        <v>90630000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85940000000</v>
+        <v>88560000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,52 +2271,52 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85320000000</v>
+        <v>87170000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>85080000000</v>
+        <v>86100000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>84420000000</v>
+        <v>83560000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>83200000000</v>
+        <v>82610000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>80460000000</v>
+        <v>81720000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>79430000000</v>
+        <v>79130000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>76170000000</v>
+        <v>76640000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,22 +2376,22 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75130000000</v>
+        <v>76480000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74190000000</v>
+        <v>75770000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73730000000</v>
+        <v>74920000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,52 +2421,52 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70790000000</v>
+        <v>72100000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70620000000</v>
+        <v>70060000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69770000000</v>
+        <v>69610000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>69190000000</v>
+        <v>68480000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65900000000</v>
+        <v>65150000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,52 +2496,52 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>61440000000</v>
+        <v>61760000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61050000000</v>
+        <v>61620000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60230000000</v>
+        <v>58560000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>57480000000</v>
+        <v>57680000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55710000000</v>
+        <v>55270000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,172 +2571,172 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54590000000</v>
+        <v>54960000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50520000000</v>
+        <v>52620000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50320000000</v>
+        <v>50510000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49800000000</v>
+        <v>49290000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49080000000</v>
+        <v>47850000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48630000000</v>
+        <v>47760000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47590000000</v>
+        <v>47230000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46240000000</v>
+        <v>46860000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45960000000</v>
+        <v>46800000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45810000000</v>
+        <v>46220000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44750000000</v>
+        <v>45770000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>44390000000</v>
+        <v>44590000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40320000000</v>
+        <v>40250000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,37 +2766,37 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>37670000000</v>
+        <v>37430000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>35140000000</v>
+        <v>35610000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34920000000</v>
+        <v>35540000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32540000000</v>
+        <v>32780000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,22 +2826,22 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31170000000</v>
+        <v>31440000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31160000000</v>
+        <v>31260000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,172 +2856,172 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30350000000</v>
+        <v>31240000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30150000000</v>
+        <v>30900000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27890000000</v>
+        <v>30440000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27430000000</v>
+        <v>27820000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26830000000</v>
+        <v>27110000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>26340000000</v>
+        <v>25100000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>25530000000</v>
+        <v>24760000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>24110000000</v>
+        <v>24730000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>23010000000</v>
+        <v>24140000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>23000000000</v>
+        <v>23380000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>22460000000</v>
+        <v>22800000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>22370000000</v>
+        <v>22250000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>22010000000</v>
+        <v>22100000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>17250000000</v>
+        <v>16990000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>14890000000</v>
+        <v>15190000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12440000000</v>
+        <v>12320000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12440000000</v>
+        <v>12320000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11900000000</v>
+        <v>11890000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10790000000</v>
+        <v>11150000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,67 +3141,67 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10120000000</v>
+        <v>10440000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7700000000</v>
+        <v>7870000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7670000000</v>
+        <v>7800000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7510000000</v>
+        <v>7700000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7460000000</v>
+        <v>7640000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,52 +3216,52 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7340000000</v>
+        <v>7490000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7010000000</v>
+        <v>7200000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6890000000</v>
+        <v>7160000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6870000000</v>
+        <v>6940000000</v>
       </c>
     </row>
     <row r="186">
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6420000000</v>
+        <v>6720000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5100000000</v>
+        <v>5120000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5000000000</v>
+        <v>5100000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4630000000</v>
+        <v>4440000000</v>
       </c>
     </row>
     <row r="191">
@@ -3357,76 +3357,76 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3820000000</v>
+        <v>3960000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3700000000</v>
+        <v>3870000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3690000000</v>
+        <v>3660000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3040000000</v>
+        <v>2980000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2850000000</v>
+        <v>2920000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2490000000</v>
+        <v>2540000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,82 +3456,82 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2390000000</v>
+        <v>2410000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>QUBT</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Quantum Computing Inc</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1830000000</v>
+        <v>1800000000</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Quantum Computing Inc</t>
+          <t>C3.ai Inc</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1810000000</v>
+        <v>1800000000</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>C3.ai Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1690000000</v>
+        <v>1740000000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>TDOC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Teladoc Health Inc</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1150000000</v>
+        <v>1180000000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TDOC</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Teladoc Health Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1120000000</v>
+        <v>1130000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>881190000</v>
+        <v>853270000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>507450000</v>
+        <v>489050000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4861030000000</v>
+        <v>4835640000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5084140000000</v>
+        <v>5113300000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4249100000000</v>
+        <v>4200050000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3752940000000</v>
+        <v>3691390000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2734760000000</v>
+        <v>2679540000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2168000000000</v>
+        <v>2145910000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1695620000000</v>
+        <v>1707440000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1645570000000</v>
+        <v>1619550000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1417770000000</v>
+        <v>1408330000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1071530000000</v>
+        <v>1069490000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1043590000000</v>
+        <v>1047620000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>991490000000</v>
+        <v>994430000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>930710000000</v>
+        <v>936980000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>865410000000</v>
+        <v>857560000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>805480000000</v>
+        <v>823090000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>700670000000</v>
+        <v>701300000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>678790000000</v>
+        <v>696230000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>641800000000</v>
+        <v>643920000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>607090000000</v>
+        <v>613390000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>503200000000</v>
+        <v>502190000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>462580000000</v>
+        <v>464820000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>433920000000</v>
+        <v>433960000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>419200000000</v>
+        <v>430260000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,37 +906,37 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>417060000000</v>
+        <v>424380000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>416480000000</v>
+        <v>416210000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>415860000000</v>
+        <v>414670000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>407520000000</v>
+        <v>399730000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>384430000000</v>
+        <v>381680000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>360390000000</v>
+        <v>360170000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,67 +996,67 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>357370000000</v>
+        <v>354750000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>344270000000</v>
+        <v>345570000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>342220000000</v>
+        <v>340670000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>339700000000</v>
+        <v>338950000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>339410000000</v>
+        <v>337430000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>336650000000</v>
+        <v>334240000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,67 +1086,67 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>334450000000</v>
+        <v>324370000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>329490000000</v>
+        <v>323980000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>324450000000</v>
+        <v>318580000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>310150000000</v>
+        <v>306820000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>305880000000</v>
+        <v>304770000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>303710000000</v>
+        <v>302540000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>287810000000</v>
+        <v>284380000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>276200000000</v>
+        <v>283360000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>271510000000</v>
+        <v>271780000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>268260000000</v>
+        <v>271310000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>263270000000</v>
+        <v>263490000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>255260000000</v>
+        <v>258270000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>254430000000</v>
+        <v>253750000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>254000000000</v>
+        <v>251010000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>251940000000</v>
+        <v>248930000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>241010000000</v>
+        <v>248290000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,247 +1326,247 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>240570000000</v>
+        <v>240580000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>234680000000</v>
+        <v>237150000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>233950000000</v>
+        <v>235120000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>232980000000</v>
+        <v>234000000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>228430000000</v>
+        <v>231470000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>227240000000</v>
+        <v>228420000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>226880000000</v>
+        <v>224150000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>221350000000</v>
+        <v>219530000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>220920000000</v>
+        <v>219090000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>214080000000</v>
+        <v>213760000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>213510000000</v>
+        <v>213420000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>213100000000</v>
+        <v>210400000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>206250000000</v>
+        <v>207120000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>202710000000</v>
+        <v>203090000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>196190000000</v>
+        <v>197230000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>189200000000</v>
+        <v>193590000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>187500000000</v>
+        <v>186410000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,82 +1581,82 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>186090000000</v>
+        <v>184940000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>185580000000</v>
+        <v>184430000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>183740000000</v>
+        <v>183750000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>182210000000</v>
+        <v>183100000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>181660000000</v>
+        <v>181410000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>181540000000</v>
+        <v>178880000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>178390000000</v>
+        <v>176550000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,37 +1686,37 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>173130000000</v>
+        <v>172010000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>172270000000</v>
+        <v>169110000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>170280000000</v>
+        <v>167080000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>166190000000</v>
+        <v>165730000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>159320000000</v>
+        <v>157340000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,52 +1761,52 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>153930000000</v>
+        <v>148530000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>148350000000</v>
+        <v>147180000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>145380000000</v>
+        <v>145900000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142880000000</v>
+        <v>142300000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>133520000000</v>
+        <v>133240000000</v>
       </c>
     </row>
     <row r="90">
@@ -1842,16 +1842,16 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>131750000000</v>
+        <v>131670000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,22 +1866,22 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>130940000000</v>
+        <v>130180000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>130730000000</v>
+        <v>128730000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>128430000000</v>
+        <v>128600000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,37 +1911,37 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>123700000000</v>
+        <v>123670000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123390000000</v>
+        <v>123120000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122180000000</v>
+        <v>121610000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119980000000</v>
+        <v>119920000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119330000000</v>
+        <v>118350000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117900000000</v>
+        <v>116560000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,37 +2001,37 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117630000000</v>
+        <v>116520000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117250000000</v>
+        <v>114940000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>114530000000</v>
+        <v>113950000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,67 +2046,67 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>112990000000</v>
+        <v>111140000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>112940000000</v>
+        <v>110920000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>111850000000</v>
+        <v>110100000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>111180000000</v>
+        <v>109860000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>109890000000</v>
+        <v>109190000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>105580000000</v>
+        <v>102460000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>102180000000</v>
+        <v>100790000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>98550000000</v>
+        <v>99360000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>97660000000</v>
+        <v>96940000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>96340000000</v>
+        <v>92720000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92120000000</v>
+        <v>91760000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92000000000</v>
+        <v>90550000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>91390000000</v>
+        <v>90320000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>90630000000</v>
+        <v>88080000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>88560000000</v>
+        <v>87990000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87170000000</v>
+        <v>87080000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>86100000000</v>
+        <v>85780000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>83560000000</v>
+        <v>84920000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,37 +2316,37 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>82610000000</v>
+        <v>82680000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81720000000</v>
+        <v>80440000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>79130000000</v>
+        <v>79700000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,22 +2361,22 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>76640000000</v>
+        <v>76340000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>76480000000</v>
+        <v>75470000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>75770000000</v>
+        <v>75000000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>74920000000</v>
+        <v>74910000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72100000000</v>
+        <v>70140000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70060000000</v>
+        <v>69350000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69610000000</v>
+        <v>68540000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68480000000</v>
+        <v>66860000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65150000000</v>
+        <v>64810000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>61760000000</v>
+        <v>63500000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61620000000</v>
+        <v>58200000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>58560000000</v>
+        <v>57400000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>57680000000</v>
+        <v>56370000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55270000000</v>
+        <v>53830000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54960000000</v>
+        <v>53730000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,37 +2586,37 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52620000000</v>
+        <v>49800000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50510000000</v>
+        <v>49420000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49290000000</v>
+        <v>47500000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47850000000</v>
+        <v>47340000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,82 +2646,82 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47760000000</v>
+        <v>47050000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47230000000</v>
+        <v>46030000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46860000000</v>
+        <v>45950000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46800000000</v>
+        <v>45410000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>46220000000</v>
+        <v>44630000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>45770000000</v>
+        <v>44070000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>44590000000</v>
+        <v>43810000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40250000000</v>
+        <v>39590000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>37430000000</v>
+        <v>38030000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>35610000000</v>
+        <v>37190000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,37 +2796,37 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>35540000000</v>
+        <v>34820000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>32780000000</v>
+        <v>33570000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31440000000</v>
+        <v>32580000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31260000000</v>
+        <v>31610000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,37 +2856,37 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>31240000000</v>
+        <v>30710000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30900000000</v>
+        <v>30340000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>30440000000</v>
+        <v>30280000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27820000000</v>
+        <v>27160000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27110000000</v>
+        <v>26600000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25100000000</v>
+        <v>24730000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,97 +2946,97 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24760000000</v>
+        <v>24320000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>24730000000</v>
+        <v>23410000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>24140000000</v>
+        <v>23260000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>23380000000</v>
+        <v>22050000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>22800000000</v>
+        <v>21920000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>22250000000</v>
+        <v>21910000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>22100000000</v>
+        <v>21750000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16990000000</v>
+        <v>16360000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15190000000</v>
+        <v>15010000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12320000000</v>
+        <v>11870000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12320000000</v>
+        <v>11870000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11890000000</v>
+        <v>11140000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>11150000000</v>
+        <v>10620000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10440000000</v>
+        <v>10010000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7870000000</v>
+        <v>8170000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,52 +3171,52 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7800000000</v>
+        <v>7980000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7700000000</v>
+        <v>7550000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7640000000</v>
+        <v>7340000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7490000000</v>
+        <v>7330000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7200000000</v>
+        <v>6990000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7160000000</v>
+        <v>6830000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6940000000</v>
+        <v>6730000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6740000000</v>
+        <v>6690000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6720000000</v>
+        <v>6500000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5120000000</v>
+        <v>5040000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5100000000</v>
+        <v>5010000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4440000000</v>
+        <v>4340000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4130000000</v>
+        <v>4140000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3960000000</v>
+        <v>3870000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3870000000</v>
+        <v>3850000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3660000000</v>
+        <v>3620000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2980000000</v>
+        <v>3050000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2920000000</v>
+        <v>2840000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2540000000</v>
+        <v>2460000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2410000000</v>
+        <v>2380000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1800000000</v>
+        <v>1770000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1800000000</v>
+        <v>1730000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1740000000</v>
+        <v>1720000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1180000000</v>
+        <v>1200000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1130000000</v>
+        <v>1150000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>853270000</v>
+        <v>847350000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>489050000</v>
+        <v>484460000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4835640000000</v>
+        <v>4851250000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5113300000000</v>
+        <v>5154990000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4200050000000</v>
+        <v>4174020000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3691390000000</v>
+        <v>3640740000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2679540000000</v>
+        <v>2653000000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2145910000000</v>
+        <v>2166500000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1707440000000</v>
+        <v>1715260000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1619550000000</v>
+        <v>1620700000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1408330000000</v>
+        <v>1414250000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1069490000000</v>
+        <v>1071090000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1047620000000</v>
+        <v>1046440000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>994430000000</v>
+        <v>999960000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>936980000000</v>
+        <v>927490000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>857560000000</v>
+        <v>852880000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>823090000000</v>
+        <v>836640000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>701300000000</v>
+        <v>692540000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>696230000000</v>
+        <v>671560000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>643920000000</v>
+        <v>644120000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>613390000000</v>
+        <v>617530000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>502190000000</v>
+        <v>497350000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,82 +861,82 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>464820000000</v>
+        <v>463890000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>433960000000</v>
+        <v>432880000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>430260000000</v>
+        <v>424770000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>424380000000</v>
+        <v>418950000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>416210000000</v>
+        <v>417950000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>414670000000</v>
+        <v>404880000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>399730000000</v>
+        <v>396350000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>381680000000</v>
+        <v>378060000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>360170000000</v>
+        <v>359800000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>354750000000</v>
+        <v>358150000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>345570000000</v>
+        <v>357520000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>340670000000</v>
+        <v>341480000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>338950000000</v>
+        <v>336890000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>337430000000</v>
+        <v>336830000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,52 +1071,52 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>334240000000</v>
+        <v>329640000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>324370000000</v>
+        <v>324650000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>323980000000</v>
+        <v>318170000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>318580000000</v>
+        <v>317910000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>306820000000</v>
+        <v>307280000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>304770000000</v>
+        <v>301770000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,37 +1161,37 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>302540000000</v>
+        <v>298800000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>284380000000</v>
+        <v>274060000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>283360000000</v>
+        <v>273110000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,37 +1206,37 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>271780000000</v>
+        <v>266630000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>271310000000</v>
+        <v>265280000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>263490000000</v>
+        <v>263240000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>258270000000</v>
+        <v>260570000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>253750000000</v>
+        <v>253900000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,52 +1281,52 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>251010000000</v>
+        <v>252620000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>248930000000</v>
+        <v>247140000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>248290000000</v>
+        <v>246380000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>240580000000</v>
+        <v>246080000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,52 +1341,52 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>237150000000</v>
+        <v>239760000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>235120000000</v>
+        <v>238060000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>234000000000</v>
+        <v>227610000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>231470000000</v>
+        <v>223750000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>228420000000</v>
+        <v>223020000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>224150000000</v>
+        <v>222550000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,52 +1431,52 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>219530000000</v>
+        <v>218660000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>219090000000</v>
+        <v>213010000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>213760000000</v>
+        <v>210990000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>213420000000</v>
+        <v>206740000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,37 +1491,37 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>210400000000</v>
+        <v>206190000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>207120000000</v>
+        <v>203470000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>203090000000</v>
+        <v>202050000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>197230000000</v>
+        <v>194130000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,22 +1551,22 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>193590000000</v>
+        <v>189070000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>186410000000</v>
+        <v>184740000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,97 +1581,97 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184940000000</v>
+        <v>183360000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>184430000000</v>
+        <v>183120000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>183750000000</v>
+        <v>181860000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>183100000000</v>
+        <v>180510000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>181410000000</v>
+        <v>177200000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>178880000000</v>
+        <v>177120000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>176550000000</v>
+        <v>175890000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>172010000000</v>
+        <v>168530000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>169110000000</v>
+        <v>167650000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>167080000000</v>
+        <v>167210000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>165730000000</v>
+        <v>159620000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>157340000000</v>
+        <v>153300000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>148530000000</v>
+        <v>150330000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>147180000000</v>
+        <v>146470000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>145900000000</v>
+        <v>144960000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142300000000</v>
+        <v>139560000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>133240000000</v>
+        <v>135050000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,37 +1836,37 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131890000000</v>
+        <v>131760000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>131670000000</v>
+        <v>129920000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>130180000000</v>
+        <v>129630000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128730000000</v>
+        <v>128790000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>128600000000</v>
+        <v>126090000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>123670000000</v>
+        <v>124180000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123120000000</v>
+        <v>123990000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>121610000000</v>
+        <v>119910000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,82 +1956,82 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119920000000</v>
+        <v>118450000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118350000000</v>
+        <v>117050000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>116560000000</v>
+        <v>116780000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116520000000</v>
+        <v>116050000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>114940000000</v>
+        <v>115600000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>113950000000</v>
+        <v>112710000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,187 +2046,187 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>111140000000</v>
+        <v>112110000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>110920000000</v>
+        <v>110970000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>110100000000</v>
+        <v>109280000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>109860000000</v>
+        <v>108900000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>109190000000</v>
+        <v>108530000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>102460000000</v>
+        <v>100300000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>100790000000</v>
+        <v>100270000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>99360000000</v>
+        <v>99570000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>96940000000</v>
+        <v>93270000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92720000000</v>
+        <v>93190000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91760000000</v>
+        <v>93060000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90550000000</v>
+        <v>92170000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>90320000000</v>
+        <v>89470000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88080000000</v>
+        <v>86510000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,37 +2256,37 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>87990000000</v>
+        <v>85020000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87080000000</v>
+        <v>84350000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>85780000000</v>
+        <v>84030000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>84920000000</v>
+        <v>83880000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,97 +2316,97 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>82680000000</v>
+        <v>82870000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>80440000000</v>
+        <v>79750000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>79700000000</v>
+        <v>77620000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>76340000000</v>
+        <v>75400000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75470000000</v>
+        <v>74110000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>75000000000</v>
+        <v>73960000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>74910000000</v>
+        <v>73540000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70140000000</v>
+        <v>70270000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69350000000</v>
+        <v>69370000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68540000000</v>
+        <v>68100000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66860000000</v>
+        <v>66710000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64810000000</v>
+        <v>65670000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63500000000</v>
+        <v>59340000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>58200000000</v>
+        <v>58680000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>57400000000</v>
+        <v>58140000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56370000000</v>
+        <v>56920000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>53830000000</v>
+        <v>53230000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,37 +2571,37 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53730000000</v>
+        <v>53080000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>49800000000</v>
+        <v>51460000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49420000000</v>
+        <v>48480000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,22 +2616,22 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47500000000</v>
+        <v>47120000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47340000000</v>
+        <v>46700000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,97 +2646,97 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47050000000</v>
+        <v>46040000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46030000000</v>
+        <v>46040000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45950000000</v>
+        <v>45970000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45410000000</v>
+        <v>45250000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44630000000</v>
+        <v>45090000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44070000000</v>
+        <v>43400000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>43810000000</v>
+        <v>42620000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39590000000</v>
+        <v>39300000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38030000000</v>
+        <v>38120000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>37190000000</v>
+        <v>36690000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34820000000</v>
+        <v>34590000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>33570000000</v>
+        <v>34570000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>32580000000</v>
+        <v>32350000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,52 +2841,52 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31610000000</v>
+        <v>31240000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30710000000</v>
+        <v>30610000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30340000000</v>
+        <v>30320000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>30280000000</v>
+        <v>30170000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27160000000</v>
+        <v>26830000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,22 +2916,22 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26600000000</v>
+        <v>26300000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24730000000</v>
+        <v>24210000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24320000000</v>
+        <v>24150000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23410000000</v>
+        <v>23640000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>23260000000</v>
+        <v>23040000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>22050000000</v>
+        <v>21750000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,37 +3006,37 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>21920000000</v>
+        <v>21640000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>21910000000</v>
+        <v>20530000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>21750000000</v>
+        <v>20420000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16360000000</v>
+        <v>16770000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15010000000</v>
+        <v>14930000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11870000000</v>
+        <v>11710000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11870000000</v>
+        <v>11710000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11140000000</v>
+        <v>11160000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10620000000</v>
+        <v>10560000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10010000000</v>
+        <v>9980000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8170000000</v>
+        <v>8060000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7980000000</v>
+        <v>7950000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,67 +3186,67 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7550000000</v>
+        <v>7660000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7340000000</v>
+        <v>7230000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7330000000</v>
+        <v>7150000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6990000000</v>
+        <v>7110000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6830000000</v>
+        <v>7070000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6730000000</v>
+        <v>6650000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6690000000</v>
+        <v>6630000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6500000000</v>
+        <v>6530000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5040000000</v>
+        <v>5050000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5010000000</v>
+        <v>4940000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4340000000</v>
+        <v>4260000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,37 +3351,37 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4140000000</v>
+        <v>4110000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3870000000</v>
+        <v>3760000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3850000000</v>
+        <v>3750000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3620000000</v>
+        <v>3570000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3050000000</v>
+        <v>3040000000</v>
       </c>
     </row>
     <row r="196">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2460000000</v>
+        <v>2420000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2380000000</v>
+        <v>2370000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1770000000</v>
+        <v>1810000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1730000000</v>
+        <v>1700000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1720000000</v>
+        <v>1670000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1200000000</v>
+        <v>1170000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1150000000</v>
+        <v>1100000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>847350000</v>
+        <v>839840000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>484460000</v>
+        <v>482930000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4851250000000</v>
+        <v>4918240000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5154990000000</v>
+        <v>5286090000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4174020000000</v>
+        <v>4227030000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3640740000000</v>
+        <v>3696070000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2653000000000</v>
+        <v>2709410000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2166500000000</v>
+        <v>2231530000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1715260000000</v>
+        <v>1738190000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1620700000000</v>
+        <v>1657880000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,37 +681,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1414250000000</v>
+        <v>1446320000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lilly(Eli) &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1071090000000</v>
+        <v>1103980000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Lilly(Eli) &amp; Co</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1046440000000</v>
+        <v>1084860000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>999960000000</v>
+        <v>980490000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>927490000000</v>
+        <v>928530000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>852880000000</v>
+        <v>889850000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>836640000000</v>
+        <v>847240000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>692540000000</v>
+        <v>690680000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>671560000000</v>
+        <v>671350000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>644120000000</v>
+        <v>651200000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>617530000000</v>
+        <v>628110000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>497350000000</v>
+        <v>495590000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>463890000000</v>
+        <v>466550000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>432880000000</v>
+        <v>455340000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>424770000000</v>
+        <v>434630000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>418950000000</v>
+        <v>423520000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>417950000000</v>
+        <v>418010000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>404880000000</v>
+        <v>406840000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>396350000000</v>
+        <v>396440000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,37 +966,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>378060000000</v>
+        <v>378880000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>359800000000</v>
+        <v>374110000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>358150000000</v>
+        <v>367080000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>357520000000</v>
+        <v>363040000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>341480000000</v>
+        <v>342710000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>336890000000</v>
+        <v>336990000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>336830000000</v>
+        <v>336790000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>329640000000</v>
+        <v>331250000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,37 +1086,37 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>324650000000</v>
+        <v>325240000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>318170000000</v>
+        <v>319640000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>317910000000</v>
+        <v>313590000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>307280000000</v>
+        <v>306800000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>301770000000</v>
+        <v>301810000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,22 +1161,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>298800000000</v>
+        <v>296880000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>274060000000</v>
+        <v>282910000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>273110000000</v>
+        <v>277040000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>266630000000</v>
+        <v>274250000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>265280000000</v>
+        <v>269790000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,22 +1236,22 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>263240000000</v>
+        <v>262760000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>260570000000</v>
+        <v>260850000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>253900000000</v>
+        <v>257960000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>252620000000</v>
+        <v>257660000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,37 +1296,37 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>247140000000</v>
+        <v>251580000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>246380000000</v>
+        <v>246610000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>246080000000</v>
+        <v>246340000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,82 +1341,82 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>239760000000</v>
+        <v>243410000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>238060000000</v>
+        <v>236380000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>227610000000</v>
+        <v>235750000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>223750000000</v>
+        <v>229620000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>223020000000</v>
+        <v>223990000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>222550000000</v>
+        <v>222600000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>218660000000</v>
+        <v>220780000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>213010000000</v>
+        <v>211350000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,67 +1461,67 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>210990000000</v>
+        <v>210140000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>206740000000</v>
+        <v>205320000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>206190000000</v>
+        <v>203710000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>203470000000</v>
+        <v>200800000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>202050000000</v>
+        <v>199870000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,37 +1536,37 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>194130000000</v>
+        <v>198190000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>189070000000</v>
+        <v>187100000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184740000000</v>
+        <v>184860000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,22 +1581,22 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>183360000000</v>
+        <v>182430000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>183120000000</v>
+        <v>181910000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,67 +1611,67 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>181860000000</v>
+        <v>180940000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>180510000000</v>
+        <v>178550000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>177200000000</v>
+        <v>176900000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>177120000000</v>
+        <v>175830000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>175890000000</v>
+        <v>173980000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>168530000000</v>
+        <v>171240000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>167650000000</v>
+        <v>169550000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,37 +1716,37 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>167210000000</v>
+        <v>165460000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159620000000</v>
+        <v>155740000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>153300000000</v>
+        <v>155700000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>150330000000</v>
+        <v>152820000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>146470000000</v>
+        <v>149380000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>144960000000</v>
+        <v>144760000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139560000000</v>
+        <v>144510000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>135050000000</v>
+        <v>135500000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,37 +1836,37 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131760000000</v>
+        <v>131900000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>129920000000</v>
+        <v>131030000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>129630000000</v>
+        <v>128360000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,37 +1881,37 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128790000000</v>
+        <v>128130000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126090000000</v>
+        <v>127310000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124180000000</v>
+        <v>125690000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,67 +1926,67 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123990000000</v>
+        <v>124190000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>119910000000</v>
+        <v>119380000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>118450000000</v>
+        <v>119130000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>117050000000</v>
+        <v>118910000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>116780000000</v>
+        <v>118670000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,217 +2001,217 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116050000000</v>
+        <v>116450000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>115600000000</v>
+        <v>116380000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>112710000000</v>
+        <v>110640000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>112110000000</v>
+        <v>110200000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>110970000000</v>
+        <v>108950000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>109280000000</v>
+        <v>108880000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>108900000000</v>
+        <v>108150000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>108530000000</v>
+        <v>107620000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100300000000</v>
+        <v>101230000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>100270000000</v>
+        <v>100440000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>99570000000</v>
+        <v>99360000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93270000000</v>
+        <v>93870000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93190000000</v>
+        <v>92970000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93060000000</v>
+        <v>92890000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92170000000</v>
+        <v>92530000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89470000000</v>
+        <v>89840000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,82 +2241,82 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86510000000</v>
+        <v>86060000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85020000000</v>
+        <v>85220000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84350000000</v>
+        <v>84940000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>84030000000</v>
+        <v>84740000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>83880000000</v>
+        <v>83680000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>82870000000</v>
+        <v>83310000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>79750000000</v>
+        <v>81280000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,67 +2346,67 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>77620000000</v>
+        <v>77290000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75400000000</v>
+        <v>76000000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74110000000</v>
+        <v>74440000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>73960000000</v>
+        <v>74410000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73540000000</v>
+        <v>72930000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70270000000</v>
+        <v>72610000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69370000000</v>
+        <v>69940000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68100000000</v>
+        <v>66980000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66710000000</v>
+        <v>66850000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,67 +2481,67 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65670000000</v>
+        <v>65940000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>59340000000</v>
+        <v>63110000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>58680000000</v>
+        <v>59270000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>58140000000</v>
+        <v>59260000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56920000000</v>
+        <v>57420000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>53230000000</v>
+        <v>54270000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,127 +2571,127 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53080000000</v>
+        <v>53940000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>51460000000</v>
+        <v>50930000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>48480000000</v>
+        <v>50870000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47120000000</v>
+        <v>50810000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46700000000</v>
+        <v>48180000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46040000000</v>
+        <v>48030000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46040000000</v>
+        <v>45940000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45970000000</v>
+        <v>45900000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45250000000</v>
+        <v>45700000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,22 +2706,22 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45090000000</v>
+        <v>45290000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>43400000000</v>
+        <v>44060000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,37 +2736,37 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42620000000</v>
+        <v>42400000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39300000000</v>
+        <v>40590000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38120000000</v>
+        <v>39950000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,67 +2781,67 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>36690000000</v>
+        <v>37820000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34590000000</v>
+        <v>37020000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34570000000</v>
+        <v>33960000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>32350000000</v>
+        <v>32200000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31240000000</v>
+        <v>32040000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,37 +2856,37 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30610000000</v>
+        <v>30370000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30320000000</v>
+        <v>30170000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>30170000000</v>
+        <v>29400000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,37 +2901,37 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26830000000</v>
+        <v>26890000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26300000000</v>
+        <v>26510000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24210000000</v>
+        <v>26220000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24150000000</v>
+        <v>23710000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23640000000</v>
+        <v>23360000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,67 +2976,67 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>23040000000</v>
+        <v>22880000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21750000000</v>
+        <v>21620000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>21640000000</v>
+        <v>21610000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>20530000000</v>
+        <v>21600000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>20420000000</v>
+        <v>19990000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16770000000</v>
+        <v>17110000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>14930000000</v>
+        <v>16340000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11710000000</v>
+        <v>11460000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11710000000</v>
+        <v>11460000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11160000000</v>
+        <v>10950000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10560000000</v>
+        <v>10370000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,112 +3141,112 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9980000000</v>
+        <v>9870000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8060000000</v>
+        <v>8300000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7950000000</v>
+        <v>8070000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7660000000</v>
+        <v>7690000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7230000000</v>
+        <v>7640000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7150000000</v>
+        <v>7380000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7110000000</v>
+        <v>7170000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7070000000</v>
+        <v>7020000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,22 +3261,22 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6650000000</v>
+        <v>6840000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6630000000</v>
+        <v>6800000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6530000000</v>
+        <v>6510000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5050000000</v>
+        <v>5540000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4940000000</v>
+        <v>5340000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4260000000</v>
+        <v>4500000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,82 +3351,82 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4110000000</v>
+        <v>4220000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3760000000</v>
+        <v>3910000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3750000000</v>
+        <v>3880000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3570000000</v>
+        <v>3760000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3040000000</v>
+        <v>3060000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2840000000</v>
+        <v>3000000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2420000000</v>
+        <v>2410000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2370000000</v>
+        <v>2340000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1810000000</v>
+        <v>1910000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1700000000</v>
+        <v>1730000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,37 +3501,37 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1670000000</v>
+        <v>1410000000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TDOC</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Teladoc Health Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1170000000</v>
+        <v>1190000000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>TDOC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Teladoc Health Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1100000000</v>
+        <v>1140000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>839840000</v>
+        <v>911260000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>482930000</v>
+        <v>497480000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4918240000000</v>
+        <v>4905540000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5286090000000</v>
+        <v>5356710000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4227030000000</v>
+        <v>4236650000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3696070000000</v>
+        <v>3666590000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2709410000000</v>
+        <v>2736600000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,37 +636,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2231530000000</v>
+        <v>2254410000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1738190000000</v>
+        <v>1707100000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1657880000000</v>
+        <v>1696000000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1446320000000</v>
+        <v>1438700000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1103980000000</v>
+        <v>1147240000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1084860000000</v>
+        <v>1085320000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>980490000000</v>
+        <v>981360000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>928530000000</v>
+        <v>929490000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>889850000000</v>
+        <v>913890000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>847240000000</v>
+        <v>846770000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>690680000000</v>
+        <v>687610000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>671350000000</v>
+        <v>672460000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>651200000000</v>
+        <v>650650000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>628110000000</v>
+        <v>647470000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>495590000000</v>
+        <v>495160000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>466550000000</v>
+        <v>466450000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>455340000000</v>
+        <v>446330000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>434630000000</v>
+        <v>431750000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>423520000000</v>
+        <v>426880000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>418010000000</v>
+        <v>413940000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>406840000000</v>
+        <v>403690000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>396440000000</v>
+        <v>397050000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,112 +966,112 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>378880000000</v>
+        <v>379700000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>374110000000</v>
+        <v>371870000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>367080000000</v>
+        <v>362350000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>363040000000</v>
+        <v>361180000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>342710000000</v>
+        <v>360520000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>336990000000</v>
+        <v>352810000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>336790000000</v>
+        <v>340020000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>331250000000</v>
+        <v>338300000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>325240000000</v>
+        <v>326070000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,142 +1101,142 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>319640000000</v>
+        <v>318170000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>313590000000</v>
+        <v>299290000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>306800000000</v>
+        <v>298930000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>301810000000</v>
+        <v>297410000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>296880000000</v>
+        <v>294350000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>282910000000</v>
+        <v>293990000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>277040000000</v>
+        <v>281470000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>274250000000</v>
+        <v>274280000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>269790000000</v>
+        <v>270500000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>262760000000</v>
+        <v>262360000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,22 +1251,22 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>260850000000</v>
+        <v>261470000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>257960000000</v>
+        <v>260430000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,127 +1281,127 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>257660000000</v>
+        <v>257570000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>251580000000</v>
+        <v>256950000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>246610000000</v>
+        <v>250440000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>246340000000</v>
+        <v>243510000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>243410000000</v>
+        <v>243340000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>236380000000</v>
+        <v>241750000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>235750000000</v>
+        <v>240870000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>229620000000</v>
+        <v>231250000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>223990000000</v>
+        <v>226810000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>222600000000</v>
+        <v>221040000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>220780000000</v>
+        <v>216270000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>211350000000</v>
+        <v>212240000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>210140000000</v>
+        <v>210400000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>205320000000</v>
+        <v>208490000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>203710000000</v>
+        <v>202000000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>200800000000</v>
+        <v>199800000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>199870000000</v>
+        <v>195810000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>198190000000</v>
+        <v>186650000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187100000000</v>
+        <v>186130000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,82 +1566,82 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184860000000</v>
+        <v>184420000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>182430000000</v>
+        <v>182010000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>181910000000</v>
+        <v>180400000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>180940000000</v>
+        <v>177550000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>178550000000</v>
+        <v>177280000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>176900000000</v>
+        <v>177090000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>175830000000</v>
+        <v>175660000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>173980000000</v>
+        <v>174050000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>171240000000</v>
+        <v>173810000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>169550000000</v>
+        <v>167860000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,22 +1716,22 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>165460000000</v>
+        <v>165330000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>155740000000</v>
+        <v>159130000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,22 +1746,22 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>155700000000</v>
+        <v>156650000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>152820000000</v>
+        <v>155180000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>149380000000</v>
+        <v>148900000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>144760000000</v>
+        <v>144680000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>144510000000</v>
+        <v>144000000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>135500000000</v>
+        <v>138950000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131900000000</v>
+        <v>131420000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,52 +1851,52 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>131030000000</v>
+        <v>130700000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>128360000000</v>
+        <v>129320000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128130000000</v>
+        <v>128810000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>127310000000</v>
+        <v>126160000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>125690000000</v>
+        <v>124050000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,112 +1926,112 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>124190000000</v>
+        <v>123100000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>119380000000</v>
+        <v>119490000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119130000000</v>
+        <v>117850000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118910000000</v>
+        <v>117280000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118670000000</v>
+        <v>116080000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116450000000</v>
+        <v>115230000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116380000000</v>
+        <v>112310000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>110640000000</v>
+        <v>110940000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>110200000000</v>
+        <v>109250000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,37 +2061,37 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>108950000000</v>
+        <v>108000000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>108880000000</v>
+        <v>107750000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>108150000000</v>
+        <v>104890000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>107620000000</v>
+        <v>103090000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,67 +2121,67 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>101230000000</v>
+        <v>100780000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>100440000000</v>
+        <v>99530000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>99360000000</v>
+        <v>98950000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93870000000</v>
+        <v>96010000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92970000000</v>
+        <v>93580000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92890000000</v>
+        <v>92600000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92530000000</v>
+        <v>90610000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89840000000</v>
+        <v>89120000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,82 +2241,82 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86060000000</v>
+        <v>87280000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85220000000</v>
+        <v>85550000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84940000000</v>
+        <v>84280000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>84740000000</v>
+        <v>83520000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>83680000000</v>
+        <v>82560000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>83310000000</v>
+        <v>81020000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81280000000</v>
+        <v>80800000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,67 +2346,67 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>77290000000</v>
+        <v>75870000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>76000000000</v>
+        <v>74920000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74440000000</v>
+        <v>74360000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74410000000</v>
+        <v>72740000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72930000000</v>
+        <v>72130000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72610000000</v>
+        <v>71870000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69940000000</v>
+        <v>69730000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>66980000000</v>
+        <v>65940000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66850000000</v>
+        <v>65930000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65940000000</v>
+        <v>64770000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,67 +2496,67 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63110000000</v>
+        <v>61500000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59270000000</v>
+        <v>60770000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59260000000</v>
+        <v>59140000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>57420000000</v>
+        <v>58820000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54270000000</v>
+        <v>57710000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,112 +2571,112 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53940000000</v>
+        <v>52680000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50930000000</v>
+        <v>52680000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50870000000</v>
+        <v>52610000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>50810000000</v>
+        <v>51250000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48180000000</v>
+        <v>50870000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48030000000</v>
+        <v>47210000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>45940000000</v>
+        <v>46720000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45900000000</v>
+        <v>45830000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45700000000</v>
+        <v>45340000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45290000000</v>
+        <v>44870000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44060000000</v>
+        <v>44830000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,37 +2736,37 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42400000000</v>
+        <v>42300000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40590000000</v>
+        <v>40190000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>39950000000</v>
+        <v>38640000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>37820000000</v>
+        <v>37450000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>37020000000</v>
+        <v>36180000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>33960000000</v>
+        <v>33800000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>32200000000</v>
+        <v>32380000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32040000000</v>
+        <v>32170000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30370000000</v>
+        <v>29910000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30170000000</v>
+        <v>29500000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29400000000</v>
+        <v>29020000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26890000000</v>
+        <v>25900000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26510000000</v>
+        <v>25680000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>26220000000</v>
+        <v>25090000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,22 +2946,22 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23710000000</v>
+        <v>24030000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23360000000</v>
+        <v>23300000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,22 +2976,22 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22880000000</v>
+        <v>22820000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21620000000</v>
+        <v>22440000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,22 +3006,22 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>21610000000</v>
+        <v>21910000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>21600000000</v>
+        <v>21060000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>19990000000</v>
+        <v>19350000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>17110000000</v>
+        <v>18370000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16340000000</v>
+        <v>15850000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11460000000</v>
+        <v>11400000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11460000000</v>
+        <v>11400000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10950000000</v>
+        <v>11000000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10370000000</v>
+        <v>10530000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,52 +3141,52 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9870000000</v>
+        <v>9920000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8300000000</v>
+        <v>8200000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8070000000</v>
+        <v>8130000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7690000000</v>
+        <v>7830000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,37 +3201,37 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7640000000</v>
+        <v>7430000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7380000000</v>
+        <v>7090000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7170000000</v>
+        <v>7070000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7020000000</v>
+        <v>6990000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6840000000</v>
+        <v>6820000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6800000000</v>
+        <v>6730000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6510000000</v>
+        <v>6530000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5540000000</v>
+        <v>5470000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5340000000</v>
+        <v>5260000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4500000000</v>
+        <v>5110000000</v>
       </c>
     </row>
     <row r="191">
@@ -3366,67 +3366,67 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3910000000</v>
+        <v>3800000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3880000000</v>
+        <v>3640000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3760000000</v>
+        <v>3550000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3060000000</v>
+        <v>3000000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3000000000</v>
+        <v>2970000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2410000000</v>
+        <v>2430000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2340000000</v>
+        <v>2210000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1910000000</v>
+        <v>1970000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1730000000</v>
+        <v>1680000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1410000000</v>
+        <v>1350000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1190000000</v>
+        <v>1160000000</v>
       </c>
     </row>
     <row r="203">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>911260000</v>
+        <v>844670000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>497480000</v>
+        <v>466060000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4236650000000</v>
+        <v>4246520000000</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>981360000000</v>
+        <v>980780000000</v>
       </c>
     </row>
     <row r="17">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6730000000</v>
+        <v>6720000000</v>
       </c>
     </row>
     <row r="187">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4905540000000</v>
+        <v>4947140000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5356710000000</v>
+        <v>5479860000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4246520000000</v>
+        <v>4326170000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3666590000000</v>
+        <v>3724730000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2736600000000</v>
+        <v>2787720000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,37 +636,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2254410000000</v>
+        <v>2308710000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1707100000000</v>
+        <v>1888330000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1696000000000</v>
+        <v>1731200000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1438700000000</v>
+        <v>1482270000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1147240000000</v>
+        <v>1179040000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,52 +711,52 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1085320000000</v>
+        <v>1096580000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>980780000000</v>
+        <v>1004820000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>929490000000</v>
+        <v>965850000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>913890000000</v>
+        <v>935790000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>846770000000</v>
+        <v>852400000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,52 +786,52 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>687610000000</v>
+        <v>690710000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>672460000000</v>
+        <v>659580000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>650650000000</v>
+        <v>650920000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>647470000000</v>
+        <v>649400000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>495160000000</v>
+        <v>497270000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>466450000000</v>
+        <v>467370000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,67 +876,67 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>446330000000</v>
+        <v>449210000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>431750000000</v>
+        <v>439980000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>426880000000</v>
+        <v>439440000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>413940000000</v>
+        <v>405300000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>403690000000</v>
+        <v>402410000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>397050000000</v>
+        <v>398460000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>379700000000</v>
+        <v>378250000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,142 +981,142 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>371870000000</v>
+        <v>375320000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>362350000000</v>
+        <v>374840000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>361180000000</v>
+        <v>368840000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>360520000000</v>
+        <v>368420000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>352810000000</v>
+        <v>365790000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>340020000000</v>
+        <v>344860000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>338300000000</v>
+        <v>339300000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>326070000000</v>
+        <v>338900000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>318170000000</v>
+        <v>330990000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>299290000000</v>
+        <v>323730000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>298930000000</v>
+        <v>305470000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,22 +1146,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>297410000000</v>
+        <v>304100000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>294350000000</v>
+        <v>296510000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>293990000000</v>
+        <v>292210000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>281470000000</v>
+        <v>287710000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>274280000000</v>
+        <v>279350000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,67 +1221,67 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>270500000000</v>
+        <v>266780000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>262360000000</v>
+        <v>261920000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>261470000000</v>
+        <v>261700000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>260430000000</v>
+        <v>260700000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>257570000000</v>
+        <v>258670000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,82 +1296,82 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>256950000000</v>
+        <v>258070000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>250440000000</v>
+        <v>255320000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>243510000000</v>
+        <v>252010000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>243340000000</v>
+        <v>247370000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>241750000000</v>
+        <v>243570000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>240870000000</v>
+        <v>241480000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>231250000000</v>
+        <v>240370000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>226810000000</v>
+        <v>227950000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>221040000000</v>
+        <v>226540000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,22 +1431,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>216270000000</v>
+        <v>218510000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>212240000000</v>
+        <v>212550000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,82 +1461,82 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>210400000000</v>
+        <v>211770000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>208490000000</v>
+        <v>210900000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>202000000000</v>
+        <v>203990000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>199800000000</v>
+        <v>200310000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>195810000000</v>
+        <v>198100000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>186650000000</v>
+        <v>194570000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,52 +1551,52 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>186130000000</v>
+        <v>186690000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184420000000</v>
+        <v>184830000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>182010000000</v>
+        <v>184620000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>180400000000</v>
+        <v>179970000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,112 +1611,112 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177550000000</v>
+        <v>178190000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>177280000000</v>
+        <v>177450000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>177090000000</v>
+        <v>177280000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>175660000000</v>
+        <v>177140000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>174050000000</v>
+        <v>176880000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>173810000000</v>
+        <v>175410000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>167860000000</v>
+        <v>174390000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>165330000000</v>
+        <v>166110000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159130000000</v>
+        <v>161580000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>156650000000</v>
+        <v>158980000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>155180000000</v>
+        <v>156980000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,67 +1776,67 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>148900000000</v>
+        <v>151730000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>144680000000</v>
+        <v>144690000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>144000000000</v>
+        <v>141890000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>138950000000</v>
+        <v>136940000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131420000000</v>
+        <v>133170000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,22 +1851,22 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>130700000000</v>
+        <v>131650000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>129320000000</v>
+        <v>130110000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128810000000</v>
+        <v>127910000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,22 +1896,22 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126160000000</v>
+        <v>126620000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124050000000</v>
+        <v>125220000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,142 +1926,142 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123100000000</v>
+        <v>123570000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>119490000000</v>
+        <v>123330000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>117850000000</v>
+        <v>119740000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>117280000000</v>
+        <v>119240000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>116080000000</v>
+        <v>117360000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>115230000000</v>
+        <v>114430000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>112310000000</v>
+        <v>113890000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>110940000000</v>
+        <v>112870000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>109250000000</v>
+        <v>110490000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>108000000000</v>
+        <v>108190000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,37 +2076,37 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>107750000000</v>
+        <v>107240000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104890000000</v>
+        <v>107150000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103090000000</v>
+        <v>106390000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100780000000</v>
+        <v>104320000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99530000000</v>
+        <v>99900000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>98950000000</v>
+        <v>99180000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>96010000000</v>
+        <v>96580000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,37 +2181,37 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93580000000</v>
+        <v>94170000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92600000000</v>
+        <v>92290000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90610000000</v>
+        <v>92220000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,52 +2226,52 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89120000000</v>
+        <v>88770000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87280000000</v>
+        <v>87990000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85550000000</v>
+        <v>87220000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84280000000</v>
+        <v>85080000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,22 +2286,22 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>83520000000</v>
+        <v>82420000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>82560000000</v>
+        <v>82180000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,22 +2316,22 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>81020000000</v>
+        <v>81270000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>80800000000</v>
+        <v>80610000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,67 +2346,67 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75870000000</v>
+        <v>76820000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74920000000</v>
+        <v>75540000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74360000000</v>
+        <v>74820000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>72740000000</v>
+        <v>73660000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72130000000</v>
+        <v>72530000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,127 +2421,127 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>71870000000</v>
+        <v>71650000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69730000000</v>
+        <v>69040000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>65940000000</v>
+        <v>68760000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65930000000</v>
+        <v>67920000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64770000000</v>
+        <v>67120000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>61500000000</v>
+        <v>66280000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60770000000</v>
+        <v>64740000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59140000000</v>
+        <v>63290000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>58820000000</v>
+        <v>59110000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,67 +2556,67 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>57710000000</v>
+        <v>58200000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>52680000000</v>
+        <v>57230000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52680000000</v>
+        <v>53550000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52610000000</v>
+        <v>53040000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>51250000000</v>
+        <v>52520000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>50870000000</v>
+        <v>50920000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,22 +2646,22 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47210000000</v>
+        <v>47250000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46720000000</v>
+        <v>47120000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,37 +2676,37 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45830000000</v>
+        <v>46810000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45340000000</v>
+        <v>46250000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44870000000</v>
+        <v>45740000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44830000000</v>
+        <v>45010000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,52 +2736,52 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42300000000</v>
+        <v>41940000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40190000000</v>
+        <v>41830000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38640000000</v>
+        <v>40860000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>37450000000</v>
+        <v>40640000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>36180000000</v>
+        <v>36060000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>33800000000</v>
+        <v>34860000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>32380000000</v>
+        <v>33770000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32170000000</v>
+        <v>32810000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,67 +2856,67 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29910000000</v>
+        <v>30560000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29500000000</v>
+        <v>30540000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29020000000</v>
+        <v>29480000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25900000000</v>
+        <v>27070000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25680000000</v>
+        <v>26520000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25090000000</v>
+        <v>24710000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24030000000</v>
+        <v>23990000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23300000000</v>
+        <v>23970000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,37 +2976,37 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22820000000</v>
+        <v>22920000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>22440000000</v>
+        <v>21920000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>21910000000</v>
+        <v>21600000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>21060000000</v>
+        <v>21480000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>19350000000</v>
+        <v>19540000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>18370000000</v>
+        <v>18590000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15850000000</v>
+        <v>16410000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11400000000</v>
+        <v>11870000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,37 +3096,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11400000000</v>
+        <v>11870000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11000000000</v>
+        <v>10960000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10530000000</v>
+        <v>10870000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,157 +3141,157 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9920000000</v>
+        <v>9660000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8200000000</v>
+        <v>8280000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8130000000</v>
+        <v>8220000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7830000000</v>
+        <v>8180000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7430000000</v>
+        <v>7470000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7090000000</v>
+        <v>7410000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7070000000</v>
+        <v>7090000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6990000000</v>
+        <v>6910000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6820000000</v>
+        <v>6850000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6720000000</v>
+        <v>6840000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6530000000</v>
+        <v>6790000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5470000000</v>
+        <v>5640000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5260000000</v>
+        <v>5520000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,97 +3336,97 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5110000000</v>
+        <v>5130000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4220000000</v>
+        <v>4370000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3800000000</v>
+        <v>4220000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3640000000</v>
+        <v>3780000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3550000000</v>
+        <v>3700000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3000000000</v>
+        <v>3170000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2970000000</v>
+        <v>3030000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2430000000</v>
+        <v>2490000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2210000000</v>
+        <v>2160000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1970000000</v>
+        <v>2030000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1680000000</v>
+        <v>1740000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1350000000</v>
+        <v>1360000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1160000000</v>
+        <v>1210000000</v>
       </c>
     </row>
     <row r="203">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>844670000</v>
+        <v>918240000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>466060000</v>
+        <v>487520000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4947140000000</v>
+        <v>4958370000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5479860000000</v>
+        <v>5515770000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4326170000000</v>
+        <v>4276040000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3724730000000</v>
+        <v>3697920000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2787720000000</v>
+        <v>2750290000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2308710000000</v>
+        <v>2344290000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1888330000000</v>
+        <v>1876480000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1731200000000</v>
+        <v>1740180000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1482270000000</v>
+        <v>1496480000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1179040000000</v>
+        <v>1238000000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1096580000000</v>
+        <v>1101520000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1004820000000</v>
+        <v>1018290000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>965850000000</v>
+        <v>968800000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>935790000000</v>
+        <v>903780000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>852400000000</v>
+        <v>873660000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>690710000000</v>
+        <v>675950000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>659580000000</v>
+        <v>673680000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>650920000000</v>
+        <v>652600000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>649400000000</v>
+        <v>648720000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>497270000000</v>
+        <v>486970000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>467370000000</v>
+        <v>468660000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>449210000000</v>
+        <v>451140000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>439980000000</v>
+        <v>444540000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,52 +906,52 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>439440000000</v>
+        <v>419650000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>405300000000</v>
+        <v>399920000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>402410000000</v>
+        <v>398870000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>398460000000</v>
+        <v>392990000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,37 +966,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>378250000000</v>
+        <v>389110000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>375320000000</v>
+        <v>381250000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>374840000000</v>
+        <v>374940000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,52 +1011,52 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>368840000000</v>
+        <v>372320000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>368420000000</v>
+        <v>371420000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>365790000000</v>
+        <v>355860000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>344860000000</v>
+        <v>349010000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>339300000000</v>
+        <v>344270000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>338900000000</v>
+        <v>334760000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>330990000000</v>
+        <v>331210000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,52 +1116,52 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>323730000000</v>
+        <v>314400000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>305470000000</v>
+        <v>306400000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>304100000000</v>
+        <v>304640000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>296510000000</v>
+        <v>300470000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>292210000000</v>
+        <v>296500000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>287710000000</v>
+        <v>289100000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,127 +1206,127 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>279350000000</v>
+        <v>276460000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>266780000000</v>
+        <v>276300000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>261920000000</v>
+        <v>268670000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>261700000000</v>
+        <v>261120000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>260700000000</v>
+        <v>258620000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>258670000000</v>
+        <v>257410000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>258070000000</v>
+        <v>256050000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>255320000000</v>
+        <v>253090000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>252010000000</v>
+        <v>251450000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,52 +1341,52 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>247370000000</v>
+        <v>247860000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>243570000000</v>
+        <v>246050000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>241480000000</v>
+        <v>243490000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>240370000000</v>
+        <v>243170000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>227950000000</v>
+        <v>227430000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,82 +1416,82 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>226540000000</v>
+        <v>222210000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>218510000000</v>
+        <v>221790000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>212550000000</v>
+        <v>217990000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>211770000000</v>
+        <v>214310000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>210900000000</v>
+        <v>208230000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>203990000000</v>
+        <v>206020000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>200310000000</v>
+        <v>199840000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>198100000000</v>
+        <v>192990000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,157 +1536,157 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>194570000000</v>
+        <v>191990000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>186690000000</v>
+        <v>190090000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184830000000</v>
+        <v>189580000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184620000000</v>
+        <v>189300000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>179970000000</v>
+        <v>179420000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>178190000000</v>
+        <v>179260000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>177450000000</v>
+        <v>179060000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>177280000000</v>
+        <v>177160000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>177140000000</v>
+        <v>174210000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>176880000000</v>
+        <v>173540000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>175410000000</v>
+        <v>173310000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,37 +1701,37 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>174390000000</v>
+        <v>171990000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>166110000000</v>
+        <v>167510000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>161580000000</v>
+        <v>165330000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,37 +1746,37 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>158980000000</v>
+        <v>156270000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>156980000000</v>
+        <v>155420000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>151730000000</v>
+        <v>154000000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>144690000000</v>
+        <v>142750000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>141890000000</v>
+        <v>142050000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>136940000000</v>
+        <v>137560000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>133170000000</v>
+        <v>131830000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>131650000000</v>
+        <v>131710000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>130110000000</v>
+        <v>129540000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,37 +1881,37 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>127910000000</v>
+        <v>127160000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126620000000</v>
+        <v>125700000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>125220000000</v>
+        <v>123390000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123570000000</v>
+        <v>120550000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123330000000</v>
+        <v>120250000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119740000000</v>
+        <v>118750000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119240000000</v>
+        <v>118640000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117360000000</v>
+        <v>116110000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,337 +2001,337 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>114430000000</v>
+        <v>114610000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113890000000</v>
+        <v>114370000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>112870000000</v>
+        <v>112430000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>110490000000</v>
+        <v>110010000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>108190000000</v>
+        <v>110010000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>107240000000</v>
+        <v>108430000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>107150000000</v>
+        <v>107120000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>106390000000</v>
+        <v>104520000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>104320000000</v>
+        <v>103210000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99900000000</v>
+        <v>97580000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>99180000000</v>
+        <v>96890000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>96580000000</v>
+        <v>94850000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94170000000</v>
+        <v>94700000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92290000000</v>
+        <v>92610000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92220000000</v>
+        <v>92600000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>88770000000</v>
+        <v>88860000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87990000000</v>
+        <v>87310000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>87220000000</v>
+        <v>87270000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85080000000</v>
+        <v>85850000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82420000000</v>
+        <v>82770000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>82180000000</v>
+        <v>81560000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>81270000000</v>
+        <v>81130000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>80610000000</v>
+        <v>78130000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76820000000</v>
+        <v>77350000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,82 +2361,82 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75540000000</v>
+        <v>73320000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74820000000</v>
+        <v>73220000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>73660000000</v>
+        <v>72880000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72530000000</v>
+        <v>72430000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>71650000000</v>
+        <v>72330000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69040000000</v>
+        <v>72240000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68760000000</v>
+        <v>69390000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,82 +2466,82 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67920000000</v>
+        <v>68400000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>67120000000</v>
+        <v>65830000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>66280000000</v>
+        <v>64290000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>64740000000</v>
+        <v>64190000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>63290000000</v>
+        <v>63050000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>59110000000</v>
+        <v>63000000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>58200000000</v>
+        <v>58780000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>57230000000</v>
+        <v>56290000000</v>
       </c>
     </row>
     <row r="140">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>53040000000</v>
+        <v>53050000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>52520000000</v>
+        <v>52240000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>50920000000</v>
+        <v>51170000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47250000000</v>
+        <v>47850000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47120000000</v>
+        <v>47130000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,37 +2676,37 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46810000000</v>
+        <v>46580000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46250000000</v>
+        <v>45900000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45740000000</v>
+        <v>45360000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,22 +2721,22 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>45010000000</v>
+        <v>45250000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>41940000000</v>
+        <v>43700000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,22 +2751,22 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>41830000000</v>
+        <v>43080000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>40860000000</v>
+        <v>41290000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40640000000</v>
+        <v>39900000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>36060000000</v>
+        <v>37370000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34860000000</v>
+        <v>36280000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33770000000</v>
+        <v>34270000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32810000000</v>
+        <v>32930000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,37 +2856,37 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30560000000</v>
+        <v>30520000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30540000000</v>
+        <v>30110000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29480000000</v>
+        <v>29950000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27070000000</v>
+        <v>27290000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26520000000</v>
+        <v>26540000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24710000000</v>
+        <v>24510000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23990000000</v>
+        <v>24220000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23970000000</v>
+        <v>24010000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22920000000</v>
+        <v>22910000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21920000000</v>
+        <v>22160000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>21600000000</v>
+        <v>21580000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>21480000000</v>
+        <v>20530000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>19540000000</v>
+        <v>19390000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>18590000000</v>
+        <v>19110000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16410000000</v>
+        <v>16510000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11870000000</v>
+        <v>12930000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,37 +3096,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11870000000</v>
+        <v>12930000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10960000000</v>
+        <v>10900000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10870000000</v>
+        <v>10410000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,37 +3141,37 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9660000000</v>
+        <v>9470000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8280000000</v>
+        <v>8320000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8220000000</v>
+        <v>8300000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>8180000000</v>
+        <v>7940000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,67 +3201,67 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7470000000</v>
+        <v>7520000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7410000000</v>
+        <v>7440000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7090000000</v>
+        <v>7110000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6910000000</v>
+        <v>7100000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6850000000</v>
+        <v>6980000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6840000000</v>
+        <v>6770000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6790000000</v>
+        <v>6530000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5640000000</v>
+        <v>5710000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5520000000</v>
+        <v>5510000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5130000000</v>
+        <v>5270000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4370000000</v>
+        <v>4500000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4220000000</v>
+        <v>4150000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3780000000</v>
+        <v>3820000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3700000000</v>
+        <v>3690000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3170000000</v>
+        <v>3230000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3030000000</v>
+        <v>3050000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2490000000</v>
+        <v>2530000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2160000000</v>
+        <v>2130000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2030000000</v>
+        <v>2060000000</v>
       </c>
     </row>
     <row r="200">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1360000000</v>
+        <v>1340000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1210000000</v>
+        <v>1200000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1140000000</v>
+        <v>1150000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>918240000</v>
+        <v>930050000</v>
       </c>
     </row>
     <row r="205">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4958370000000</v>
+        <v>4918530000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5515770000000</v>
+        <v>5434790000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4276040000000</v>
+        <v>4121040000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3697920000000</v>
+        <v>3717150000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2750290000000</v>
+        <v>2688700000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2344290000000</v>
+        <v>2316130000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1876480000000</v>
+        <v>1895600000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1740180000000</v>
+        <v>1694590000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1496480000000</v>
+        <v>1501300000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1238000000000</v>
+        <v>1210570000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1101520000000</v>
+        <v>1083490000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1018290000000</v>
+        <v>1003340000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>968800000000</v>
+        <v>976500000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>903780000000</v>
+        <v>897220000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>873660000000</v>
+        <v>876920000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>675950000000</v>
+        <v>674970000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>673680000000</v>
+        <v>672410000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>652600000000</v>
+        <v>662960000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>648720000000</v>
+        <v>648670000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>486970000000</v>
+        <v>490500000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,37 +861,37 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>468660000000</v>
+        <v>468430000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>451140000000</v>
+        <v>460880000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>444540000000</v>
+        <v>437110000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>419650000000</v>
+        <v>419610000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>399920000000</v>
+        <v>406040000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>398870000000</v>
+        <v>401220000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>392990000000</v>
+        <v>391590000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>389110000000</v>
+        <v>384510000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>381250000000</v>
+        <v>379010000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,37 +996,37 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>374940000000</v>
+        <v>376470000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>372320000000</v>
+        <v>373270000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>371420000000</v>
+        <v>365340000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>355860000000</v>
+        <v>355170000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>349010000000</v>
+        <v>349590000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>344270000000</v>
+        <v>342340000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>334760000000</v>
+        <v>333270000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,52 +1101,52 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>331210000000</v>
+        <v>331810000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>314400000000</v>
+        <v>321720000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>306400000000</v>
+        <v>311580000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>304640000000</v>
+        <v>297450000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,22 +1161,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>300470000000</v>
+        <v>297140000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>296500000000</v>
+        <v>296030000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,67 +1191,67 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>289100000000</v>
+        <v>275410000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>276460000000</v>
+        <v>272820000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>276300000000</v>
+        <v>272640000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>268670000000</v>
+        <v>268770000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>261120000000</v>
+        <v>265980000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>258620000000</v>
+        <v>261240000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,97 +1281,97 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>257410000000</v>
+        <v>259030000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>256050000000</v>
+        <v>253500000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>253090000000</v>
+        <v>253310000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>251450000000</v>
+        <v>248970000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>247860000000</v>
+        <v>247670000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>246050000000</v>
+        <v>245990000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>243490000000</v>
+        <v>245450000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>243170000000</v>
+        <v>243100000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>227430000000</v>
+        <v>225420000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>222210000000</v>
+        <v>221300000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>221790000000</v>
+        <v>219550000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>217990000000</v>
+        <v>219290000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>214310000000</v>
+        <v>216530000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>208230000000</v>
+        <v>207150000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>206020000000</v>
+        <v>203920000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,82 +1506,82 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>199840000000</v>
+        <v>203890000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>192990000000</v>
+        <v>195530000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>191990000000</v>
+        <v>193280000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>190090000000</v>
+        <v>191290000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>189580000000</v>
+        <v>187690000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>189300000000</v>
+        <v>183140000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>179420000000</v>
+        <v>179080000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,112 +1611,112 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>179260000000</v>
+        <v>178640000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>179060000000</v>
+        <v>177700000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>177160000000</v>
+        <v>177680000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>174210000000</v>
+        <v>173370000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>173540000000</v>
+        <v>172370000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>173310000000</v>
+        <v>172070000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>171990000000</v>
+        <v>170780000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>167510000000</v>
+        <v>168650000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>165330000000</v>
+        <v>160660000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>156270000000</v>
+        <v>158020000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>155420000000</v>
+        <v>155750000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>154000000000</v>
+        <v>148110000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>142750000000</v>
+        <v>141790000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142050000000</v>
+        <v>140710000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,187 +1821,187 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137560000000</v>
+        <v>133070000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131830000000</v>
+        <v>129840000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>131710000000</v>
+        <v>129320000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>129540000000</v>
+        <v>127710000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>127160000000</v>
+        <v>125460000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>125700000000</v>
+        <v>124910000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>123390000000</v>
+        <v>121090000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>120550000000</v>
+        <v>119840000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120250000000</v>
+        <v>118120000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>118750000000</v>
+        <v>118040000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118640000000</v>
+        <v>117140000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>116110000000</v>
+        <v>115130000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>114610000000</v>
+        <v>114230000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>114370000000</v>
+        <v>112730000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>112430000000</v>
+        <v>112300000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,82 +2046,82 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>110010000000</v>
+        <v>107360000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>110010000000</v>
+        <v>107320000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>108430000000</v>
+        <v>105500000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>107120000000</v>
+        <v>105080000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>104520000000</v>
+        <v>104750000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>103210000000</v>
+        <v>102390000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,22 +2136,22 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>97580000000</v>
+        <v>95780000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96890000000</v>
+        <v>95670000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94850000000</v>
+        <v>94500000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94700000000</v>
+        <v>91220000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,37 +2196,37 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92610000000</v>
+        <v>91110000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92600000000</v>
+        <v>90300000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>88860000000</v>
+        <v>89570000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87310000000</v>
+        <v>87830000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>87270000000</v>
+        <v>87770000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85850000000</v>
+        <v>86440000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82770000000</v>
+        <v>82550000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>81560000000</v>
+        <v>81520000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,127 +2316,127 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>81130000000</v>
+        <v>81310000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>78130000000</v>
+        <v>76980000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>77350000000</v>
+        <v>76640000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>73320000000</v>
+        <v>73500000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73220000000</v>
+        <v>73440000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>72880000000</v>
+        <v>73080000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72430000000</v>
+        <v>72700000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72330000000</v>
+        <v>70990000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>72240000000</v>
+        <v>70890000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,82 +2451,82 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69390000000</v>
+        <v>68500000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68400000000</v>
+        <v>65790000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65830000000</v>
+        <v>65790000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64290000000</v>
+        <v>62530000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>64190000000</v>
+        <v>62320000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>63050000000</v>
+        <v>61610000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>63000000000</v>
+        <v>61590000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>58780000000</v>
+        <v>58560000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>56290000000</v>
+        <v>57340000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53550000000</v>
+        <v>53480000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>53050000000</v>
+        <v>52270000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>52240000000</v>
+        <v>51600000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>51170000000</v>
+        <v>50040000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,37 +2646,37 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47850000000</v>
+        <v>47930000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47130000000</v>
+        <v>46360000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46580000000</v>
+        <v>46310000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45900000000</v>
+        <v>45380000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45360000000</v>
+        <v>44920000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>45250000000</v>
+        <v>44870000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>43700000000</v>
+        <v>44640000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>43080000000</v>
+        <v>42080000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41290000000</v>
+        <v>41390000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>39900000000</v>
+        <v>40400000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>37370000000</v>
+        <v>38560000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>36280000000</v>
+        <v>35760000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34270000000</v>
+        <v>34970000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32930000000</v>
+        <v>32660000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30520000000</v>
+        <v>29860000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30110000000</v>
+        <v>29590000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29950000000</v>
+        <v>29240000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27290000000</v>
+        <v>27220000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26540000000</v>
+        <v>26810000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24510000000</v>
+        <v>24430000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24220000000</v>
+        <v>23290000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>24010000000</v>
+        <v>22980000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22910000000</v>
+        <v>22790000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>22160000000</v>
+        <v>21380000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>21580000000</v>
+        <v>20630000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>20530000000</v>
+        <v>20420000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>19390000000</v>
+        <v>18900000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>19110000000</v>
+        <v>18520000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16510000000</v>
+        <v>17230000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12930000000</v>
+        <v>13050000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12930000000</v>
+        <v>13050000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10900000000</v>
+        <v>10820000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10410000000</v>
+        <v>10450000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,37 +3141,37 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9470000000</v>
+        <v>9420000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8320000000</v>
+        <v>8390000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8300000000</v>
+        <v>7940000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,37 +3186,37 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7940000000</v>
+        <v>7920000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7520000000</v>
+        <v>7380000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7440000000</v>
+        <v>7220000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,67 +3231,67 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7110000000</v>
+        <v>7150000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>7100000000</v>
+        <v>6710000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6980000000</v>
+        <v>6620000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6770000000</v>
+        <v>6470000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6530000000</v>
+        <v>6470000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5710000000</v>
+        <v>5390000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5510000000</v>
+        <v>5340000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5270000000</v>
+        <v>5160000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4500000000</v>
+        <v>4720000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4150000000</v>
+        <v>4310000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3820000000</v>
+        <v>3730000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3690000000</v>
+        <v>3430000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3230000000</v>
+        <v>3090000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3050000000</v>
+        <v>3020000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2530000000</v>
+        <v>2380000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2130000000</v>
+        <v>2090000000</v>
       </c>
     </row>
     <row r="199">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1740000000</v>
+        <v>1750000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1340000000</v>
+        <v>1400000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1200000000</v>
+        <v>1130000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1150000000</v>
+        <v>1110000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>930050000</v>
+        <v>913400000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>487520000</v>
+        <v>461460000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4918530000000</v>
+        <v>4902480000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5434790000000</v>
+        <v>5412380000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4121040000000</v>
+        <v>4165430000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3717150000000</v>
+        <v>3697400000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2688700000000</v>
+        <v>2689890000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2316130000000</v>
+        <v>2339880000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1895600000000</v>
+        <v>1980920000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1694590000000</v>
+        <v>1672490000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1501300000000</v>
+        <v>1492690000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1210570000000</v>
+        <v>1220340000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1083490000000</v>
+        <v>1112580000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1003340000000</v>
+        <v>1027250000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>976500000000</v>
+        <v>974540000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>897220000000</v>
+        <v>899960000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>876920000000</v>
+        <v>853590000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>674970000000</v>
+        <v>687040000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>672410000000</v>
+        <v>666710000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>662960000000</v>
+        <v>663890000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>648670000000</v>
+        <v>652310000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>490500000000</v>
+        <v>495890000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>468430000000</v>
+        <v>468500000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>460880000000</v>
+        <v>462800000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>437110000000</v>
+        <v>421930000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>419610000000</v>
+        <v>421740000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>406040000000</v>
+        <v>406320000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>401220000000</v>
+        <v>397570000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>391590000000</v>
+        <v>391800000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>384510000000</v>
+        <v>384360000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>379010000000</v>
+        <v>379050000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>376470000000</v>
+        <v>376360000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>373270000000</v>
+        <v>370150000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,82 +1026,82 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>365340000000</v>
+        <v>365090000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>355170000000</v>
+        <v>340810000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>349590000000</v>
+        <v>338370000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>342340000000</v>
+        <v>336610000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>333270000000</v>
+        <v>331790000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>331810000000</v>
+        <v>327170000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>321720000000</v>
+        <v>318950000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,37 +1131,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>311580000000</v>
+        <v>308330000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>297450000000</v>
+        <v>298640000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>297140000000</v>
+        <v>298470000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>296030000000</v>
+        <v>291500000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>275410000000</v>
+        <v>274990000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>272820000000</v>
+        <v>273270000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>272640000000</v>
+        <v>268840000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,52 +1236,52 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>268770000000</v>
+        <v>265890000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>265980000000</v>
+        <v>262810000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261240000000</v>
+        <v>256760000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>259030000000</v>
+        <v>255210000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,37 +1296,37 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>253500000000</v>
+        <v>254360000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>253310000000</v>
+        <v>254200000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>248970000000</v>
+        <v>250830000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,22 +1341,22 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>247670000000</v>
+        <v>248510000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>245990000000</v>
+        <v>247170000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>245450000000</v>
+        <v>244180000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,37 +1386,37 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>243100000000</v>
+        <v>241350000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>225420000000</v>
+        <v>221590000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>221300000000</v>
+        <v>221110000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,112 +1431,112 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>219550000000</v>
+        <v>219520000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>219290000000</v>
+        <v>215800000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>216530000000</v>
+        <v>213920000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>207150000000</v>
+        <v>206420000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>203920000000</v>
+        <v>204380000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>203890000000</v>
+        <v>204020000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>195530000000</v>
+        <v>196600000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>193280000000</v>
+        <v>196060000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,127 +1551,127 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>191290000000</v>
+        <v>187370000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>187690000000</v>
+        <v>186770000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>183140000000</v>
+        <v>185610000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>179080000000</v>
+        <v>182270000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>178640000000</v>
+        <v>177370000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>177700000000</v>
+        <v>174910000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>177680000000</v>
+        <v>174890000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>173370000000</v>
+        <v>174410000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>172370000000</v>
+        <v>174390000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,37 +1686,37 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>172070000000</v>
+        <v>172050000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>170780000000</v>
+        <v>167730000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>168650000000</v>
+        <v>162360000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,37 +1731,37 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>160660000000</v>
+        <v>157740000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>158020000000</v>
+        <v>157310000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>155750000000</v>
+        <v>155540000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>148110000000</v>
+        <v>145560000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>141790000000</v>
+        <v>141390000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>140710000000</v>
+        <v>141140000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>133070000000</v>
+        <v>132780000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,37 +1836,37 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>129840000000</v>
+        <v>129710000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>129320000000</v>
+        <v>129220000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>127710000000</v>
+        <v>129180000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>125460000000</v>
+        <v>127770000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>124910000000</v>
+        <v>125630000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>121090000000</v>
+        <v>120870000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,52 +1926,52 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>119840000000</v>
+        <v>118880000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>118120000000</v>
+        <v>118270000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>118040000000</v>
+        <v>117840000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>117140000000</v>
+        <v>117480000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>115130000000</v>
+        <v>115010000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>114230000000</v>
+        <v>113220000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>112730000000</v>
+        <v>111310000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,67 +2031,67 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>112300000000</v>
+        <v>108560000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107360000000</v>
+        <v>106760000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>107320000000</v>
+        <v>105750000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>105500000000</v>
+        <v>105280000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>105080000000</v>
+        <v>104570000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>104750000000</v>
+        <v>104520000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>102390000000</v>
+        <v>102100000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>95780000000</v>
+        <v>94440000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,37 +2151,37 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>95670000000</v>
+        <v>92990000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94500000000</v>
+        <v>92250000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>91220000000</v>
+        <v>91680000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,67 +2196,67 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91110000000</v>
+        <v>90990000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90300000000</v>
+        <v>90650000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89570000000</v>
+        <v>88930000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87830000000</v>
+        <v>88100000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>87770000000</v>
+        <v>86390000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>86440000000</v>
+        <v>86370000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,142 +2286,142 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82550000000</v>
+        <v>81950000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>81520000000</v>
+        <v>81090000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>81310000000</v>
+        <v>78310000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76980000000</v>
+        <v>77780000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76640000000</v>
+        <v>76330000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>73500000000</v>
+        <v>74060000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73440000000</v>
+        <v>72310000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>73080000000</v>
+        <v>71270000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72700000000</v>
+        <v>70940000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70990000000</v>
+        <v>70700000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70890000000</v>
+        <v>70160000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,127 +2451,127 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68500000000</v>
+        <v>68010000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65790000000</v>
+        <v>66190000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65790000000</v>
+        <v>65590000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62530000000</v>
+        <v>65500000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62320000000</v>
+        <v>63920000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61610000000</v>
+        <v>62540000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>61590000000</v>
+        <v>62090000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>58560000000</v>
+        <v>58030000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>57340000000</v>
+        <v>57110000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53480000000</v>
+        <v>53390000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52270000000</v>
+        <v>52560000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,127 +2616,127 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>51600000000</v>
+        <v>50240000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>50040000000</v>
+        <v>49710000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47930000000</v>
+        <v>49410000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46360000000</v>
+        <v>46300000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46310000000</v>
+        <v>46110000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45380000000</v>
+        <v>46030000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44920000000</v>
+        <v>46020000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44870000000</v>
+        <v>45000000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>44640000000</v>
+        <v>44170000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,82 +2751,82 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>42080000000</v>
+        <v>44050000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41390000000</v>
+        <v>41360000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40400000000</v>
+        <v>40510000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38560000000</v>
+        <v>40430000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35760000000</v>
+        <v>35000000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34970000000</v>
+        <v>34500000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32660000000</v>
+        <v>32170000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,37 +2856,37 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29860000000</v>
+        <v>29840000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29590000000</v>
+        <v>29380000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29240000000</v>
+        <v>29040000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27220000000</v>
+        <v>27270000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26810000000</v>
+        <v>26360000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24430000000</v>
+        <v>24450000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23290000000</v>
+        <v>24150000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22980000000</v>
+        <v>23730000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22790000000</v>
+        <v>22770000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,82 +2991,82 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21380000000</v>
+        <v>21700000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>20630000000</v>
+        <v>20580000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>20420000000</v>
+        <v>18920000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18900000000</v>
+        <v>18500000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>18520000000</v>
+        <v>18220000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>17230000000</v>
+        <v>18160000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13050000000</v>
+        <v>12680000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,37 +3096,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13050000000</v>
+        <v>12680000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10820000000</v>
+        <v>10600000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10450000000</v>
+        <v>10600000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9420000000</v>
+        <v>8910000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,37 +3156,37 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8390000000</v>
+        <v>8350000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7940000000</v>
+        <v>8060000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7920000000</v>
+        <v>7890000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7380000000</v>
+        <v>7190000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7220000000</v>
+        <v>7120000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,37 +3231,37 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7150000000</v>
+        <v>7000000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6710000000</v>
+        <v>6830000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6620000000</v>
+        <v>6730000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6470000000</v>
+        <v>6540000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6470000000</v>
+        <v>6360000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5390000000</v>
+        <v>5510000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5340000000</v>
+        <v>5390000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>5160000000</v>
+        <v>4990000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4720000000</v>
+        <v>4430000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4310000000</v>
+        <v>4250000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3730000000</v>
+        <v>3640000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3430000000</v>
+        <v>3500000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3090000000</v>
+        <v>3010000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3020000000</v>
+        <v>2910000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2380000000</v>
+        <v>2400000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2090000000</v>
+        <v>2080000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2060000000</v>
+        <v>2070000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1750000000</v>
+        <v>1730000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1400000000</v>
+        <v>1380000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1130000000</v>
+        <v>1200000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1110000000</v>
+        <v>1120000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>913400000</v>
+        <v>913950000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>461460000</v>
+        <v>452260000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4902480000000</v>
+        <v>4977640000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5412380000000</v>
+        <v>5424190000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4165430000000</v>
+        <v>4194000000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3697400000000</v>
+        <v>3832840000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2689890000000</v>
+        <v>2693020000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2339880000000</v>
+        <v>2337080000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1980920000000</v>
+        <v>1914860000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1672490000000</v>
+        <v>1684180000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1492690000000</v>
+        <v>1469670000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1220340000000</v>
+        <v>1222320000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1112580000000</v>
+        <v>1114060000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1027250000000</v>
+        <v>1029490000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>974540000000</v>
+        <v>973740000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>899960000000</v>
+        <v>911920000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>853590000000</v>
+        <v>856690000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>687040000000</v>
+        <v>685920000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>666710000000</v>
+        <v>672150000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>663890000000</v>
+        <v>660330000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>652310000000</v>
+        <v>653610000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>495890000000</v>
+        <v>497270000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>468500000000</v>
+        <v>467120000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,67 +876,67 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>462800000000</v>
+        <v>455790000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>421930000000</v>
+        <v>420670000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>421740000000</v>
+        <v>414550000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>406320000000</v>
+        <v>409230000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>397570000000</v>
+        <v>403950000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>391800000000</v>
+        <v>396490000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,37 +966,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>384360000000</v>
+        <v>394430000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>379050000000</v>
+        <v>384890000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>376360000000</v>
+        <v>377810000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>370150000000</v>
+        <v>377660000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>365090000000</v>
+        <v>367070000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>340810000000</v>
+        <v>357890000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,37 +1056,37 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>338370000000</v>
+        <v>339640000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>336610000000</v>
+        <v>339380000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>331790000000</v>
+        <v>338030000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,67 +1101,67 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>327170000000</v>
+        <v>331420000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>318950000000</v>
+        <v>308320000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>308330000000</v>
+        <v>306540000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>298640000000</v>
+        <v>296880000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>298470000000</v>
+        <v>296240000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,37 +1176,37 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>291500000000</v>
+        <v>292520000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>274990000000</v>
+        <v>273700000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>273270000000</v>
+        <v>272770000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,112 +1221,112 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>268840000000</v>
+        <v>272380000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>265890000000</v>
+        <v>266270000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>262810000000</v>
+        <v>260300000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>256760000000</v>
+        <v>258350000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>255210000000</v>
+        <v>258160000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>254360000000</v>
+        <v>255270000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>254200000000</v>
+        <v>255050000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>250830000000</v>
+        <v>253950000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,22 +1341,22 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>248510000000</v>
+        <v>250900000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>247170000000</v>
+        <v>249580000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>244180000000</v>
+        <v>245240000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,37 +1386,37 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>241350000000</v>
+        <v>243170000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>221590000000</v>
+        <v>225400000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>221110000000</v>
+        <v>225250000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>219520000000</v>
+        <v>224150000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>215800000000</v>
+        <v>216610000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,52 +1461,52 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>213920000000</v>
+        <v>212460000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>206420000000</v>
+        <v>212120000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>204380000000</v>
+        <v>208600000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>204020000000</v>
+        <v>202270000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>196600000000</v>
+        <v>195610000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,67 +1536,67 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>196060000000</v>
+        <v>192600000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187370000000</v>
+        <v>187150000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>186770000000</v>
+        <v>186170000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>185610000000</v>
+        <v>183290000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182270000000</v>
+        <v>183020000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,52 +1611,52 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177370000000</v>
+        <v>177450000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>174910000000</v>
+        <v>176500000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>174890000000</v>
+        <v>175570000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>174410000000</v>
+        <v>175270000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>174390000000</v>
+        <v>173910000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>172050000000</v>
+        <v>171260000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>167730000000</v>
+        <v>167360000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>162360000000</v>
+        <v>164700000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>157740000000</v>
+        <v>158700000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>157310000000</v>
+        <v>157810000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>155540000000</v>
+        <v>156550000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>145560000000</v>
+        <v>147060000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>141390000000</v>
+        <v>143140000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>141140000000</v>
+        <v>142200000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,37 +1821,37 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>132780000000</v>
+        <v>135010000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>129710000000</v>
+        <v>129820000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>129220000000</v>
+        <v>128960000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,112 +1866,112 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>129180000000</v>
+        <v>128610000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>127770000000</v>
+        <v>128410000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>125630000000</v>
+        <v>124280000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>120870000000</v>
+        <v>123190000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>118880000000</v>
+        <v>119910000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>118270000000</v>
+        <v>119420000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>117840000000</v>
+        <v>118890000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>117480000000</v>
+        <v>118520000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>115010000000</v>
+        <v>114910000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>113220000000</v>
+        <v>113380000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,37 +2016,37 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>111310000000</v>
+        <v>110410000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>108560000000</v>
+        <v>108140000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106760000000</v>
+        <v>107770000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>105750000000</v>
+        <v>106200000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,37 +2076,37 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>105280000000</v>
+        <v>105000000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104570000000</v>
+        <v>104750000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>104520000000</v>
+        <v>103990000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>102100000000</v>
+        <v>99470000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,52 +2136,52 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>94440000000</v>
+        <v>97510000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>92990000000</v>
+        <v>96280000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>92250000000</v>
+        <v>94310000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>91680000000</v>
+        <v>94290000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>90990000000</v>
+        <v>92440000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90650000000</v>
+        <v>91640000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>88930000000</v>
+        <v>88850000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88100000000</v>
+        <v>87440000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86390000000</v>
+        <v>86630000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,37 +2271,37 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>86370000000</v>
+        <v>85900000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81950000000</v>
+        <v>81660000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>81090000000</v>
+        <v>81130000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>78310000000</v>
+        <v>79940000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>77780000000</v>
+        <v>79400000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76330000000</v>
+        <v>76490000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74060000000</v>
+        <v>73700000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,67 +2376,67 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>72310000000</v>
+        <v>72530000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71270000000</v>
+        <v>72500000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70940000000</v>
+        <v>71880000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70700000000</v>
+        <v>71860000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70160000000</v>
+        <v>71530000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,22 +2451,22 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68010000000</v>
+        <v>68600000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66190000000</v>
+        <v>65650000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,37 +2481,37 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65590000000</v>
+        <v>65510000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>65500000000</v>
+        <v>64910000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>63920000000</v>
+        <v>64520000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>62540000000</v>
+        <v>63260000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>62090000000</v>
+        <v>60940000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>58030000000</v>
+        <v>56840000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>57110000000</v>
+        <v>56440000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53390000000</v>
+        <v>53040000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52560000000</v>
+        <v>51480000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,112 +2616,112 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>50240000000</v>
+        <v>50680000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49710000000</v>
+        <v>49740000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>49410000000</v>
+        <v>48310000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46300000000</v>
+        <v>47080000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46110000000</v>
+        <v>46470000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46030000000</v>
+        <v>45910000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>46020000000</v>
+        <v>45660000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>45000000000</v>
+        <v>44260000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,22 +2736,22 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>44170000000</v>
+        <v>43760000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>44050000000</v>
+        <v>42360000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,82 +2766,82 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41360000000</v>
+        <v>40770000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40510000000</v>
+        <v>40080000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>40430000000</v>
+        <v>39650000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35000000000</v>
+        <v>34180000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34500000000</v>
+        <v>31880000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32170000000</v>
+        <v>31480000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,37 +2856,37 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>29840000000</v>
+        <v>30470000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29380000000</v>
+        <v>29360000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29040000000</v>
+        <v>28830000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27270000000</v>
+        <v>28420000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26360000000</v>
+        <v>26180000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24450000000</v>
+        <v>24720000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24150000000</v>
+        <v>24130000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23730000000</v>
+        <v>22710000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22770000000</v>
+        <v>22670000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21700000000</v>
+        <v>21410000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>20580000000</v>
+        <v>19770000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18920000000</v>
+        <v>19590000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18500000000</v>
+        <v>19100000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>18220000000</v>
+        <v>18430000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>18160000000</v>
+        <v>17360000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12680000000</v>
+        <v>12770000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12680000000</v>
+        <v>12770000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10600000000</v>
+        <v>10700000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10600000000</v>
+        <v>10490000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>8910000000</v>
+        <v>9140000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8350000000</v>
+        <v>7790000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>8060000000</v>
+        <v>7730000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7890000000</v>
+        <v>7650000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7190000000</v>
+        <v>7080000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7120000000</v>
+        <v>7080000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7000000000</v>
+        <v>7060000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,37 +3246,37 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6830000000</v>
+        <v>6860000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6730000000</v>
+        <v>6830000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6540000000</v>
+        <v>6620000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6360000000</v>
+        <v>6430000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5510000000</v>
+        <v>5560000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5390000000</v>
+        <v>5240000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4990000000</v>
+        <v>4850000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4430000000</v>
+        <v>4450000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4250000000</v>
+        <v>3980000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3640000000</v>
+        <v>3620000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3500000000</v>
+        <v>3480000000</v>
       </c>
     </row>
     <row r="195">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2910000000</v>
+        <v>2960000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2400000000</v>
+        <v>2320000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2080000000</v>
+        <v>2100000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2070000000</v>
+        <v>2030000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1730000000</v>
+        <v>1710000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1380000000</v>
+        <v>1450000000</v>
       </c>
     </row>
     <row r="202">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1120000000</v>
+        <v>1110000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>913950000</v>
+        <v>912330000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>452260000</v>
+        <v>448430000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4194000000000</v>
+        <v>4190440000000</v>
       </c>
     </row>
     <row r="8">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>973740000000</v>
+        <v>973180000000</v>
       </c>
     </row>
     <row r="18">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>394430000000</v>
+        <v>394460000000</v>
       </c>
     </row>
     <row r="33">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>273700000000</v>
+        <v>273620000000</v>
       </c>
     </row>
     <row r="48">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104750000000</v>
+        <v>104480000000</v>
       </c>
     </row>
     <row r="108">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4977640000000</v>
+        <v>4938670000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5424190000000</v>
+        <v>5515530000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4190440000000</v>
+        <v>4166860000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3832840000000</v>
+        <v>3781240000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2693020000000</v>
+        <v>2655050000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2337080000000</v>
+        <v>2348850000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1914860000000</v>
+        <v>1823050000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1684180000000</v>
+        <v>1668720000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1469670000000</v>
+        <v>1411770000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1222320000000</v>
+        <v>1190360000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1114060000000</v>
+        <v>1115300000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1029490000000</v>
+        <v>992330000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>973180000000</v>
+        <v>968580000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>911920000000</v>
+        <v>894720000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>856690000000</v>
+        <v>862640000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>685920000000</v>
+        <v>686590000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>672150000000</v>
+        <v>682740000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>660330000000</v>
+        <v>668270000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>653610000000</v>
+        <v>655370000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>497270000000</v>
+        <v>497800000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>467120000000</v>
+        <v>470550000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>455790000000</v>
+        <v>450530000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,82 +891,82 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>420670000000</v>
+        <v>420830000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>414550000000</v>
+        <v>409300000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>409230000000</v>
+        <v>407740000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>403950000000</v>
+        <v>400950000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>396490000000</v>
+        <v>393540000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>394460000000</v>
+        <v>387890000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>384890000000</v>
+        <v>386290000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>377810000000</v>
+        <v>376910000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>377660000000</v>
+        <v>375100000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,82 +1026,82 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>367070000000</v>
+        <v>366840000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>357890000000</v>
+        <v>346150000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>339640000000</v>
+        <v>345520000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>339380000000</v>
+        <v>339140000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>338030000000</v>
+        <v>330190000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>331420000000</v>
+        <v>320730000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,22 +1116,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>308320000000</v>
+        <v>304120000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>306540000000</v>
+        <v>302600000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,37 +1146,37 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>296880000000</v>
+        <v>302000000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>296240000000</v>
+        <v>289220000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>292520000000</v>
+        <v>288270000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>273620000000</v>
+        <v>275550000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,52 +1206,52 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>272770000000</v>
+        <v>270340000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>272380000000</v>
+        <v>268870000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>266270000000</v>
+        <v>266790000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>260300000000</v>
+        <v>265460000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,112 +1266,112 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>258350000000</v>
+        <v>257680000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>258160000000</v>
+        <v>254170000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>255270000000</v>
+        <v>252960000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>255050000000</v>
+        <v>252920000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>253950000000</v>
+        <v>250910000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>250900000000</v>
+        <v>250800000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>249580000000</v>
+        <v>246870000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>245240000000</v>
+        <v>244370000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,52 +1386,52 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>243170000000</v>
+        <v>241590000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>225400000000</v>
+        <v>226050000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>225250000000</v>
+        <v>222980000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>224150000000</v>
+        <v>220260000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>216610000000</v>
+        <v>217600000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,52 +1461,52 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>212460000000</v>
+        <v>207900000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>212120000000</v>
+        <v>206870000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>208600000000</v>
+        <v>200930000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>202270000000</v>
+        <v>196900000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,37 +1521,37 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>195610000000</v>
+        <v>193940000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>192600000000</v>
+        <v>188730000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187150000000</v>
+        <v>187040000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,37 +1566,37 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>186170000000</v>
+        <v>185930000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>183290000000</v>
+        <v>185290000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>183020000000</v>
+        <v>182320000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,52 +1611,52 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177450000000</v>
+        <v>178550000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>176500000000</v>
+        <v>175390000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>175570000000</v>
+        <v>174730000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>175270000000</v>
+        <v>174050000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>173910000000</v>
+        <v>170620000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>171260000000</v>
+        <v>169990000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>167360000000</v>
+        <v>165310000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,82 +1716,82 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>164700000000</v>
+        <v>163410000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>158700000000</v>
+        <v>159810000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>157810000000</v>
+        <v>157470000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>156550000000</v>
+        <v>146540000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>147060000000</v>
+        <v>145740000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>143140000000</v>
+        <v>142260000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142200000000</v>
+        <v>139220000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,67 +1821,67 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>135010000000</v>
+        <v>130580000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>129820000000</v>
+        <v>130490000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>128960000000</v>
+        <v>129520000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>128610000000</v>
+        <v>128370000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128410000000</v>
+        <v>127840000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>124280000000</v>
+        <v>126050000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,37 +1911,37 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>123190000000</v>
+        <v>123130000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>119910000000</v>
+        <v>121720000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>119420000000</v>
+        <v>119570000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>118890000000</v>
+        <v>116720000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118520000000</v>
+        <v>115760000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>114910000000</v>
+        <v>115430000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>113380000000</v>
+        <v>114480000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>110410000000</v>
+        <v>111720000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>108140000000</v>
+        <v>108610000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107770000000</v>
+        <v>106770000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,52 +2061,52 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>106200000000</v>
+        <v>105290000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>105000000000</v>
+        <v>103740000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104480000000</v>
+        <v>103150000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103990000000</v>
+        <v>102430000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,37 +2121,37 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99470000000</v>
+        <v>99760000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>97510000000</v>
+        <v>96480000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96280000000</v>
+        <v>93950000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94310000000</v>
+        <v>93660000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94290000000</v>
+        <v>93460000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92440000000</v>
+        <v>91580000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,37 +2211,37 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>91640000000</v>
+        <v>89910000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>88850000000</v>
+        <v>87400000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87440000000</v>
+        <v>86810000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86630000000</v>
+        <v>85840000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85900000000</v>
+        <v>85570000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,52 +2286,52 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81660000000</v>
+        <v>80660000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>81130000000</v>
+        <v>80190000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>79940000000</v>
+        <v>78760000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>79400000000</v>
+        <v>77450000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76490000000</v>
+        <v>76420000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,37 +2361,37 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>73700000000</v>
+        <v>71990000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>72530000000</v>
+        <v>71970000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>72500000000</v>
+        <v>71860000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,37 +2406,37 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>71880000000</v>
+        <v>71830000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>71860000000</v>
+        <v>70760000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>71530000000</v>
+        <v>70270000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,22 +2451,22 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68600000000</v>
+        <v>68970000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>65650000000</v>
+        <v>64880000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,67 +2481,67 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65510000000</v>
+        <v>63390000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64910000000</v>
+        <v>63040000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>64520000000</v>
+        <v>60950000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>63260000000</v>
+        <v>60380000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>60940000000</v>
+        <v>59080000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>56840000000</v>
+        <v>56080000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>56440000000</v>
+        <v>56080000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53040000000</v>
+        <v>53980000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,37 +2601,37 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>51480000000</v>
+        <v>50600000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>50680000000</v>
+        <v>50050000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49740000000</v>
+        <v>49370000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48310000000</v>
+        <v>46920000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47080000000</v>
+        <v>46430000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,52 +2676,52 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46470000000</v>
+        <v>46320000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45910000000</v>
+        <v>45450000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45660000000</v>
+        <v>44070000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44260000000</v>
+        <v>44040000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,22 +2736,22 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>43760000000</v>
+        <v>43300000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>42360000000</v>
+        <v>43200000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,37 +2766,37 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>40770000000</v>
+        <v>41060000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40080000000</v>
+        <v>40300000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39650000000</v>
+        <v>39460000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34180000000</v>
+        <v>34580000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>31880000000</v>
+        <v>32510000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31480000000</v>
+        <v>32000000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30470000000</v>
+        <v>30320000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29360000000</v>
+        <v>29520000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28830000000</v>
+        <v>27530000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28420000000</v>
+        <v>27450000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26180000000</v>
+        <v>25470000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24720000000</v>
+        <v>24470000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24130000000</v>
+        <v>22680000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22710000000</v>
+        <v>22670000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22670000000</v>
+        <v>21890000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>21410000000</v>
+        <v>20570000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19770000000</v>
+        <v>19510000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>19590000000</v>
+        <v>18820000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>19100000000</v>
+        <v>18590000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>18430000000</v>
+        <v>18060000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>17360000000</v>
+        <v>16420000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12770000000</v>
+        <v>12620000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12770000000</v>
+        <v>12620000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10700000000</v>
+        <v>10430000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10490000000</v>
+        <v>10400000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9140000000</v>
+        <v>9150000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7790000000</v>
+        <v>7910000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7730000000</v>
+        <v>7480000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7650000000</v>
+        <v>7150000000</v>
       </c>
     </row>
     <row r="181">
@@ -3207,31 +3207,31 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7080000000</v>
+        <v>7050000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>7060000000</v>
+        <v>6900000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6860000000</v>
+        <v>6710000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6830000000</v>
+        <v>6630000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6620000000</v>
+        <v>6590000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6430000000</v>
+        <v>6210000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5560000000</v>
+        <v>5320000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5240000000</v>
+        <v>5230000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4850000000</v>
+        <v>4680000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4450000000</v>
+        <v>4470000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3980000000</v>
+        <v>3970000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3620000000</v>
+        <v>3400000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,37 +3396,37 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3480000000</v>
+        <v>3400000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3010000000</v>
+        <v>2870000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2960000000</v>
+        <v>2870000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2320000000</v>
+        <v>2240000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2100000000</v>
+        <v>2040000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2030000000</v>
+        <v>1940000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1710000000</v>
+        <v>1670000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1450000000</v>
+        <v>1380000000</v>
       </c>
     </row>
     <row r="202">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1110000000</v>
+        <v>1070000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>912330000</v>
+        <v>867760000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>448430000</v>
+        <v>398600000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4938670000000</v>
+        <v>4807320000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5515530000000</v>
+        <v>5475760000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4166860000000</v>
+        <v>4149360000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3781240000000</v>
+        <v>3779310000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2655050000000</v>
+        <v>2660660000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2348850000000</v>
+        <v>2369910000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1823050000000</v>
+        <v>1882070000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1668720000000</v>
+        <v>1695120000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1411770000000</v>
+        <v>1393560000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1190360000000</v>
+        <v>1202890000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1115300000000</v>
+        <v>1115160000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>992330000000</v>
+        <v>991840000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>968580000000</v>
+        <v>966640000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>894720000000</v>
+        <v>890440000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,37 +771,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>862640000000</v>
+        <v>847320000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>686590000000</v>
+        <v>707010000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>682740000000</v>
+        <v>683120000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>668270000000</v>
+        <v>663460000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>655370000000</v>
+        <v>644820000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>497800000000</v>
+        <v>493700000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>470550000000</v>
+        <v>465260000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>450530000000</v>
+        <v>449300000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,52 +891,52 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>420830000000</v>
+        <v>421620000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>409300000000</v>
+        <v>416640000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>407740000000</v>
+        <v>409840000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>400950000000</v>
+        <v>406330000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>393540000000</v>
+        <v>405290000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>387890000000</v>
+        <v>403810000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>386290000000</v>
+        <v>384320000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>376910000000</v>
+        <v>379990000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>375100000000</v>
+        <v>373630000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>366840000000</v>
+        <v>368300000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>346150000000</v>
+        <v>344500000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>345520000000</v>
+        <v>343080000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>339140000000</v>
+        <v>336540000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>330190000000</v>
+        <v>329830000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,37 +1101,37 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>320730000000</v>
+        <v>317720000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>304120000000</v>
+        <v>313640000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>302600000000</v>
+        <v>302740000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,37 +1146,37 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>302000000000</v>
+        <v>302220000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>289220000000</v>
+        <v>292720000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>288270000000</v>
+        <v>287370000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>275550000000</v>
+        <v>271750000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>270340000000</v>
+        <v>269030000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>268870000000</v>
+        <v>267800000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,52 +1236,52 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>266790000000</v>
+        <v>266780000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>265460000000</v>
+        <v>266730000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>257680000000</v>
+        <v>257250000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>254170000000</v>
+        <v>256470000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,67 +1296,67 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>252960000000</v>
+        <v>256340000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>252920000000</v>
+        <v>254670000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>250910000000</v>
+        <v>253270000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>250800000000</v>
+        <v>251950000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>246870000000</v>
+        <v>251280000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>244370000000</v>
+        <v>243370000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>241590000000</v>
+        <v>243360000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>226050000000</v>
+        <v>229030000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>222980000000</v>
+        <v>221100000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>220260000000</v>
+        <v>219410000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>217600000000</v>
+        <v>218210000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>207900000000</v>
+        <v>207260000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>206870000000</v>
+        <v>206240000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>200930000000</v>
+        <v>195080000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>196900000000</v>
+        <v>193350000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,67 +1521,67 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>193940000000</v>
+        <v>191040000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>188730000000</v>
+        <v>190760000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187040000000</v>
+        <v>187580000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>185930000000</v>
+        <v>185430000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>185290000000</v>
+        <v>183480000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,37 +1596,37 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182320000000</v>
+        <v>182010000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>178550000000</v>
+        <v>175650000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>175390000000</v>
+        <v>174820000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>174730000000</v>
+        <v>174680000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>174050000000</v>
+        <v>173510000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>170620000000</v>
+        <v>171380000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>169990000000</v>
+        <v>167750000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>165310000000</v>
+        <v>165570000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>163410000000</v>
+        <v>163500000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159810000000</v>
+        <v>158950000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,67 +1746,67 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>157470000000</v>
+        <v>158300000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>146540000000</v>
+        <v>148340000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>145740000000</v>
+        <v>145610000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>142260000000</v>
+        <v>141670000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139220000000</v>
+        <v>141570000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,52 +1821,52 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>130580000000</v>
+        <v>136710000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>130490000000</v>
+        <v>128540000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>129520000000</v>
+        <v>128410000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>128370000000</v>
+        <v>128180000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>127840000000</v>
+        <v>128120000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,37 +1896,37 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126050000000</v>
+        <v>125430000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>123130000000</v>
+        <v>122330000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>121720000000</v>
+        <v>121980000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,37 +1941,37 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>119570000000</v>
+        <v>118210000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>116720000000</v>
+        <v>116530000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>115760000000</v>
+        <v>115690000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>115430000000</v>
+        <v>114740000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>114480000000</v>
+        <v>111400000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>111720000000</v>
+        <v>110310000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>108610000000</v>
+        <v>108790000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106770000000</v>
+        <v>108390000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>105290000000</v>
+        <v>105060000000</v>
       </c>
     </row>
     <row r="106">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>103150000000</v>
+        <v>102290000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>102430000000</v>
+        <v>101640000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99760000000</v>
+        <v>100180000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96480000000</v>
+        <v>96430000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,97 +2151,97 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>93950000000</v>
+        <v>95610000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93660000000</v>
+        <v>93990000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93460000000</v>
+        <v>93450000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91580000000</v>
+        <v>90750000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89910000000</v>
+        <v>90590000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87400000000</v>
+        <v>87450000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86810000000</v>
+        <v>86890000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85840000000</v>
+        <v>85440000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85570000000</v>
+        <v>85170000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,37 +2286,37 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>80660000000</v>
+        <v>81330000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>80190000000</v>
+        <v>81230000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>78760000000</v>
+        <v>79910000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>77450000000</v>
+        <v>77270000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,67 +2346,67 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76420000000</v>
+        <v>74010000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>71990000000</v>
+        <v>72730000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>71970000000</v>
+        <v>71690000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71860000000</v>
+        <v>71630000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>71830000000</v>
+        <v>71070000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70760000000</v>
+        <v>70610000000</v>
       </c>
     </row>
     <row r="130">
@@ -2442,61 +2442,61 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68970000000</v>
+        <v>69720000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>64880000000</v>
+        <v>68920000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>63390000000</v>
+        <v>64530000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63040000000</v>
+        <v>64030000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,67 +2511,67 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60950000000</v>
+        <v>62080000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60380000000</v>
+        <v>59660000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>59080000000</v>
+        <v>59430000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>56080000000</v>
+        <v>55910000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>56080000000</v>
+        <v>54920000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,37 +2586,37 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53980000000</v>
+        <v>53170000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50600000000</v>
+        <v>50770000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>50050000000</v>
+        <v>50130000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49370000000</v>
+        <v>49050000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,37 +2646,37 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46920000000</v>
+        <v>47390000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46430000000</v>
+        <v>47270000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46320000000</v>
+        <v>46100000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45450000000</v>
+        <v>45590000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44070000000</v>
+        <v>44660000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44040000000</v>
+        <v>44490000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>43300000000</v>
+        <v>42460000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>43200000000</v>
+        <v>41710000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41060000000</v>
+        <v>41070000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40300000000</v>
+        <v>40340000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,67 +2796,67 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39460000000</v>
+        <v>39240000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34580000000</v>
+        <v>34390000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>32510000000</v>
+        <v>34140000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32000000000</v>
+        <v>32340000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30320000000</v>
+        <v>31630000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29520000000</v>
+        <v>29050000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27530000000</v>
+        <v>27970000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27450000000</v>
+        <v>26950000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25470000000</v>
+        <v>25780000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24470000000</v>
+        <v>24120000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22680000000</v>
+        <v>23380000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22670000000</v>
+        <v>22590000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21890000000</v>
+        <v>21350000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20570000000</v>
+        <v>20550000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,52 +3006,52 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19510000000</v>
+        <v>19380000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18820000000</v>
+        <v>19010000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18590000000</v>
+        <v>17790000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>18060000000</v>
+        <v>17420000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16420000000</v>
+        <v>16280000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12620000000</v>
+        <v>12720000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12620000000</v>
+        <v>12720000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10430000000</v>
+        <v>10500000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10400000000</v>
+        <v>10320000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9150000000</v>
+        <v>9190000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,37 +3156,37 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7910000000</v>
+        <v>8110000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7480000000</v>
+        <v>7600000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7150000000</v>
+        <v>7280000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7080000000</v>
+        <v>7010000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7050000000</v>
+        <v>6970000000</v>
       </c>
     </row>
     <row r="183">
@@ -3246,37 +3246,37 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6710000000</v>
+        <v>6700000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6630000000</v>
+        <v>6660000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6590000000</v>
+        <v>6430000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,37 +3291,37 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6210000000</v>
+        <v>6180000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5320000000</v>
+        <v>5410000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5230000000</v>
+        <v>5250000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4680000000</v>
+        <v>4630000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4470000000</v>
+        <v>4360000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,37 +3366,37 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3970000000</v>
+        <v>4060000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3400000000</v>
+        <v>3450000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3400000000</v>
+        <v>3330000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2870000000</v>
+        <v>2920000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2870000000</v>
+        <v>2830000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2240000000</v>
+        <v>2250000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2040000000</v>
+        <v>1960000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1940000000</v>
+        <v>1910000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1670000000</v>
+        <v>1660000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1380000000</v>
+        <v>1440000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1200000000</v>
+        <v>1250000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1070000000</v>
+        <v>1040000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>867760000</v>
+        <v>847890000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>398600000</v>
+        <v>403970000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4807320000000</v>
+        <v>4860150000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5475760000000</v>
+        <v>5503960000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4149360000000</v>
+        <v>4191630000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3779310000000</v>
+        <v>3808560000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2660660000000</v>
+        <v>2687410000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2369910000000</v>
+        <v>2366020000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1882070000000</v>
+        <v>1847400000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1695120000000</v>
+        <v>1676450000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1393560000000</v>
+        <v>1401340000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1202890000000</v>
+        <v>1202930000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1115160000000</v>
+        <v>1089230000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>991840000000</v>
+        <v>998680000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>966640000000</v>
+        <v>958470000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>890440000000</v>
+        <v>879410000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>847320000000</v>
+        <v>824470000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>707010000000</v>
+        <v>698250000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>683120000000</v>
+        <v>670890000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>663460000000</v>
+        <v>669210000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>644820000000</v>
+        <v>638000000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>493700000000</v>
+        <v>483090000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>465260000000</v>
+        <v>462260000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>449300000000</v>
+        <v>449490000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>421620000000</v>
+        <v>424340000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,22 +906,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>416640000000</v>
+        <v>415160000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>409840000000</v>
+        <v>411110000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,22 +936,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>406330000000</v>
+        <v>405830000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>405290000000</v>
+        <v>403520000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>403810000000</v>
+        <v>403470000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>384320000000</v>
+        <v>380620000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>379990000000</v>
+        <v>372700000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>373630000000</v>
+        <v>370360000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,37 +1026,37 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>368300000000</v>
+        <v>358500000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>344500000000</v>
+        <v>342040000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>343080000000</v>
+        <v>337440000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>336540000000</v>
+        <v>329490000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>329830000000</v>
+        <v>325000000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>317720000000</v>
+        <v>324020000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,37 +1116,37 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>313640000000</v>
+        <v>309360000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>302740000000</v>
+        <v>297410000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>302220000000</v>
+        <v>295390000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>292720000000</v>
+        <v>289730000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>287370000000</v>
+        <v>283830000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>271750000000</v>
+        <v>271460000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>269030000000</v>
+        <v>271090000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>267800000000</v>
+        <v>267300000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>266780000000</v>
+        <v>262160000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>266730000000</v>
+        <v>260980000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,67 +1266,67 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>257250000000</v>
+        <v>255790000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>256470000000</v>
+        <v>254750000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>256340000000</v>
+        <v>254380000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>254670000000</v>
+        <v>253150000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>253270000000</v>
+        <v>250420000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>251950000000</v>
+        <v>250210000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>251280000000</v>
+        <v>249600000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>243370000000</v>
+        <v>242070000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>243360000000</v>
+        <v>240630000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>229030000000</v>
+        <v>227880000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>221100000000</v>
+        <v>218800000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,22 +1431,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>219410000000</v>
+        <v>217190000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>218210000000</v>
+        <v>216820000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>207260000000</v>
+        <v>207200000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,37 +1476,37 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>206240000000</v>
+        <v>205360000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>195080000000</v>
+        <v>193290000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>193350000000</v>
+        <v>190810000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,142 +1521,142 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>191040000000</v>
+        <v>190580000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>190760000000</v>
+        <v>190170000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187580000000</v>
+        <v>188940000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>185430000000</v>
+        <v>184820000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>183480000000</v>
+        <v>181130000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182010000000</v>
+        <v>181070000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175650000000</v>
+        <v>174930000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>174820000000</v>
+        <v>172960000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>174680000000</v>
+        <v>171950000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>173510000000</v>
+        <v>171010000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>171380000000</v>
+        <v>169030000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,67 +1686,67 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>167750000000</v>
+        <v>167200000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>165570000000</v>
+        <v>163850000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>163500000000</v>
+        <v>163420000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>158950000000</v>
+        <v>157990000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>158300000000</v>
+        <v>155750000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>148340000000</v>
+        <v>147050000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>145610000000</v>
+        <v>143650000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>141670000000</v>
+        <v>139940000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>141570000000</v>
+        <v>139200000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,52 +1821,52 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>136710000000</v>
+        <v>132450000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>128540000000</v>
+        <v>127470000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>128410000000</v>
+        <v>126840000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>128180000000</v>
+        <v>125850000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128120000000</v>
+        <v>125480000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,67 +1896,67 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>125430000000</v>
+        <v>123660000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>122330000000</v>
+        <v>122410000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>121980000000</v>
+        <v>120470000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>118210000000</v>
+        <v>119800000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>116530000000</v>
+        <v>117530000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>115690000000</v>
+        <v>116290000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,22 +1986,22 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>114740000000</v>
+        <v>112440000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>111400000000</v>
+        <v>112210000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,37 +2016,37 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>110310000000</v>
+        <v>110940000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>108790000000</v>
+        <v>110380000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>108390000000</v>
+        <v>107110000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>105060000000</v>
+        <v>103400000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,127 +2076,127 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>103740000000</v>
+        <v>102260000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>102290000000</v>
+        <v>100340000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>101640000000</v>
+        <v>99810000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100180000000</v>
+        <v>98330000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96430000000</v>
+        <v>97190000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>95610000000</v>
+        <v>96190000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93990000000</v>
+        <v>93380000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93450000000</v>
+        <v>92900000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>90750000000</v>
+        <v>92390000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90590000000</v>
+        <v>89990000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87450000000</v>
+        <v>87630000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86890000000</v>
+        <v>85350000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85440000000</v>
+        <v>84660000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85170000000</v>
+        <v>84320000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,142 +2286,142 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81330000000</v>
+        <v>81470000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>81230000000</v>
+        <v>79500000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>79910000000</v>
+        <v>78070000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>77270000000</v>
+        <v>76880000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>74010000000</v>
+        <v>73680000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>72730000000</v>
+        <v>72310000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>71690000000</v>
+        <v>71830000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71630000000</v>
+        <v>71180000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>71070000000</v>
+        <v>71100000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70610000000</v>
+        <v>68680000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70270000000</v>
+        <v>68540000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69720000000</v>
+        <v>68010000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68920000000</v>
+        <v>67560000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64530000000</v>
+        <v>64130000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64030000000</v>
+        <v>62570000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62080000000</v>
+        <v>61760000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59660000000</v>
+        <v>61150000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,37 +2541,37 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>59430000000</v>
+        <v>58820000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55910000000</v>
+        <v>55300000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54920000000</v>
+        <v>55200000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53170000000</v>
+        <v>52520000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50770000000</v>
+        <v>49750000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>50130000000</v>
+        <v>49180000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49050000000</v>
+        <v>48090000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47390000000</v>
+        <v>48050000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,37 +2661,37 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47270000000</v>
+        <v>46440000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46100000000</v>
+        <v>45900000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45590000000</v>
+        <v>44940000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44660000000</v>
+        <v>44910000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44490000000</v>
+        <v>44180000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42460000000</v>
+        <v>43680000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>41710000000</v>
+        <v>41700000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41070000000</v>
+        <v>41330000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40340000000</v>
+        <v>40430000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39240000000</v>
+        <v>39160000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34390000000</v>
+        <v>33610000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34140000000</v>
+        <v>33560000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32340000000</v>
+        <v>32520000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>31630000000</v>
+        <v>31990000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29050000000</v>
+        <v>28860000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27970000000</v>
+        <v>27400000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26950000000</v>
+        <v>26980000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25780000000</v>
+        <v>26490000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24120000000</v>
+        <v>24030000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23380000000</v>
+        <v>23360000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22590000000</v>
+        <v>22610000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21350000000</v>
+        <v>20960000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20550000000</v>
+        <v>20300000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19380000000</v>
+        <v>19420000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>19010000000</v>
+        <v>18820000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17790000000</v>
+        <v>17770000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>17420000000</v>
+        <v>16900000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16280000000</v>
+        <v>16090000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12720000000</v>
+        <v>12680000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12720000000</v>
+        <v>12680000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10500000000</v>
+        <v>10700000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10320000000</v>
+        <v>10260000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9190000000</v>
+        <v>9520000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8110000000</v>
+        <v>8270000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7600000000</v>
+        <v>7290000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,48 +3186,48 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7280000000</v>
+        <v>7230000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7010000000</v>
+        <v>6950000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6970000000</v>
+        <v>6920000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L183" t="n">
@@ -3237,16 +3237,16 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6700000000</v>
+        <v>6890000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6660000000</v>
+        <v>6740000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6430000000</v>
+        <v>6280000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6180000000</v>
+        <v>6130000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5410000000</v>
+        <v>5350000000</v>
       </c>
     </row>
     <row r="189">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4630000000</v>
+        <v>4380000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4360000000</v>
+        <v>4270000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4060000000</v>
+        <v>4090000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3450000000</v>
+        <v>3490000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3330000000</v>
+        <v>3390000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2920000000</v>
+        <v>2890000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2830000000</v>
+        <v>2850000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2250000000</v>
+        <v>2240000000</v>
       </c>
     </row>
     <row r="198">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1660000000</v>
+        <v>1770000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1440000000</v>
+        <v>1420000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1250000000</v>
+        <v>1220000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1040000000</v>
+        <v>1050000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>847890000</v>
+        <v>851110000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>403970000</v>
+        <v>406270000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4860150000000</v>
+        <v>4820750000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5503960000000</v>
+        <v>5563730000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4191630000000</v>
+        <v>4118200000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3808560000000</v>
+        <v>3807820000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2687410000000</v>
+        <v>2677490000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2366020000000</v>
+        <v>2381630000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1847400000000</v>
+        <v>1849310000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1676450000000</v>
+        <v>1640410000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1401340000000</v>
+        <v>1398570000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1202930000000</v>
+        <v>1239380000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1089230000000</v>
+        <v>1082420000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>998680000000</v>
+        <v>1005160000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>958470000000</v>
+        <v>963490000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>879410000000</v>
+        <v>885650000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>824470000000</v>
+        <v>827170000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>698250000000</v>
+        <v>697030000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>670890000000</v>
+        <v>673610000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>669210000000</v>
+        <v>671860000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>638000000000</v>
+        <v>623340000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>483090000000</v>
+        <v>481810000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>462260000000</v>
+        <v>459330000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>449490000000</v>
+        <v>456680000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,112 +891,112 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>424340000000</v>
+        <v>428800000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>415160000000</v>
+        <v>425610000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>411110000000</v>
+        <v>420050000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>405830000000</v>
+        <v>417490000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>403520000000</v>
+        <v>409180000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>403470000000</v>
+        <v>405560000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>380620000000</v>
+        <v>379850000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>372700000000</v>
+        <v>375720000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>370360000000</v>
+        <v>370450000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>358500000000</v>
+        <v>354800000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>342040000000</v>
+        <v>344450000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>337440000000</v>
+        <v>334350000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>329490000000</v>
+        <v>327800000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>325000000000</v>
+        <v>324130000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>324020000000</v>
+        <v>324120000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,37 +1116,37 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>309360000000</v>
+        <v>312220000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>297410000000</v>
+        <v>295280000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>295390000000</v>
+        <v>293300000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>289730000000</v>
+        <v>282520000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>283830000000</v>
+        <v>281810000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>271460000000</v>
+        <v>273020000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>271090000000</v>
+        <v>272460000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,142 +1221,142 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>267300000000</v>
+        <v>267310000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>262160000000</v>
+        <v>262990000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>260980000000</v>
+        <v>261750000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>255790000000</v>
+        <v>261430000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>254750000000</v>
+        <v>261080000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>254380000000</v>
+        <v>258200000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>253150000000</v>
+        <v>256910000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>250420000000</v>
+        <v>249350000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>250210000000</v>
+        <v>244580000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>249600000000</v>
+        <v>243290000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>242070000000</v>
+        <v>242680000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>240630000000</v>
+        <v>241260000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,52 +1401,52 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>227880000000</v>
+        <v>220180000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>218800000000</v>
+        <v>217110000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>217190000000</v>
+        <v>216410000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>216820000000</v>
+        <v>213030000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>207200000000</v>
+        <v>212560000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,22 +1476,22 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>205360000000</v>
+        <v>204000000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>193290000000</v>
+        <v>194800000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,52 +1506,52 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190810000000</v>
+        <v>191830000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>190580000000</v>
+        <v>191240000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>190170000000</v>
+        <v>191040000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>188940000000</v>
+        <v>187970000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,37 +1566,37 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184820000000</v>
+        <v>182890000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>181130000000</v>
+        <v>179910000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>181070000000</v>
+        <v>174970000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,97 +1611,97 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>174930000000</v>
+        <v>173480000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172960000000</v>
+        <v>172930000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171950000000</v>
+        <v>171430000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>171010000000</v>
+        <v>170110000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>169030000000</v>
+        <v>167310000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>167200000000</v>
+        <v>166770000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>163850000000</v>
+        <v>166510000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>163420000000</v>
+        <v>164050000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,37 +1731,37 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>157990000000</v>
+        <v>159260000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>155750000000</v>
+        <v>151970000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>147050000000</v>
+        <v>148860000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>143650000000</v>
+        <v>141750000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>139940000000</v>
+        <v>139380000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139200000000</v>
+        <v>138650000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,67 +1821,67 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>132450000000</v>
+        <v>138180000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>127470000000</v>
+        <v>129920000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>126840000000</v>
+        <v>127820000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>125850000000</v>
+        <v>125550000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>125480000000</v>
+        <v>125140000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,22 +1896,22 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>123660000000</v>
+        <v>124980000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>122410000000</v>
+        <v>124240000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>120470000000</v>
+        <v>122590000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,97 +1941,97 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>119800000000</v>
+        <v>120650000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>117530000000</v>
+        <v>120430000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>116290000000</v>
+        <v>116660000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>112440000000</v>
+        <v>114430000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>112210000000</v>
+        <v>111790000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>110940000000</v>
+        <v>110570000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>110380000000</v>
+        <v>108890000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,37 +2046,37 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107110000000</v>
+        <v>108160000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>103400000000</v>
+        <v>104590000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>102260000000</v>
+        <v>102330000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>100340000000</v>
+        <v>101170000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>99810000000</v>
+        <v>99890000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,67 +2121,67 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>98330000000</v>
+        <v>99270000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>97190000000</v>
+        <v>96090000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96190000000</v>
+        <v>94750000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93380000000</v>
+        <v>94140000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92900000000</v>
+        <v>93910000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92390000000</v>
+        <v>91660000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89990000000</v>
+        <v>89370000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87630000000</v>
+        <v>85430000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>85350000000</v>
+        <v>85030000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>84660000000</v>
+        <v>84070000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84320000000</v>
+        <v>82770000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81470000000</v>
+        <v>82010000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79500000000</v>
+        <v>79880000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,37 +2316,37 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>78070000000</v>
+        <v>75650000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76880000000</v>
+        <v>75570000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>73680000000</v>
+        <v>75430000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,22 +2361,22 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>72310000000</v>
+        <v>72220000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>71830000000</v>
+        <v>72210000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,112 +2391,112 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71180000000</v>
+        <v>71190000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>71100000000</v>
+        <v>70810000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>68680000000</v>
+        <v>69590000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68540000000</v>
+        <v>68470000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68010000000</v>
+        <v>67520000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67560000000</v>
+        <v>67390000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64130000000</v>
+        <v>64200000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62570000000</v>
+        <v>63150000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,22 +2511,22 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61760000000</v>
+        <v>61830000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61150000000</v>
+        <v>61690000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>58820000000</v>
+        <v>61670000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55300000000</v>
+        <v>57820000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>55200000000</v>
+        <v>54010000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,37 +2586,37 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52520000000</v>
+        <v>52140000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49750000000</v>
+        <v>49940000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49180000000</v>
+        <v>49100000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48090000000</v>
+        <v>48930000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48050000000</v>
+        <v>48850000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,22 +2661,22 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46440000000</v>
+        <v>46910000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45900000000</v>
+        <v>46270000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,22 +2691,22 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>44940000000</v>
+        <v>45390000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44910000000</v>
+        <v>45010000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44180000000</v>
+        <v>44480000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>43680000000</v>
+        <v>44160000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>41700000000</v>
+        <v>42170000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41330000000</v>
+        <v>40900000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40430000000</v>
+        <v>40120000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39160000000</v>
+        <v>39650000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>33610000000</v>
+        <v>33710000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33560000000</v>
+        <v>32680000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32520000000</v>
+        <v>32410000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,37 +2856,37 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>31990000000</v>
+        <v>31710000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28860000000</v>
+        <v>28770000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27400000000</v>
+        <v>28550000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26980000000</v>
+        <v>27540000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26490000000</v>
+        <v>27370000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24030000000</v>
+        <v>24130000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23360000000</v>
+        <v>23760000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22610000000</v>
+        <v>22460000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20960000000</v>
+        <v>21150000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20300000000</v>
+        <v>20460000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19420000000</v>
+        <v>19500000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18820000000</v>
+        <v>18500000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17770000000</v>
+        <v>17820000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16900000000</v>
+        <v>17210000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16090000000</v>
+        <v>16000000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12680000000</v>
+        <v>12720000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12680000000</v>
+        <v>12720000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10700000000</v>
+        <v>11020000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10260000000</v>
+        <v>10290000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9520000000</v>
+        <v>9230000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8270000000</v>
+        <v>8590000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7290000000</v>
+        <v>7230000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,112 +3186,112 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7230000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6950000000</v>
+        <v>6940000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6920000000</v>
+        <v>6900000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6900000000</v>
+        <v>6840000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6890000000</v>
+        <v>6750000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6740000000</v>
+        <v>6720000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6280000000</v>
+        <v>6260000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6130000000</v>
+        <v>6250000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5350000000</v>
+        <v>5360000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5250000000</v>
+        <v>5210000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4380000000</v>
+        <v>4330000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4270000000</v>
+        <v>4200000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4090000000</v>
+        <v>4150000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3490000000</v>
+        <v>3620000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,37 +3396,37 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3390000000</v>
+        <v>3350000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2890000000</v>
+        <v>2850000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2850000000</v>
+        <v>2730000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2240000000</v>
+        <v>2230000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1960000000</v>
+        <v>1950000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1910000000</v>
+        <v>1900000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1770000000</v>
+        <v>1790000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1420000000</v>
+        <v>1400000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1220000000</v>
+        <v>1090000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1050000000</v>
+        <v>1030000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>851110000</v>
+        <v>844680000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>406270000</v>
+        <v>413940000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4820750000000</v>
+        <v>4869930000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5563730000000</v>
+        <v>5638190000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4118200000000</v>
+        <v>4185030000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3807820000000</v>
+        <v>3842940000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2677490000000</v>
+        <v>2712970000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2381630000000</v>
+        <v>2452060000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1849310000000</v>
+        <v>1854790000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1640410000000</v>
+        <v>1695310000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1398570000000</v>
+        <v>1463660000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1239380000000</v>
+        <v>1213970000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1082420000000</v>
+        <v>1075830000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1005160000000</v>
+        <v>1034840000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>963490000000</v>
+        <v>968080000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>885650000000</v>
+        <v>883530000000</v>
       </c>
     </row>
     <row r="19">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>697030000000</v>
+        <v>719700000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>673610000000</v>
+        <v>674390000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>671860000000</v>
+        <v>673370000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>623340000000</v>
+        <v>617010000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>481810000000</v>
+        <v>483790000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>459330000000</v>
+        <v>464430000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>456680000000</v>
+        <v>453580000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>428800000000</v>
+        <v>442360000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,37 +906,37 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>425610000000</v>
+        <v>434860000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>420050000000</v>
+        <v>430280000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>417490000000</v>
+        <v>428570000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>409180000000</v>
+        <v>408370000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>405560000000</v>
+        <v>408090000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>379850000000</v>
+        <v>388620000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>375720000000</v>
+        <v>375860000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,37 +1011,37 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>370450000000</v>
+        <v>368510000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>354800000000</v>
+        <v>357660000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>344450000000</v>
+        <v>356010000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>334350000000</v>
+        <v>336580000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>327800000000</v>
+        <v>333820000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,37 +1086,37 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>324130000000</v>
+        <v>329850000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>324120000000</v>
+        <v>328400000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>312220000000</v>
+        <v>321190000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>295280000000</v>
+        <v>298890000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,127 +1146,127 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>293300000000</v>
+        <v>292180000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>282520000000</v>
+        <v>282200000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>281810000000</v>
+        <v>279230000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>273020000000</v>
+        <v>276500000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>272460000000</v>
+        <v>274700000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>267310000000</v>
+        <v>269990000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>262990000000</v>
+        <v>268310000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>261750000000</v>
+        <v>263330000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261430000000</v>
+        <v>263320000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>261080000000</v>
+        <v>262800000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,22 +1296,22 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>258200000000</v>
+        <v>258110000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>256910000000</v>
+        <v>251840000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>249350000000</v>
+        <v>248900000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,112 +1341,112 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>244580000000</v>
+        <v>243330000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>243290000000</v>
+        <v>243280000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>242680000000</v>
+        <v>242110000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>241260000000</v>
+        <v>240730000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>220180000000</v>
+        <v>221030000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>217110000000</v>
+        <v>217900000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>216410000000</v>
+        <v>215550000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>213030000000</v>
+        <v>214920000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>212560000000</v>
+        <v>209760000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,52 +1476,52 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>204000000000</v>
+        <v>204470000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194800000000</v>
+        <v>194780000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>191830000000</v>
+        <v>194160000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>191240000000</v>
+        <v>193150000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>191040000000</v>
+        <v>190790000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,37 +1551,37 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187970000000</v>
+        <v>187720000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>182890000000</v>
+        <v>185230000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>179910000000</v>
+        <v>179470000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>174970000000</v>
+        <v>176450000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>173480000000</v>
+        <v>175530000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172930000000</v>
+        <v>172160000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,217 +1641,217 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171430000000</v>
+        <v>171830000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>170110000000</v>
+        <v>168710000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167310000000</v>
+        <v>167230000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166770000000</v>
+        <v>166510000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>166510000000</v>
+        <v>164090000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>164050000000</v>
+        <v>160270000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159260000000</v>
+        <v>152980000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>151970000000</v>
+        <v>150480000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>148860000000</v>
+        <v>149730000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>141750000000</v>
+        <v>141430000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>139380000000</v>
+        <v>139120000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>138650000000</v>
+        <v>138780000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>138180000000</v>
+        <v>138470000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>129920000000</v>
+        <v>127660000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>127820000000</v>
+        <v>124950000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>125550000000</v>
+        <v>124910000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>125140000000</v>
+        <v>124870000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,37 +1896,37 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>124980000000</v>
+        <v>124300000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124240000000</v>
+        <v>122210000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>122590000000</v>
+        <v>121720000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120650000000</v>
+        <v>120320000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120430000000</v>
+        <v>119480000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>116660000000</v>
+        <v>116640000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>114430000000</v>
+        <v>113870000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>111790000000</v>
+        <v>112460000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,37 +2016,37 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>110570000000</v>
+        <v>110490000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>108890000000</v>
+        <v>107970000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>108160000000</v>
+        <v>107300000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>104590000000</v>
+        <v>102110000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,52 +2076,52 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>102330000000</v>
+        <v>101440000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>101170000000</v>
+        <v>101210000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>99890000000</v>
+        <v>99540000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99270000000</v>
+        <v>97360000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96090000000</v>
+        <v>97260000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,52 +2151,52 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>94750000000</v>
+        <v>97090000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94140000000</v>
+        <v>92510000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93910000000</v>
+        <v>92380000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91660000000</v>
+        <v>89760000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89370000000</v>
+        <v>89600000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>85430000000</v>
+        <v>86010000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>85030000000</v>
+        <v>84290000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>84070000000</v>
+        <v>83800000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>82770000000</v>
+        <v>83490000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82010000000</v>
+        <v>81150000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,112 +2301,112 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79880000000</v>
+        <v>79140000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>75650000000</v>
+        <v>75860000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>75570000000</v>
+        <v>75690000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75430000000</v>
+        <v>75110000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>72220000000</v>
+        <v>74280000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>72210000000</v>
+        <v>72340000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71190000000</v>
+        <v>71480000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70810000000</v>
+        <v>70870000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>69590000000</v>
+        <v>68680000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>68470000000</v>
+        <v>67910000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67520000000</v>
+        <v>67330000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,82 +2466,82 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67390000000</v>
+        <v>67170000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64200000000</v>
+        <v>66010000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63150000000</v>
+        <v>64870000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61830000000</v>
+        <v>61850000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61690000000</v>
+        <v>61480000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>61670000000</v>
+        <v>60780000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>57820000000</v>
+        <v>58060000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54010000000</v>
+        <v>53970000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,22 +2586,22 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52140000000</v>
+        <v>50250000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49940000000</v>
+        <v>49430000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,37 +2616,37 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49100000000</v>
+        <v>49080000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48930000000</v>
+        <v>48280000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48850000000</v>
+        <v>48250000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46910000000</v>
+        <v>47000000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46270000000</v>
+        <v>45240000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45390000000</v>
+        <v>45170000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45010000000</v>
+        <v>44860000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44480000000</v>
+        <v>44660000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>44160000000</v>
+        <v>44310000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>42170000000</v>
+        <v>44240000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>40900000000</v>
+        <v>41230000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40120000000</v>
+        <v>40950000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39650000000</v>
+        <v>38960000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>33710000000</v>
+        <v>34640000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>32680000000</v>
+        <v>33320000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32410000000</v>
+        <v>32060000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,52 +2856,52 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>31710000000</v>
+        <v>31000000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28770000000</v>
+        <v>28800000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28550000000</v>
+        <v>28700000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27540000000</v>
+        <v>28450000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,37 +2916,37 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27370000000</v>
+        <v>27100000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24130000000</v>
+        <v>23880000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23760000000</v>
+        <v>23590000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22460000000</v>
+        <v>22630000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21150000000</v>
+        <v>20730000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20460000000</v>
+        <v>20370000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19500000000</v>
+        <v>19140000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18500000000</v>
+        <v>18770000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17820000000</v>
+        <v>17730000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>17210000000</v>
+        <v>16540000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16000000000</v>
+        <v>16430000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12720000000</v>
+        <v>12560000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12720000000</v>
+        <v>12560000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11020000000</v>
+        <v>10910000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10290000000</v>
+        <v>10250000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9230000000</v>
+        <v>9550000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8590000000</v>
+        <v>8720000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7230000000</v>
+        <v>7590000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,37 +3186,37 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7130000000</v>
+        <v>7160000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6940000000</v>
+        <v>7060000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6900000000</v>
+        <v>6770000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6840000000</v>
+        <v>6770000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6750000000</v>
+        <v>6760000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,37 +3261,37 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6720000000</v>
+        <v>6670000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6260000000</v>
+        <v>6310000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6250000000</v>
+        <v>6190000000</v>
       </c>
     </row>
     <row r="188">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5210000000</v>
+        <v>5090000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4330000000</v>
+        <v>4340000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4200000000</v>
+        <v>4220000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4150000000</v>
+        <v>4110000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3620000000</v>
+        <v>3600000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3350000000</v>
+        <v>3330000000</v>
       </c>
     </row>
     <row r="195">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2730000000</v>
+        <v>2770000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2230000000</v>
+        <v>2220000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1950000000</v>
+        <v>1980000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1900000000</v>
+        <v>1850000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1790000000</v>
+        <v>1770000000</v>
       </c>
     </row>
     <row r="201">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1090000000</v>
+        <v>1120000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1030000000</v>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>844680000</v>
+        <v>838760000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>413940000</v>
+        <v>446140000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4185030000000</v>
+        <v>4183590000000</v>
       </c>
     </row>
     <row r="8">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>968080000000</v>
+        <v>967990000000</v>
       </c>
     </row>
     <row r="18">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>446140000</v>
+        <v>446130000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4869930000000</v>
+        <v>4858260000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5638190000000</v>
+        <v>5757490000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4183590000000</v>
+        <v>4226370000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3842940000000</v>
+        <v>3899750000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2712970000000</v>
+        <v>2711680000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2452060000000</v>
+        <v>2519590000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1854790000000</v>
+        <v>1889990000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1695310000000</v>
+        <v>1730490000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1463660000000</v>
+        <v>1495810000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1213970000000</v>
+        <v>1201630000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1075830000000</v>
+        <v>1076080000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1034840000000</v>
+        <v>1031320000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>967990000000</v>
+        <v>971090000000</v>
       </c>
     </row>
     <row r="18">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>827170000000</v>
+        <v>833600000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,37 +786,37 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>719700000000</v>
+        <v>716830000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>674390000000</v>
+        <v>690270000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>673370000000</v>
+        <v>674350000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>617010000000</v>
+        <v>609540000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>483790000000</v>
+        <v>494590000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>464430000000</v>
+        <v>469630000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>453580000000</v>
+        <v>455140000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>442360000000</v>
+        <v>444800000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>434860000000</v>
+        <v>432740000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>430280000000</v>
+        <v>430820000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>428570000000</v>
+        <v>430350000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>408370000000</v>
+        <v>409370000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>408090000000</v>
+        <v>407940000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>388620000000</v>
+        <v>389870000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>375860000000</v>
+        <v>377610000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>368510000000</v>
+        <v>372210000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>357660000000</v>
+        <v>351150000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,37 +1041,37 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>356010000000</v>
+        <v>344270000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>336580000000</v>
+        <v>339810000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>333820000000</v>
+        <v>338970000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>329850000000</v>
+        <v>332730000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>328400000000</v>
+        <v>323500000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>321190000000</v>
+        <v>317850000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>298890000000</v>
+        <v>298710000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,37 +1146,37 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>292180000000</v>
+        <v>295400000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>282200000000</v>
+        <v>281070000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>279230000000</v>
+        <v>280500000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,67 +1191,67 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>276500000000</v>
+        <v>279200000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>274700000000</v>
+        <v>275640000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>269990000000</v>
+        <v>275520000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>268310000000</v>
+        <v>269940000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>263330000000</v>
+        <v>269320000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>263320000000</v>
+        <v>263670000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>262800000000</v>
+        <v>260150000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,52 +1296,52 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>258110000000</v>
+        <v>257980000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>251840000000</v>
+        <v>250230000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>248900000000</v>
+        <v>249520000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>243330000000</v>
+        <v>248430000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,22 +1356,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>243280000000</v>
+        <v>246270000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>242110000000</v>
+        <v>242760000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>240730000000</v>
+        <v>239770000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,52 +1401,52 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>221030000000</v>
+        <v>222370000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>217900000000</v>
+        <v>218030000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>215550000000</v>
+        <v>217860000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>214920000000</v>
+        <v>215630000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,82 +1461,82 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>209760000000</v>
+        <v>208760000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>204470000000</v>
+        <v>206000000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>194780000000</v>
+        <v>205310000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>194160000000</v>
+        <v>190500000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>193150000000</v>
+        <v>189870000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>190790000000</v>
+        <v>189120000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187720000000</v>
+        <v>187650000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>185230000000</v>
+        <v>183940000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>179470000000</v>
+        <v>179330000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>176450000000</v>
+        <v>178900000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175530000000</v>
+        <v>176600000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,37 +1626,37 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172160000000</v>
+        <v>173270000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171830000000</v>
+        <v>173210000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>168710000000</v>
+        <v>171500000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167230000000</v>
+        <v>169410000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166510000000</v>
+        <v>166100000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,37 +1701,37 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>164090000000</v>
+        <v>164910000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>160270000000</v>
+        <v>159230000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>152980000000</v>
+        <v>159120000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,37 +1746,37 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>150480000000</v>
+        <v>155510000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>149730000000</v>
+        <v>152320000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>141430000000</v>
+        <v>143600000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>139120000000</v>
+        <v>141920000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,142 +1806,142 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>138780000000</v>
+        <v>138650000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>138470000000</v>
+        <v>137280000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>127660000000</v>
+        <v>128010000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>124950000000</v>
+        <v>127500000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>124910000000</v>
+        <v>125600000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>124870000000</v>
+        <v>124140000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>124300000000</v>
+        <v>123550000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>122210000000</v>
+        <v>120130000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>121720000000</v>
+        <v>119600000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120320000000</v>
+        <v>119360000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119480000000</v>
+        <v>118970000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>116640000000</v>
+        <v>116930000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>113870000000</v>
+        <v>115240000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>112460000000</v>
+        <v>113340000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,37 +2016,37 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>110490000000</v>
+        <v>112530000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>107970000000</v>
+        <v>110880000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107300000000</v>
+        <v>107650000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,67 +2061,67 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>102110000000</v>
+        <v>103130000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>101440000000</v>
+        <v>100980000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>101210000000</v>
+        <v>100710000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>99540000000</v>
+        <v>99450000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>97360000000</v>
+        <v>99250000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>97260000000</v>
+        <v>98240000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,112 +2151,112 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>97090000000</v>
+        <v>97640000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>92510000000</v>
+        <v>94360000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92380000000</v>
+        <v>94330000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>89760000000</v>
+        <v>94160000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>89600000000</v>
+        <v>92940000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>86010000000</v>
+        <v>89230000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>84290000000</v>
+        <v>85560000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>83800000000</v>
+        <v>85420000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>83490000000</v>
+        <v>84160000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,127 +2286,127 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81150000000</v>
+        <v>81330000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79140000000</v>
+        <v>81130000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>75860000000</v>
+        <v>79240000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>75690000000</v>
+        <v>76080000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>75110000000</v>
+        <v>74790000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74280000000</v>
+        <v>74620000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>72340000000</v>
+        <v>73560000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>71480000000</v>
+        <v>73330000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>70870000000</v>
+        <v>71690000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,127 +2421,127 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>68680000000</v>
+        <v>70400000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>67910000000</v>
+        <v>69500000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67330000000</v>
+        <v>68710000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67170000000</v>
+        <v>68120000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>66010000000</v>
+        <v>67640000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64870000000</v>
+        <v>63230000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61850000000</v>
+        <v>63180000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61480000000</v>
+        <v>62860000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>60780000000</v>
+        <v>61060000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>58060000000</v>
+        <v>58290000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>53970000000</v>
+        <v>54910000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,52 +2586,52 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50250000000</v>
+        <v>50370000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49430000000</v>
+        <v>50280000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49080000000</v>
+        <v>49660000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48280000000</v>
+        <v>48630000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,67 +2646,67 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48250000000</v>
+        <v>48450000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47000000000</v>
+        <v>48200000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45240000000</v>
+        <v>46550000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45170000000</v>
+        <v>46310000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44860000000</v>
+        <v>46210000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,82 +2721,82 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44660000000</v>
+        <v>45800000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>44310000000</v>
+        <v>45540000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>44240000000</v>
+        <v>44350000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41230000000</v>
+        <v>43700000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40950000000</v>
+        <v>40160000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38960000000</v>
+        <v>39040000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34640000000</v>
+        <v>34370000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33320000000</v>
+        <v>33800000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32060000000</v>
+        <v>32900000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>31000000000</v>
+        <v>31700000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,37 +2871,37 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>28800000000</v>
+        <v>29510000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28700000000</v>
+        <v>28940000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28450000000</v>
+        <v>28370000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27100000000</v>
+        <v>27320000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23880000000</v>
+        <v>25220000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23590000000</v>
+        <v>24540000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22630000000</v>
+        <v>22780000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20730000000</v>
+        <v>21250000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,67 +2991,67 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20370000000</v>
+        <v>20560000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19140000000</v>
+        <v>18930000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18770000000</v>
+        <v>18870000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17730000000</v>
+        <v>17430000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16540000000</v>
+        <v>17410000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16430000000</v>
+        <v>15930000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12560000000</v>
+        <v>12930000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12560000000</v>
+        <v>12930000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10910000000</v>
+        <v>11360000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10250000000</v>
+        <v>10430000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9550000000</v>
+        <v>10010000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8720000000</v>
+        <v>8850000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7590000000</v>
+        <v>7390000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7160000000</v>
+        <v>7200000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7060000000</v>
+        <v>7080000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6770000000</v>
+        <v>6960000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,37 +3231,37 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6770000000</v>
+        <v>6920000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6760000000</v>
+        <v>6690000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6670000000</v>
+        <v>6680000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6310000000</v>
+        <v>6440000000</v>
       </c>
     </row>
     <row r="187">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5360000000</v>
+        <v>5540000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,37 +3321,37 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5090000000</v>
+        <v>5060000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4340000000</v>
+        <v>4320000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4220000000</v>
+        <v>4310000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4110000000</v>
+        <v>4140000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3600000000</v>
+        <v>3610000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3330000000</v>
+        <v>3300000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2850000000</v>
+        <v>2890000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2770000000</v>
+        <v>2880000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2220000000</v>
+        <v>2370000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1980000000</v>
+        <v>2020000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1850000000</v>
+        <v>1800000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1770000000</v>
+        <v>1780000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1400000000</v>
+        <v>1410000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1120000000</v>
+        <v>1090000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1000000000</v>
+        <v>1050000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>838760000</v>
+        <v>832850000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>446130000</v>
+        <v>449200000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4858260000000</v>
+        <v>4869060000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5757490000000</v>
+        <v>5765680000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4226370000000</v>
+        <v>4232070000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3899750000000</v>
+        <v>3930340000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2711680000000</v>
+        <v>2764420000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2519590000000</v>
+        <v>2501440000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1889990000000</v>
+        <v>1882300000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1730490000000</v>
+        <v>1793980000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1495810000000</v>
+        <v>1503510000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1201630000000</v>
+        <v>1180850000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1076080000000</v>
+        <v>1089610000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1031320000000</v>
+        <v>1060160000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>971090000000</v>
+        <v>973150000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>883530000000</v>
+        <v>880600000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>833600000000</v>
+        <v>850500000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>716830000000</v>
+        <v>706900000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>690270000000</v>
+        <v>692000000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>674350000000</v>
+        <v>676330000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>609540000000</v>
+        <v>613990000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>494590000000</v>
+        <v>496330000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,82 +861,82 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>469630000000</v>
+        <v>471270000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>455140000000</v>
+        <v>464990000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>444800000000</v>
+        <v>461560000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>432740000000</v>
+        <v>437750000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>430820000000</v>
+        <v>420820000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>430350000000</v>
+        <v>417840000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>409370000000</v>
+        <v>414760000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>407940000000</v>
+        <v>410130000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>389870000000</v>
+        <v>396900000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>377610000000</v>
+        <v>378240000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>372210000000</v>
+        <v>370750000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>351150000000</v>
+        <v>364960000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,52 +1041,52 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>344270000000</v>
+        <v>350190000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>339810000000</v>
+        <v>344710000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>338970000000</v>
+        <v>343490000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>332730000000</v>
+        <v>337780000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>323500000000</v>
+        <v>323130000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>317850000000</v>
+        <v>321010000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>298710000000</v>
+        <v>300010000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,37 +1146,37 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>295400000000</v>
+        <v>296760000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>281070000000</v>
+        <v>286030000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>280500000000</v>
+        <v>286020000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,52 +1191,52 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>279200000000</v>
+        <v>285530000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>275640000000</v>
+        <v>278660000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>275520000000</v>
+        <v>274110000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>269940000000</v>
+        <v>271810000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,142 +1251,142 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>269320000000</v>
+        <v>271440000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>263670000000</v>
+        <v>261230000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>260150000000</v>
+        <v>257720000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>257980000000</v>
+        <v>257690000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>250230000000</v>
+        <v>247030000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>249520000000</v>
+        <v>246490000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>248430000000</v>
+        <v>245990000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>246270000000</v>
+        <v>243120000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>242760000000</v>
+        <v>242910000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>239770000000</v>
+        <v>242770000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>222370000000</v>
+        <v>225860000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>218030000000</v>
+        <v>219750000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>217860000000</v>
+        <v>217660000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>215630000000</v>
+        <v>215580000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>208760000000</v>
+        <v>211580000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>206000000000</v>
+        <v>208480000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>205310000000</v>
+        <v>205670000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190500000000</v>
+        <v>191040000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,37 +1521,37 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>189870000000</v>
+        <v>190120000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>189120000000</v>
+        <v>186790000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187650000000</v>
+        <v>185170000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,37 +1566,37 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>183940000000</v>
+        <v>184100000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>179330000000</v>
+        <v>179630000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>178900000000</v>
+        <v>178840000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>176600000000</v>
+        <v>177990000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,67 +1626,67 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>173270000000</v>
+        <v>175380000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>173210000000</v>
+        <v>171580000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>171500000000</v>
+        <v>169850000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>169410000000</v>
+        <v>167400000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166100000000</v>
+        <v>167400000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,157 +1701,157 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>164910000000</v>
+        <v>164490000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>159230000000</v>
+        <v>162460000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159120000000</v>
+        <v>151570000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>155510000000</v>
+        <v>150030000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>152320000000</v>
+        <v>148200000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>143600000000</v>
+        <v>145550000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>141920000000</v>
+        <v>142990000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>138650000000</v>
+        <v>141100000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137280000000</v>
+        <v>140770000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>128010000000</v>
+        <v>128940000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>127500000000</v>
+        <v>126410000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>125600000000</v>
+        <v>125570000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>124140000000</v>
+        <v>124730000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>123550000000</v>
+        <v>123220000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>120130000000</v>
+        <v>121730000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,37 +1926,37 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>119600000000</v>
+        <v>118520000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>119360000000</v>
+        <v>118440000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>118970000000</v>
+        <v>118350000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>116930000000</v>
+        <v>117730000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>115240000000</v>
+        <v>116780000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,37 +2001,37 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>113340000000</v>
+        <v>114460000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>112530000000</v>
+        <v>111590000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>110880000000</v>
+        <v>111400000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>107650000000</v>
+        <v>109570000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>103130000000</v>
+        <v>103960000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>100980000000</v>
+        <v>103340000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>100710000000</v>
+        <v>103050000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>99450000000</v>
+        <v>100500000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,82 +2121,82 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99250000000</v>
+        <v>99910000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>98240000000</v>
+        <v>97460000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>97640000000</v>
+        <v>96040000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94360000000</v>
+        <v>94190000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94330000000</v>
+        <v>93570000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>94160000000</v>
+        <v>93290000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92940000000</v>
+        <v>92680000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89230000000</v>
+        <v>89260000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>85560000000</v>
+        <v>86770000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85420000000</v>
+        <v>86170000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84160000000</v>
+        <v>84390000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,52 +2286,52 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81330000000</v>
+        <v>81960000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>81130000000</v>
+        <v>79220000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>79240000000</v>
+        <v>77450000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>76080000000</v>
+        <v>77230000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,52 +2346,52 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>74790000000</v>
+        <v>76050000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>74620000000</v>
+        <v>75650000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73560000000</v>
+        <v>74840000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>73330000000</v>
+        <v>74210000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>71690000000</v>
+        <v>72500000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>70400000000</v>
+        <v>71960000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69500000000</v>
+        <v>70110000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,37 +2451,37 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68710000000</v>
+        <v>69550000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68120000000</v>
+        <v>68630000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>67640000000</v>
+        <v>68470000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,37 +2496,37 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63230000000</v>
+        <v>67930000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>63180000000</v>
+        <v>67620000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>62860000000</v>
+        <v>63220000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>61060000000</v>
+        <v>61560000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>58290000000</v>
+        <v>58310000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,202 +2571,202 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54910000000</v>
+        <v>54730000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50370000000</v>
+        <v>53870000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50280000000</v>
+        <v>51390000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49660000000</v>
+        <v>50590000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48630000000</v>
+        <v>49850000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48450000000</v>
+        <v>49010000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>48200000000</v>
+        <v>48970000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46550000000</v>
+        <v>48340000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46310000000</v>
+        <v>46720000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>46210000000</v>
+        <v>45990000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>45800000000</v>
+        <v>44960000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>45540000000</v>
+        <v>44920000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>44350000000</v>
+        <v>43060000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>43700000000</v>
+        <v>41300000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40160000000</v>
+        <v>40340000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39040000000</v>
+        <v>39100000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34370000000</v>
+        <v>35740000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33800000000</v>
+        <v>34610000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32900000000</v>
+        <v>33830000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>31700000000</v>
+        <v>31870000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29510000000</v>
+        <v>29480000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28940000000</v>
+        <v>28660000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28370000000</v>
+        <v>28550000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27320000000</v>
+        <v>27490000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25220000000</v>
+        <v>25270000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24540000000</v>
+        <v>24180000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22780000000</v>
+        <v>22580000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21250000000</v>
+        <v>21460000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20560000000</v>
+        <v>20360000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18930000000</v>
+        <v>19320000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18870000000</v>
+        <v>19020000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17430000000</v>
+        <v>17570000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>17410000000</v>
+        <v>17540000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15930000000</v>
+        <v>16250000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12930000000</v>
+        <v>12520000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12930000000</v>
+        <v>12520000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11360000000</v>
+        <v>11340000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10430000000</v>
+        <v>10740000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10010000000</v>
+        <v>9980000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8850000000</v>
+        <v>8980000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,48 +3171,48 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7390000000</v>
+        <v>7580000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7200000000</v>
+        <v>7290000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7080000000</v>
+        <v>7170000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -3222,31 +3222,31 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6920000000</v>
+        <v>6910000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6690000000</v>
+        <v>6880000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6680000000</v>
+        <v>6820000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6440000000</v>
+        <v>6350000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6190000000</v>
+        <v>6260000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5540000000</v>
+        <v>5220000000</v>
       </c>
     </row>
     <row r="189">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4320000000</v>
+        <v>4310000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4310000000</v>
+        <v>4240000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4140000000</v>
+        <v>4060000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3610000000</v>
+        <v>3580000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3300000000</v>
+        <v>3450000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2890000000</v>
+        <v>3150000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2880000000</v>
+        <v>2780000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2370000000</v>
+        <v>2320000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,33 +3456,33 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2020000000</v>
+        <v>2130000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Quantum Computing Inc</t>
+          <t>C3.ai Inc</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1800000000</v>
+        <v>1810000000</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>QUBT</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>C3.ai Inc</t>
+          <t>Quantum Computing Inc</t>
         </is>
       </c>
       <c r="L200" t="n">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1410000000</v>
+        <v>1480000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1090000000</v>
+        <v>1120000000</v>
       </c>
     </row>
     <row r="203">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>832850000</v>
+        <v>885480000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>449200000</v>
+        <v>436940000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4869060000000</v>
+        <v>4913420000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5765680000000</v>
+        <v>5723030000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4232070000000</v>
+        <v>4269210000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3930340000000</v>
+        <v>3933760000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2764420000000</v>
+        <v>2803580000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2501440000000</v>
+        <v>2449060000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1882300000000</v>
+        <v>1837540000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1793980000000</v>
+        <v>1797320000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1503510000000</v>
+        <v>1492180000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1180850000000</v>
+        <v>1228780000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1089610000000</v>
+        <v>1119010000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1060160000000</v>
+        <v>1054350000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>973150000000</v>
+        <v>974450000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>880600000000</v>
+        <v>876090000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>850500000000</v>
+        <v>858110000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>706900000000</v>
+        <v>695670000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>692000000000</v>
+        <v>694730000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>676330000000</v>
+        <v>674560000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>613990000000</v>
+        <v>622840000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>496330000000</v>
+        <v>499380000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,37 +861,37 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>471270000000</v>
+        <v>479520000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>464990000000</v>
+        <v>466480000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>461560000000</v>
+        <v>462820000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,52 +906,52 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>437750000000</v>
+        <v>434090000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>420820000000</v>
+        <v>417670000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>417840000000</v>
+        <v>413190000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>414760000000</v>
+        <v>412360000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,37 +966,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>410130000000</v>
+        <v>405330000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>396900000000</v>
+        <v>374250000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>378240000000</v>
+        <v>374100000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>370750000000</v>
+        <v>369240000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>364960000000</v>
+        <v>368110000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>350190000000</v>
+        <v>352290000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,187 +1056,187 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>344710000000</v>
+        <v>343340000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>343490000000</v>
+        <v>337480000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>337780000000</v>
+        <v>331760000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>323130000000</v>
+        <v>315020000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>321010000000</v>
+        <v>314390000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>300010000000</v>
+        <v>300330000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>296760000000</v>
+        <v>297950000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>286030000000</v>
+        <v>290230000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>286020000000</v>
+        <v>285110000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>285530000000</v>
+        <v>276470000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>278660000000</v>
+        <v>271790000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>274110000000</v>
+        <v>266190000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>271810000000</v>
+        <v>265560000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,37 +1251,37 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>271440000000</v>
+        <v>263910000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261230000000</v>
+        <v>262280000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>257720000000</v>
+        <v>258330000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,172 +1296,172 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>257690000000</v>
+        <v>256860000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>247030000000</v>
+        <v>248330000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>246490000000</v>
+        <v>247800000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>245990000000</v>
+        <v>244790000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>243120000000</v>
+        <v>242950000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>242910000000</v>
+        <v>242710000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>242770000000</v>
+        <v>242530000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>225860000000</v>
+        <v>223320000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>219750000000</v>
+        <v>223110000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>217660000000</v>
+        <v>216600000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>215580000000</v>
+        <v>213620000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>211580000000</v>
+        <v>213570000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>208480000000</v>
+        <v>207750000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>205670000000</v>
+        <v>205460000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>191040000000</v>
+        <v>190160000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>190120000000</v>
+        <v>189140000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>186790000000</v>
+        <v>187340000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,22 +1551,22 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>185170000000</v>
+        <v>184810000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184100000000</v>
+        <v>182090000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,37 +1581,37 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>179630000000</v>
+        <v>180870000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>178840000000</v>
+        <v>179830000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177990000000</v>
+        <v>177110000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,37 +1626,37 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>175380000000</v>
+        <v>173790000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171580000000</v>
+        <v>170840000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169850000000</v>
+        <v>168880000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167400000000</v>
+        <v>167680000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>167400000000</v>
+        <v>165290000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>164490000000</v>
+        <v>163380000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>162460000000</v>
+        <v>160750000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>151570000000</v>
+        <v>153600000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,52 +1746,52 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>150030000000</v>
+        <v>148840000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>148200000000</v>
+        <v>146440000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>145550000000</v>
+        <v>146170000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>142990000000</v>
+        <v>140620000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>141100000000</v>
+        <v>139810000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140770000000</v>
+        <v>138870000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,37 +1836,37 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>128940000000</v>
+        <v>129130000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>126410000000</v>
+        <v>128010000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>125570000000</v>
+        <v>124430000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,22 +1881,22 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>124730000000</v>
+        <v>123390000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>123220000000</v>
+        <v>122120000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,97 +1911,97 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>121730000000</v>
+        <v>121950000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>118520000000</v>
+        <v>120330000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>118440000000</v>
+        <v>117430000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>118350000000</v>
+        <v>117120000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>117730000000</v>
+        <v>116500000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>116780000000</v>
+        <v>115850000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>114460000000</v>
+        <v>115220000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>111590000000</v>
+        <v>111740000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>111400000000</v>
+        <v>109380000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,37 +2046,37 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>109570000000</v>
+        <v>106680000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>103960000000</v>
+        <v>105600000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>103340000000</v>
+        <v>104610000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,22 +2091,22 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>103050000000</v>
+        <v>101850000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>100500000000</v>
+        <v>101810000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,37 +2121,37 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99910000000</v>
+        <v>97430000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>97460000000</v>
+        <v>96180000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96040000000</v>
+        <v>95080000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,22 +2166,22 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94190000000</v>
+        <v>94940000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93570000000</v>
+        <v>94900000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93290000000</v>
+        <v>94130000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,37 +2211,37 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92680000000</v>
+        <v>90590000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89260000000</v>
+        <v>87680000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>86770000000</v>
+        <v>87520000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86170000000</v>
+        <v>85660000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84390000000</v>
+        <v>83610000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,52 +2286,52 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>81960000000</v>
+        <v>82870000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79220000000</v>
+        <v>79430000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>77450000000</v>
+        <v>78520000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>77230000000</v>
+        <v>78440000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,67 +2346,67 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76050000000</v>
+        <v>76400000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75650000000</v>
+        <v>75510000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74840000000</v>
+        <v>75260000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74210000000</v>
+        <v>73590000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72500000000</v>
+        <v>71180000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,127 +2421,127 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>71960000000</v>
+        <v>71060000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70110000000</v>
+        <v>69520000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69550000000</v>
+        <v>68560000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68630000000</v>
+        <v>68240000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>68470000000</v>
+        <v>67260000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>67930000000</v>
+        <v>66310000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>67620000000</v>
+        <v>64470000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>63220000000</v>
+        <v>61540000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>61560000000</v>
+        <v>58930000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,37 +2556,37 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>58310000000</v>
+        <v>58190000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54730000000</v>
+        <v>55960000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53870000000</v>
+        <v>53670000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,52 +2601,52 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>51390000000</v>
+        <v>51040000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>50590000000</v>
+        <v>49440000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49850000000</v>
+        <v>49130000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>49010000000</v>
+        <v>48780000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,22 +2661,22 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>48970000000</v>
+        <v>48330000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>48340000000</v>
+        <v>47080000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46720000000</v>
+        <v>47010000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45990000000</v>
+        <v>45700000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44960000000</v>
+        <v>44410000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>44920000000</v>
+        <v>43040000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>43060000000</v>
+        <v>41930000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41300000000</v>
+        <v>40430000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40340000000</v>
+        <v>40380000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39100000000</v>
+        <v>38940000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35740000000</v>
+        <v>35160000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34610000000</v>
+        <v>34820000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>33830000000</v>
+        <v>34220000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>31870000000</v>
+        <v>32510000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,37 +2871,37 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29480000000</v>
+        <v>29570000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28660000000</v>
+        <v>29520000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28550000000</v>
+        <v>29380000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27490000000</v>
+        <v>27650000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25270000000</v>
+        <v>25410000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24180000000</v>
+        <v>24090000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22580000000</v>
+        <v>22680000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21460000000</v>
+        <v>20620000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20360000000</v>
+        <v>20230000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19320000000</v>
+        <v>19360000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>19020000000</v>
+        <v>18730000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17570000000</v>
+        <v>17030000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>17540000000</v>
+        <v>16750000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>16250000000</v>
+        <v>15230000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12520000000</v>
+        <v>12560000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12520000000</v>
+        <v>12560000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11340000000</v>
+        <v>11500000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10740000000</v>
+        <v>10670000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9980000000</v>
+        <v>10160000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8980000000</v>
+        <v>8810000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7580000000</v>
+        <v>7120000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,22 +3186,22 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7290000000</v>
+        <v>7060000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7170000000</v>
+        <v>6890000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,37 +3216,37 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6960000000</v>
+        <v>6880000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6910000000</v>
+        <v>6850000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6880000000</v>
+        <v>6810000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,37 +3261,37 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6820000000</v>
+        <v>6670000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6350000000</v>
+        <v>6160000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6260000000</v>
+        <v>6080000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5220000000</v>
+        <v>5060000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>5060000000</v>
+        <v>4870000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4310000000</v>
+        <v>4190000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4240000000</v>
+        <v>4030000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4060000000</v>
+        <v>4000000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3580000000</v>
+        <v>3620000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3450000000</v>
+        <v>3300000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3150000000</v>
+        <v>3010000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2780000000</v>
+        <v>2810000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2320000000</v>
+        <v>2340000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2130000000</v>
+        <v>2110000000</v>
       </c>
     </row>
     <row r="199">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1780000000</v>
+        <v>1720000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1480000000</v>
+        <v>1420000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1120000000</v>
+        <v>1090000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1050000000</v>
+        <v>1010000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>885480000</v>
+        <v>859700000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>436940000</v>
+        <v>438460000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4913420000000</v>
+        <v>4968150000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5723030000000</v>
+        <v>5554570000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4269210000000</v>
+        <v>4238470000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3933760000000</v>
+        <v>3880660000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2803580000000</v>
+        <v>2740370000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2449060000000</v>
+        <v>2375360000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1837540000000</v>
+        <v>1836470000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1797320000000</v>
+        <v>1719180000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1492180000000</v>
+        <v>1481080000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1228780000000</v>
+        <v>1169870000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1119010000000</v>
+        <v>1101010000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1054350000000</v>
+        <v>1013240000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>974450000000</v>
+        <v>984020000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>876090000000</v>
+        <v>880980000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,52 +771,52 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>858110000000</v>
+        <v>877150000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>695670000000</v>
+        <v>700330000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>694730000000</v>
+        <v>692860000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>674560000000</v>
+        <v>682110000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>622840000000</v>
+        <v>618090000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>499380000000</v>
+        <v>503500000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>479520000000</v>
+        <v>481400000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>466480000000</v>
+        <v>477680000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,127 +891,127 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>462820000000</v>
+        <v>452960000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>434090000000</v>
+        <v>420180000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>417670000000</v>
+        <v>417970000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>413190000000</v>
+        <v>410290000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>412360000000</v>
+        <v>404390000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>405330000000</v>
+        <v>401190000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>374250000000</v>
+        <v>377630000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>374100000000</v>
+        <v>374880000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>369240000000</v>
+        <v>365980000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>368110000000</v>
+        <v>365310000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>352290000000</v>
+        <v>351280000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>343340000000</v>
+        <v>349770000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>337480000000</v>
+        <v>332960000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>331760000000</v>
+        <v>325970000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,82 +1101,82 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>315020000000</v>
+        <v>317100000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>314390000000</v>
+        <v>312500000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>300330000000</v>
+        <v>298010000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>297950000000</v>
+        <v>294790000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>290230000000</v>
+        <v>294390000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>285110000000</v>
+        <v>294010000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>276470000000</v>
+        <v>285700000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,52 +1206,52 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>271790000000</v>
+        <v>269310000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>266190000000</v>
+        <v>266160000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>265560000000</v>
+        <v>263200000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>263910000000</v>
+        <v>262960000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>262280000000</v>
+        <v>261970000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>258330000000</v>
+        <v>256980000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,127 +1296,127 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>256860000000</v>
+        <v>256720000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>248330000000</v>
+        <v>248420000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>247800000000</v>
+        <v>248060000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>244790000000</v>
+        <v>246250000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>242950000000</v>
+        <v>245150000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>242710000000</v>
+        <v>241070000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>242530000000</v>
+        <v>235660000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>223320000000</v>
+        <v>222050000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>223110000000</v>
+        <v>220280000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,52 +1431,52 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>216600000000</v>
+        <v>220260000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>213620000000</v>
+        <v>214850000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>213570000000</v>
+        <v>213500000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>207750000000</v>
+        <v>211730000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>205460000000</v>
+        <v>208060000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,37 +1506,37 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>190160000000</v>
+        <v>192570000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>189140000000</v>
+        <v>191320000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187340000000</v>
+        <v>187950000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,52 +1551,52 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>184810000000</v>
+        <v>187480000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>182090000000</v>
+        <v>184790000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>180870000000</v>
+        <v>183760000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>179830000000</v>
+        <v>182400000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,52 +1611,52 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>177110000000</v>
+        <v>175950000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>173790000000</v>
+        <v>175170000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>170840000000</v>
+        <v>173090000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>168880000000</v>
+        <v>170430000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,37 +1671,37 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167680000000</v>
+        <v>170420000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>165290000000</v>
+        <v>167640000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>163380000000</v>
+        <v>167520000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>160750000000</v>
+        <v>161390000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>153600000000</v>
+        <v>152870000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>148840000000</v>
+        <v>148390000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,82 +1761,82 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>146440000000</v>
+        <v>146760000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>146170000000</v>
+        <v>143470000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>140620000000</v>
+        <v>141800000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139810000000</v>
+        <v>139930000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>138870000000</v>
+        <v>132630000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>129130000000</v>
+        <v>131650000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,82 +1851,82 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>128010000000</v>
+        <v>127750000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>124430000000</v>
+        <v>127500000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>123390000000</v>
+        <v>127100000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>122120000000</v>
+        <v>125320000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>121950000000</v>
+        <v>121740000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>120330000000</v>
+        <v>121700000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>117430000000</v>
+        <v>121150000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,37 +1956,37 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>117120000000</v>
+        <v>120200000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>116500000000</v>
+        <v>119250000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>115850000000</v>
+        <v>118720000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,82 +2001,82 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>115220000000</v>
+        <v>117220000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>111740000000</v>
+        <v>112250000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>109380000000</v>
+        <v>111400000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>106680000000</v>
+        <v>108380000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>105600000000</v>
+        <v>107280000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>104610000000</v>
+        <v>106260000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>101850000000</v>
+        <v>105960000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>101810000000</v>
+        <v>99770000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>97430000000</v>
+        <v>98310000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96180000000</v>
+        <v>97740000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>95080000000</v>
+        <v>96350000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94940000000</v>
+        <v>94130000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,82 +2181,82 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94900000000</v>
+        <v>93830000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>94130000000</v>
+        <v>93820000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90590000000</v>
+        <v>93740000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87680000000</v>
+        <v>88860000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87520000000</v>
+        <v>87210000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>85660000000</v>
+        <v>86950000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>83610000000</v>
+        <v>84360000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>82870000000</v>
+        <v>84310000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>79430000000</v>
+        <v>81210000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>78520000000</v>
+        <v>80080000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>78440000000</v>
+        <v>78650000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76400000000</v>
+        <v>76140000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75510000000</v>
+        <v>75260000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75260000000</v>
+        <v>74290000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>73590000000</v>
+        <v>74260000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>71180000000</v>
+        <v>72690000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,172 +2421,172 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>71060000000</v>
+        <v>72170000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69520000000</v>
+        <v>70310000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>68560000000</v>
+        <v>70230000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68240000000</v>
+        <v>68830000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>67260000000</v>
+        <v>68090000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>66310000000</v>
+        <v>63930000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>64470000000</v>
+        <v>61840000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61540000000</v>
+        <v>60260000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>58930000000</v>
+        <v>60210000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>58190000000</v>
+        <v>59730000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>55960000000</v>
+        <v>52660000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53670000000</v>
+        <v>52410000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,22 +2601,22 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>51040000000</v>
+        <v>51600000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49440000000</v>
+        <v>48850000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49130000000</v>
+        <v>48820000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48780000000</v>
+        <v>48560000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>48330000000</v>
+        <v>47070000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,22 +2676,22 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>47080000000</v>
+        <v>45380000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>47010000000</v>
+        <v>45260000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,67 +2706,67 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45700000000</v>
+        <v>45200000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44410000000</v>
+        <v>44990000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>43040000000</v>
+        <v>42350000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>41930000000</v>
+        <v>41350000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>40430000000</v>
+        <v>40930000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,52 +2781,52 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40380000000</v>
+        <v>40830000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38940000000</v>
+        <v>39950000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35160000000</v>
+        <v>35350000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34820000000</v>
+        <v>35130000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>34220000000</v>
+        <v>34170000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32510000000</v>
+        <v>32360000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,37 +2871,37 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29570000000</v>
+        <v>30200000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29520000000</v>
+        <v>30100000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>29380000000</v>
+        <v>28100000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27650000000</v>
+        <v>27620000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25410000000</v>
+        <v>26030000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24090000000</v>
+        <v>24430000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22680000000</v>
+        <v>22840000000</v>
       </c>
     </row>
     <row r="166">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20230000000</v>
+        <v>20160000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19360000000</v>
+        <v>19320000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18730000000</v>
+        <v>19220000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17030000000</v>
+        <v>17670000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16750000000</v>
+        <v>15980000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>15230000000</v>
+        <v>14050000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12560000000</v>
+        <v>12680000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12560000000</v>
+        <v>12680000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11500000000</v>
+        <v>11630000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10670000000</v>
+        <v>10680000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10160000000</v>
+        <v>10220000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8810000000</v>
+        <v>8840000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,112 +3171,112 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7120000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7060000000</v>
+        <v>7000000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6890000000</v>
+        <v>6990000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6880000000</v>
+        <v>6950000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6850000000</v>
+        <v>6930000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6810000000</v>
+        <v>6590000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6670000000</v>
+        <v>6550000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6160000000</v>
+        <v>6430000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6080000000</v>
+        <v>6000000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5060000000</v>
+        <v>4880000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,37 +3321,37 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4870000000</v>
+        <v>4720000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4190000000</v>
+        <v>4030000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4030000000</v>
+        <v>3990000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4000000000</v>
+        <v>3830000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3620000000</v>
+        <v>3630000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3300000000</v>
+        <v>3150000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>3010000000</v>
+        <v>2910000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2810000000</v>
+        <v>2740000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2340000000</v>
+        <v>2350000000</v>
       </c>
     </row>
     <row r="198">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1810000000</v>
+        <v>1820000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1720000000</v>
+        <v>1690000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1420000000</v>
+        <v>1380000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1090000000</v>
+        <v>1070000000</v>
       </c>
     </row>
     <row r="203">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>859700000</v>
+        <v>819440000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>438460000</v>
+        <v>433860000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4968150000000</v>
+        <v>4912980000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5554570000000</v>
+        <v>5525650000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4238470000000</v>
+        <v>4277520000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3880660000000</v>
+        <v>3973190000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2740370000000</v>
+        <v>2830650000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2375360000000</v>
+        <v>2351080000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1836470000000</v>
+        <v>1830820000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1719180000000</v>
+        <v>1725860000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1481080000000</v>
+        <v>1511490000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1169870000000</v>
+        <v>1162150000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1101010000000</v>
+        <v>1110110000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1013240000000</v>
+        <v>992710000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>984020000000</v>
+        <v>992710000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>880980000000</v>
+        <v>885150000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>877150000000</v>
+        <v>883420000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>700330000000</v>
+        <v>719650000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>692860000000</v>
+        <v>694670000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>682110000000</v>
+        <v>686180000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>618090000000</v>
+        <v>630040000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,37 +846,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>503500000000</v>
+        <v>516090000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>481400000000</v>
+        <v>502360000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>477680000000</v>
+        <v>488550000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,52 +891,52 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>452960000000</v>
+        <v>466760000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>420180000000</v>
+        <v>427560000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>417970000000</v>
+        <v>419610000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>410290000000</v>
+        <v>418820000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>404390000000</v>
+        <v>402380000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,67 +966,67 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>401190000000</v>
+        <v>399000000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>377630000000</v>
+        <v>379850000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>374880000000</v>
+        <v>378840000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>365980000000</v>
+        <v>372620000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>365310000000</v>
+        <v>367960000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>351280000000</v>
+        <v>359220000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,37 +1056,37 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>349770000000</v>
+        <v>351260000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>332960000000</v>
+        <v>342560000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>325970000000</v>
+        <v>340460000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>317100000000</v>
+        <v>319780000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,82 +1116,82 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>312500000000</v>
+        <v>313580000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>298010000000</v>
+        <v>298440000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>294790000000</v>
+        <v>292720000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>294390000000</v>
+        <v>290070000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>294010000000</v>
+        <v>285640000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>285700000000</v>
+        <v>284390000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,82 +1206,82 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>269310000000</v>
+        <v>281620000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>266160000000</v>
+        <v>277060000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>263200000000</v>
+        <v>267590000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>262960000000</v>
+        <v>263140000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>261970000000</v>
+        <v>260690000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>256980000000</v>
+        <v>259120000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,67 +1296,67 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>256720000000</v>
+        <v>255220000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>248420000000</v>
+        <v>252660000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>248060000000</v>
+        <v>250640000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>246250000000</v>
+        <v>247900000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>245150000000</v>
+        <v>246900000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>241070000000</v>
+        <v>243300000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,97 +1386,97 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>235660000000</v>
+        <v>228620000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>222050000000</v>
+        <v>224290000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>220280000000</v>
+        <v>222990000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>220260000000</v>
+        <v>219820000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>214850000000</v>
+        <v>219430000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>213500000000</v>
+        <v>217460000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>211730000000</v>
+        <v>213990000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,67 +1491,67 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>208060000000</v>
+        <v>208110000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>192570000000</v>
+        <v>191530000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>191320000000</v>
+        <v>188570000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187950000000</v>
+        <v>187440000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187480000000</v>
+        <v>187410000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,52 +1566,52 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184790000000</v>
+        <v>186570000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>183760000000</v>
+        <v>175860000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182400000000</v>
+        <v>173050000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175950000000</v>
+        <v>172350000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,112 +1626,112 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>175170000000</v>
+        <v>171940000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>173090000000</v>
+        <v>167420000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>170430000000</v>
+        <v>167230000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>170420000000</v>
+        <v>166460000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>167640000000</v>
+        <v>161410000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>167520000000</v>
+        <v>159380000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>161390000000</v>
+        <v>154520000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>152870000000</v>
+        <v>151990000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>148390000000</v>
+        <v>150460000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,37 +1761,37 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>146760000000</v>
+        <v>149780000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>143470000000</v>
+        <v>148710000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>141800000000</v>
+        <v>146060000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,142 +1806,142 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139930000000</v>
+        <v>141930000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>132630000000</v>
+        <v>134960000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131650000000</v>
+        <v>131630000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>127750000000</v>
+        <v>130140000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>127500000000</v>
+        <v>129280000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>127100000000</v>
+        <v>128520000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>125320000000</v>
+        <v>127930000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>121740000000</v>
+        <v>126350000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>121700000000</v>
+        <v>125510000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>121150000000</v>
+        <v>120770000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,37 +1956,37 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120200000000</v>
+        <v>120480000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119250000000</v>
+        <v>120230000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118720000000</v>
+        <v>119690000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,37 +2001,37 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117220000000</v>
+        <v>117610000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>112250000000</v>
+        <v>115790000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>111400000000</v>
+        <v>113180000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>108380000000</v>
+        <v>108940000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,22 +2061,22 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>107280000000</v>
+        <v>107340000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>106260000000</v>
+        <v>105300000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,37 +2091,37 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>105960000000</v>
+        <v>104360000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>99770000000</v>
+        <v>103460000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>98310000000</v>
+        <v>101240000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>97740000000</v>
+        <v>99320000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96350000000</v>
+        <v>97660000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,37 +2166,37 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94130000000</v>
+        <v>95810000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93830000000</v>
+        <v>94290000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93820000000</v>
+        <v>93470000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,67 +2211,67 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>93740000000</v>
+        <v>92710000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>88860000000</v>
+        <v>89830000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87210000000</v>
+        <v>89500000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>86950000000</v>
+        <v>88930000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>84360000000</v>
+        <v>87680000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,97 +2286,97 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>84310000000</v>
+        <v>83870000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>81210000000</v>
+        <v>82490000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>80080000000</v>
+        <v>80910000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>78650000000</v>
+        <v>80460000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>76140000000</v>
+        <v>77870000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75260000000</v>
+        <v>76860000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74290000000</v>
+        <v>75490000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74260000000</v>
+        <v>74630000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72690000000</v>
+        <v>72650000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,67 +2421,67 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72170000000</v>
+        <v>72590000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70310000000</v>
+        <v>70370000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70230000000</v>
+        <v>70070000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68830000000</v>
+        <v>69800000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>68090000000</v>
+        <v>68290000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63930000000</v>
+        <v>65130000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,82 +2511,82 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61840000000</v>
+        <v>62100000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60260000000</v>
+        <v>60100000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>60210000000</v>
+        <v>60090000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>59730000000</v>
+        <v>59370000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>52660000000</v>
+        <v>54200000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>52410000000</v>
+        <v>54000000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,52 +2601,52 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>51600000000</v>
+        <v>51560000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48850000000</v>
+        <v>49190000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48820000000</v>
+        <v>49120000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48560000000</v>
+        <v>48530000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47070000000</v>
+        <v>47500000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,52 +2676,52 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45380000000</v>
+        <v>47330000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45260000000</v>
+        <v>46410000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45200000000</v>
+        <v>45270000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44990000000</v>
+        <v>44970000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,67 +2736,67 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42350000000</v>
+        <v>44460000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>41350000000</v>
+        <v>42000000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>40930000000</v>
+        <v>41080000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40830000000</v>
+        <v>40820000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39950000000</v>
+        <v>39970000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35350000000</v>
+        <v>38110000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>35130000000</v>
+        <v>35530000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>34170000000</v>
+        <v>35430000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32360000000</v>
+        <v>32580000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30200000000</v>
+        <v>30910000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,37 +2886,37 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>30100000000</v>
+        <v>30770000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28100000000</v>
+        <v>28520000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27620000000</v>
+        <v>27500000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>26030000000</v>
+        <v>27230000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24430000000</v>
+        <v>24260000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22840000000</v>
+        <v>22700000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20620000000</v>
+        <v>21560000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20160000000</v>
+        <v>20410000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19320000000</v>
+        <v>19110000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>19220000000</v>
+        <v>18210000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17670000000</v>
+        <v>17420000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>15980000000</v>
+        <v>16160000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>14050000000</v>
+        <v>13850000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12680000000</v>
+        <v>13010000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12680000000</v>
+        <v>13010000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11630000000</v>
+        <v>12120000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10680000000</v>
+        <v>10600000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10220000000</v>
+        <v>10300000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,108 +3156,108 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8840000000</v>
+        <v>9140000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7130000000</v>
+        <v>7230000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7000000000</v>
+        <v>7210000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6990000000</v>
+        <v>7160000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6950000000</v>
+        <v>6970000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6930000000</v>
+        <v>6970000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6590000000</v>
+        <v>6650000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6430000000</v>
+        <v>6450000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6000000000</v>
+        <v>6040000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4880000000</v>
+        <v>5160000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4720000000</v>
+        <v>4680000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4030000000</v>
+        <v>4670000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3990000000</v>
+        <v>3920000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3830000000</v>
+        <v>3730000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3630000000</v>
+        <v>3600000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3150000000</v>
+        <v>3090000000</v>
       </c>
     </row>
     <row r="195">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2740000000</v>
+        <v>2700000000</v>
       </c>
     </row>
     <row r="197">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2110000000</v>
+        <v>2080000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1820000000</v>
+        <v>1850000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1690000000</v>
+        <v>1680000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,37 +3501,37 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1380000000</v>
+        <v>1370000000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>TDOC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Teladoc Health Inc</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1070000000</v>
+        <v>1050000000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TDOC</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Teladoc Health Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1010000000</v>
+        <v>1040000000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>819440000</v>
+        <v>823730000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>433860000</v>
+        <v>406270000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4277520000000</v>
+        <v>4279800000000</v>
       </c>
     </row>
     <row r="8">
@@ -717,27 +717,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>992710000000</v>
+        <v>992980000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>171940000000</v>
+        <v>171660000000</v>
       </c>
     </row>
     <row r="77">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103460000000</v>
+        <v>103450000000</v>
       </c>
     </row>
     <row r="109">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6550000000</v>
+        <v>6560000000</v>
       </c>
     </row>
     <row r="186">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4912980000000</v>
+        <v>4976180000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5525650000000</v>
+        <v>5454310000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4279800000000</v>
+        <v>4293460000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3973190000000</v>
+        <v>4018330000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2830650000000</v>
+        <v>2799370000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2351080000000</v>
+        <v>2304610000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1830820000000</v>
+        <v>1892700000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1725860000000</v>
+        <v>1693350000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1511490000000</v>
+        <v>1493050000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1162150000000</v>
+        <v>1117010000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1110110000000</v>
+        <v>1113270000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>992980000000</v>
+        <v>996790000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>992710000000</v>
+        <v>970080000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>885150000000</v>
+        <v>897150000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>883420000000</v>
+        <v>888630000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>719650000000</v>
+        <v>726790000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>694670000000</v>
+        <v>707870000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>686180000000</v>
+        <v>674580000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>630040000000</v>
+        <v>635560000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>516090000000</v>
+        <v>521300000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>502360000000</v>
+        <v>502240000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>488550000000</v>
+        <v>496770000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,52 +891,52 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>466760000000</v>
+        <v>454740000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>427560000000</v>
+        <v>425160000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>419610000000</v>
+        <v>424790000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>418820000000</v>
+        <v>415430000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>402380000000</v>
+        <v>394840000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,67 +966,67 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>399000000000</v>
+        <v>387390000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>379850000000</v>
+        <v>386330000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>378840000000</v>
+        <v>381660000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>372620000000</v>
+        <v>367450000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>367960000000</v>
+        <v>366710000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>359220000000</v>
+        <v>358850000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,37 +1056,37 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>351260000000</v>
+        <v>355830000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>342560000000</v>
+        <v>339760000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>340460000000</v>
+        <v>330330000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>319780000000</v>
+        <v>320230000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>313580000000</v>
+        <v>314840000000</v>
       </c>
     </row>
     <row r="43">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>292720000000</v>
+        <v>294020000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>290070000000</v>
+        <v>289950000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,52 +1176,52 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>285640000000</v>
+        <v>289520000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>284390000000</v>
+        <v>275590000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>281620000000</v>
+        <v>272600000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>277060000000</v>
+        <v>269310000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>267590000000</v>
+        <v>265480000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>263140000000</v>
+        <v>263310000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>260690000000</v>
+        <v>260290000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,67 +1281,67 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>259120000000</v>
+        <v>257300000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>255220000000</v>
+        <v>251960000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>252660000000</v>
+        <v>251570000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>250640000000</v>
+        <v>251440000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>247900000000</v>
+        <v>248110000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>246900000000</v>
+        <v>245550000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>243300000000</v>
+        <v>244860000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>228620000000</v>
+        <v>230590000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>224290000000</v>
+        <v>225750000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>222990000000</v>
+        <v>224660000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>219820000000</v>
+        <v>221290000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,22 +1446,22 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>219430000000</v>
+        <v>218740000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>217460000000</v>
+        <v>214960000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>213990000000</v>
+        <v>213880000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>208110000000</v>
+        <v>210380000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>191530000000</v>
+        <v>196550000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,97 +1521,97 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>188570000000</v>
+        <v>192520000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187440000000</v>
+        <v>187330000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187410000000</v>
+        <v>186530000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>186570000000</v>
+        <v>186260000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>175860000000</v>
+        <v>177740000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>173050000000</v>
+        <v>176190000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>172350000000</v>
+        <v>176110000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>171660000000</v>
+        <v>172630000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>167420000000</v>
+        <v>170570000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>167230000000</v>
+        <v>167850000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>166460000000</v>
+        <v>166760000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>161410000000</v>
+        <v>163770000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>159380000000</v>
+        <v>162910000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>154520000000</v>
+        <v>155500000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,33 +1731,33 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>151990000000</v>
+        <v>154110000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>150460000000</v>
+        <v>151080000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L85" t="n">
@@ -1767,31 +1767,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>148710000000</v>
+        <v>146040000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>146060000000</v>
+        <v>144840000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,232 +1806,232 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>141930000000</v>
+        <v>142540000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>134960000000</v>
+        <v>133120000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131630000000</v>
+        <v>131490000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>130140000000</v>
+        <v>129080000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>129280000000</v>
+        <v>128400000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128520000000</v>
+        <v>128000000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>127930000000</v>
+        <v>127140000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>126350000000</v>
+        <v>126870000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>125510000000</v>
+        <v>124940000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120770000000</v>
+        <v>121510000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120480000000</v>
+        <v>119650000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120230000000</v>
+        <v>119040000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>119690000000</v>
+        <v>118140000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117610000000</v>
+        <v>117620000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>115790000000</v>
+        <v>117590000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>113180000000</v>
+        <v>115180000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>108940000000</v>
+        <v>108870000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,22 +2061,22 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>107340000000</v>
+        <v>108500000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>105300000000</v>
+        <v>105200000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,22 +2091,22 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104360000000</v>
+        <v>104110000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103450000000</v>
+        <v>103160000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,37 +2121,37 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>101240000000</v>
+        <v>101890000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99320000000</v>
+        <v>99290000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>97660000000</v>
+        <v>97900000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95810000000</v>
+        <v>95940000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94290000000</v>
+        <v>92680000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,82 +2196,82 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93470000000</v>
+        <v>92150000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92710000000</v>
+        <v>91540000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89830000000</v>
+        <v>90650000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>89500000000</v>
+        <v>89460000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>88930000000</v>
+        <v>88370000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87680000000</v>
+        <v>85330000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>83870000000</v>
+        <v>84250000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>82490000000</v>
+        <v>82970000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>80910000000</v>
+        <v>81770000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>80460000000</v>
+        <v>81110000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>77870000000</v>
+        <v>78540000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>76860000000</v>
+        <v>77340000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75490000000</v>
+        <v>75070000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74630000000</v>
+        <v>74870000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72650000000</v>
+        <v>72380000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72590000000</v>
+        <v>72280000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>70370000000</v>
+        <v>71730000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70070000000</v>
+        <v>70400000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>69800000000</v>
+        <v>69790000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>68290000000</v>
+        <v>68900000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>65130000000</v>
+        <v>64440000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,37 +2511,37 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62100000000</v>
+        <v>61990000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60100000000</v>
+        <v>61110000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>60090000000</v>
+        <v>57110000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,37 +2556,37 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>59370000000</v>
+        <v>56230000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54200000000</v>
+        <v>54360000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>54000000000</v>
+        <v>53070000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,67 +2601,67 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>51560000000</v>
+        <v>52510000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49190000000</v>
+        <v>49800000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49120000000</v>
+        <v>48810000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48530000000</v>
+        <v>47950000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47500000000</v>
+        <v>47850000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>47330000000</v>
+        <v>47590000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,37 +2691,37 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46410000000</v>
+        <v>46150000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45270000000</v>
+        <v>45370000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44970000000</v>
+        <v>44270000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>44460000000</v>
+        <v>43410000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>42000000000</v>
+        <v>41780000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41080000000</v>
+        <v>41290000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>40820000000</v>
+        <v>39320000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39970000000</v>
+        <v>38470000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>38110000000</v>
+        <v>36810000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>35530000000</v>
+        <v>36250000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>35430000000</v>
+        <v>35610000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32580000000</v>
+        <v>32140000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30910000000</v>
+        <v>31260000000</v>
       </c>
     </row>
     <row r="160">
@@ -2901,37 +2901,37 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28520000000</v>
+        <v>28580000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27500000000</v>
+        <v>26530000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>27230000000</v>
+        <v>26270000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24260000000</v>
+        <v>24490000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22700000000</v>
+        <v>22690000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21560000000</v>
+        <v>21400000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20410000000</v>
+        <v>19670000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19110000000</v>
+        <v>19310000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18210000000</v>
+        <v>18050000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17420000000</v>
+        <v>17490000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>16160000000</v>
+        <v>14690000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13850000000</v>
+        <v>13700000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>13010000000</v>
+        <v>12850000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>13010000000</v>
+        <v>12850000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,37 +3111,37 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12120000000</v>
+        <v>12130000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10600000000</v>
+        <v>10500000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10300000000</v>
+        <v>10420000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9140000000</v>
+        <v>8930000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7230000000</v>
+        <v>7180000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7210000000</v>
+        <v>7150000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7160000000</v>
+        <v>7030000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6970000000</v>
+        <v>6940000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6970000000</v>
+        <v>6680000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6650000000</v>
+        <v>6510000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6560000000</v>
+        <v>6290000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6450000000</v>
+        <v>5990000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>6040000000</v>
+        <v>5820000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5160000000</v>
+        <v>4980000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4680000000</v>
+        <v>4420000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4670000000</v>
+        <v>4210000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3920000000</v>
+        <v>3880000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3730000000</v>
+        <v>3650000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3600000000</v>
+        <v>3490000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>3090000000</v>
+        <v>2880000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2910000000</v>
+        <v>2770000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2700000000</v>
+        <v>2710000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2350000000</v>
+        <v>2310000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2080000000</v>
+        <v>2060000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1850000000</v>
+        <v>1870000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1680000000</v>
+        <v>1570000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1370000000</v>
+        <v>1310000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1050000000</v>
+        <v>1080000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>1040000000</v>
+        <v>981140000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>823730000</v>
+        <v>767350000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>406270000</v>
+        <v>374080000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4976180000000</v>
+        <v>4980560000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5454310000000</v>
+        <v>5507330000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4293460000000</v>
+        <v>4299810000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4018330000000</v>
+        <v>4035410000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2799370000000</v>
+        <v>2789130000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2304610000000</v>
+        <v>2308610000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1892700000000</v>
+        <v>1942470000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1693350000000</v>
+        <v>1705670000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,37 +681,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1493050000000</v>
+        <v>1481990000000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Lilly(Eli) &amp; Co</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1117010000000</v>
+        <v>1098100000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lilly(Eli) &amp; Co</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1113270000000</v>
+        <v>1078460000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>996790000000</v>
+        <v>1002590000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>970080000000</v>
+        <v>988510000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>897150000000</v>
+        <v>890800000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>888630000000</v>
+        <v>881000000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>726790000000</v>
+        <v>739460000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>707870000000</v>
+        <v>715800000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>674580000000</v>
+        <v>662060000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>635560000000</v>
+        <v>599120000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>521300000000</v>
+        <v>529810000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>502240000000</v>
+        <v>501450000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>496770000000</v>
+        <v>484830000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>454740000000</v>
+        <v>453670000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>425160000000</v>
+        <v>433000000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,142 +921,142 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>424790000000</v>
+        <v>430180000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>415430000000</v>
+        <v>423020000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>394840000000</v>
+        <v>387700000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>387390000000</v>
+        <v>377330000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>386330000000</v>
+        <v>376820000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>381660000000</v>
+        <v>368420000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>367450000000</v>
+        <v>363980000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>366710000000</v>
+        <v>355460000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>358850000000</v>
+        <v>355230000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>355830000000</v>
+        <v>350290000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>339760000000</v>
+        <v>339080000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>330330000000</v>
+        <v>324770000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>320230000000</v>
+        <v>319190000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,22 +1116,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>314840000000</v>
+        <v>310620000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>298440000000</v>
+        <v>293510000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>294020000000</v>
+        <v>293390000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,22 +1161,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>289950000000</v>
+        <v>293240000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>289520000000</v>
+        <v>293130000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>275590000000</v>
+        <v>275770000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>272600000000</v>
+        <v>272760000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>269310000000</v>
+        <v>267460000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,67 +1236,67 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>265480000000</v>
+        <v>267410000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>263310000000</v>
+        <v>262880000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>260290000000</v>
+        <v>260690000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>257300000000</v>
+        <v>259700000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>251960000000</v>
+        <v>253640000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,37 +1311,37 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>251570000000</v>
+        <v>246670000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>251440000000</v>
+        <v>245160000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>248110000000</v>
+        <v>244160000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,22 +1356,22 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>245550000000</v>
+        <v>241660000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>244860000000</v>
+        <v>240120000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,67 +1386,67 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>230590000000</v>
+        <v>227120000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>225750000000</v>
+        <v>226850000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>224660000000</v>
+        <v>223470000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>221290000000</v>
+        <v>223190000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>218740000000</v>
+        <v>217430000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,37 +1461,37 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>214960000000</v>
+        <v>214240000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>213880000000</v>
+        <v>209240000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>210380000000</v>
+        <v>208890000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>196550000000</v>
+        <v>197840000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,52 +1521,52 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>192520000000</v>
+        <v>195880000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>187330000000</v>
+        <v>188860000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>186530000000</v>
+        <v>187480000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>186260000000</v>
+        <v>183410000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>177740000000</v>
+        <v>180860000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,22 +1596,22 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>176190000000</v>
+        <v>177550000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>176110000000</v>
+        <v>175260000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,82 +1626,82 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>172630000000</v>
+        <v>173480000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>170570000000</v>
+        <v>173220000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>167850000000</v>
+        <v>166870000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>166760000000</v>
+        <v>165910000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163770000000</v>
+        <v>164900000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>162910000000</v>
+        <v>163170000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>155500000000</v>
+        <v>156650000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>154110000000</v>
+        <v>156580000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>151080000000</v>
+        <v>149100000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>149780000000</v>
+        <v>147400000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>146040000000</v>
+        <v>145680000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>144840000000</v>
+        <v>142510000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>142540000000</v>
+        <v>136580000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>133120000000</v>
+        <v>133550000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,22 +1836,22 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131490000000</v>
+        <v>130690000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>129080000000</v>
+        <v>129520000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,52 +1866,52 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>128400000000</v>
+        <v>129450000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128000000000</v>
+        <v>127950000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>127140000000</v>
+        <v>127340000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>126870000000</v>
+        <v>126220000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>124940000000</v>
+        <v>123810000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>121510000000</v>
+        <v>120870000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,142 +1956,142 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119650000000</v>
+        <v>119490000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119040000000</v>
+        <v>118980000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118140000000</v>
+        <v>118350000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117620000000</v>
+        <v>116660000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117590000000</v>
+        <v>116320000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>115180000000</v>
+        <v>115760000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>108870000000</v>
+        <v>109330000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>108500000000</v>
+        <v>108590000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>105200000000</v>
+        <v>105890000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104110000000</v>
+        <v>104880000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103160000000</v>
+        <v>101740000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>101890000000</v>
+        <v>100590000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99290000000</v>
+        <v>99750000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>97900000000</v>
+        <v>99150000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,52 +2166,52 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95940000000</v>
+        <v>95110000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92680000000</v>
+        <v>92230000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92150000000</v>
+        <v>91960000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>91540000000</v>
+        <v>91350000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>90650000000</v>
+        <v>91120000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>89460000000</v>
+        <v>88640000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>88370000000</v>
+        <v>87810000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85330000000</v>
+        <v>86330000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>84250000000</v>
+        <v>84470000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,37 +2301,37 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>82970000000</v>
+        <v>83940000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>81770000000</v>
+        <v>80650000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81110000000</v>
+        <v>80560000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,37 +2346,37 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>78540000000</v>
+        <v>77540000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>77340000000</v>
+        <v>75290000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75070000000</v>
+        <v>75260000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,37 +2391,37 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74870000000</v>
+        <v>74660000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72380000000</v>
+        <v>73710000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72280000000</v>
+        <v>72380000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>71730000000</v>
+        <v>71710000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70400000000</v>
+        <v>69050000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>69790000000</v>
+        <v>68670000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>68900000000</v>
+        <v>68390000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64440000000</v>
+        <v>64230000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61990000000</v>
+        <v>62370000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,67 +2526,67 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61110000000</v>
+        <v>61630000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>57110000000</v>
+        <v>56450000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>56230000000</v>
+        <v>56240000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54360000000</v>
+        <v>54490000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>53070000000</v>
+        <v>54390000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52510000000</v>
+        <v>52480000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,52 +2616,52 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49800000000</v>
+        <v>49150000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48810000000</v>
+        <v>48250000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47950000000</v>
+        <v>48160000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47850000000</v>
+        <v>48050000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>47590000000</v>
+        <v>47960000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46150000000</v>
+        <v>46180000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,37 +2706,37 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45370000000</v>
+        <v>44830000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>44270000000</v>
+        <v>43250000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>43410000000</v>
+        <v>42920000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>41780000000</v>
+        <v>40950000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>41290000000</v>
+        <v>40770000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>39320000000</v>
+        <v>38430000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38470000000</v>
+        <v>38410000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>36810000000</v>
+        <v>37280000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>36250000000</v>
+        <v>36130000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>35610000000</v>
+        <v>35940000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32140000000</v>
+        <v>32210000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>31260000000</v>
+        <v>30700000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>30770000000</v>
+        <v>29880000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28580000000</v>
+        <v>28640000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26530000000</v>
+        <v>26280000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>26270000000</v>
+        <v>25670000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24490000000</v>
+        <v>24810000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22690000000</v>
+        <v>22670000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,37 +2976,37 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21400000000</v>
+        <v>21500000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19670000000</v>
+        <v>20050000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19310000000</v>
+        <v>19680000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18050000000</v>
+        <v>18840000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17490000000</v>
+        <v>17540000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14690000000</v>
+        <v>14070000000</v>
       </c>
     </row>
     <row r="172">
@@ -3072,16 +3072,16 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12850000000</v>
+        <v>12670000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,52 +3096,52 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12850000000</v>
+        <v>12150000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12130000000</v>
+        <v>12150000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10500000000</v>
+        <v>10650000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10420000000</v>
+        <v>10430000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8930000000</v>
+        <v>8360000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7180000000</v>
+        <v>7070000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,67 +3186,67 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7150000000</v>
+        <v>6930000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7030000000</v>
+        <v>6840000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6940000000</v>
+        <v>6790000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6680000000</v>
+        <v>6640000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6510000000</v>
+        <v>6460000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,37 +3261,37 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6290000000</v>
+        <v>6330000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5990000000</v>
+        <v>5970000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5820000000</v>
+        <v>5910000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,37 +3306,37 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4980000000</v>
+        <v>4840000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4420000000</v>
+        <v>4320000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4210000000</v>
+        <v>4270000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3880000000</v>
+        <v>3910000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3650000000</v>
+        <v>3520000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3490000000</v>
+        <v>3460000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2880000000</v>
+        <v>2790000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2770000000</v>
+        <v>2750000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2710000000</v>
+        <v>2740000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2310000000</v>
+        <v>2320000000</v>
       </c>
     </row>
     <row r="198">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1870000000</v>
+        <v>1930000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1570000000</v>
+        <v>1550000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1310000000</v>
+        <v>1250000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1080000000</v>
+        <v>1090000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>981140000</v>
+        <v>971160000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>767350000</v>
+        <v>770570000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>374080000</v>
+        <v>349540000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4980560000000</v>
+        <v>5005220000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5507330000000</v>
+        <v>5333330000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4299810000000</v>
+        <v>4230910000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4035410000000</v>
+        <v>3962940000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2789130000000</v>
+        <v>2740590000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2308610000000</v>
+        <v>2230190000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1942470000000</v>
+        <v>1878890000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1705670000000</v>
+        <v>1652870000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1481990000000</v>
+        <v>1450120000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1098100000000</v>
+        <v>1137860000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1078460000000</v>
+        <v>1034270000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1002590000000</v>
+        <v>1012950000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>988510000000</v>
+        <v>931850000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>890800000000</v>
+        <v>921580000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>881000000000</v>
+        <v>891240000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>739460000000</v>
+        <v>730820000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>715800000000</v>
+        <v>727850000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>662060000000</v>
+        <v>635940000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>599120000000</v>
+        <v>611900000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,37 +846,37 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>529810000000</v>
+        <v>528440000000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>501450000000</v>
+        <v>500940000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>484830000000</v>
+        <v>482940000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,202 +891,202 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>453670000000</v>
+        <v>448040000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>433000000000</v>
+        <v>438700000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>430180000000</v>
+        <v>435150000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>423020000000</v>
+        <v>394890000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>387700000000</v>
+        <v>394750000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>377330000000</v>
+        <v>363590000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>376820000000</v>
+        <v>363570000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>368420000000</v>
+        <v>359360000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>363980000000</v>
+        <v>359060000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>355460000000</v>
+        <v>355110000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>355230000000</v>
+        <v>354440000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>350290000000</v>
+        <v>344290000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>339080000000</v>
+        <v>322950000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>324770000000</v>
+        <v>320420000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>319190000000</v>
+        <v>318550000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>310620000000</v>
+        <v>306780000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,37 +1131,37 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>293510000000</v>
+        <v>295140000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>293390000000</v>
+        <v>294830000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>293240000000</v>
+        <v>293850000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>293130000000</v>
+        <v>285070000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,172 +1191,172 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>275770000000</v>
+        <v>276560000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>272760000000</v>
+        <v>268870000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>267460000000</v>
+        <v>256300000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>267410000000</v>
+        <v>255860000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>262880000000</v>
+        <v>255260000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>260690000000</v>
+        <v>254490000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>259700000000</v>
+        <v>254190000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>253640000000</v>
+        <v>251320000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>246670000000</v>
+        <v>251290000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>245160000000</v>
+        <v>250830000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>244160000000</v>
+        <v>248910000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>241660000000</v>
+        <v>242830000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>240120000000</v>
+        <v>233350000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>227120000000</v>
+        <v>230370000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>226850000000</v>
+        <v>227120000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>223470000000</v>
+        <v>223340000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>223190000000</v>
+        <v>221950000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,52 +1446,52 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>217430000000</v>
+        <v>214690000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>214240000000</v>
+        <v>207290000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>209240000000</v>
+        <v>205100000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>208890000000</v>
+        <v>202820000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>197840000000</v>
+        <v>199380000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,22 +1521,22 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>195880000000</v>
+        <v>194190000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>188860000000</v>
+        <v>190380000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,37 +1551,37 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187480000000</v>
+        <v>188190000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>183410000000</v>
+        <v>184560000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>180860000000</v>
+        <v>184330000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,37 +1596,37 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>177550000000</v>
+        <v>178180000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>175260000000</v>
+        <v>176160000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>173480000000</v>
+        <v>175360000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,52 +1641,52 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>173220000000</v>
+        <v>174470000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>166870000000</v>
+        <v>169260000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>165910000000</v>
+        <v>168640000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>164900000000</v>
+        <v>167400000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,37 +1701,37 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>163170000000</v>
+        <v>163480000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>156650000000</v>
+        <v>157950000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>156580000000</v>
+        <v>157950000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>149100000000</v>
+        <v>148460000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>147400000000</v>
+        <v>145950000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>145680000000</v>
+        <v>141530000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,37 +1791,37 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>142510000000</v>
+        <v>136290000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>136580000000</v>
+        <v>135090000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>133550000000</v>
+        <v>131900000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,22 +1836,22 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>130690000000</v>
+        <v>131540000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>129520000000</v>
+        <v>127540000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,172 +1866,172 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>129450000000</v>
+        <v>126450000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>127950000000</v>
+        <v>124040000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>127340000000</v>
+        <v>122110000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>126220000000</v>
+        <v>121360000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123810000000</v>
+        <v>121090000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120870000000</v>
+        <v>120730000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119490000000</v>
+        <v>120540000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>118980000000</v>
+        <v>120530000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118350000000</v>
+        <v>120450000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116660000000</v>
+        <v>118220000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116320000000</v>
+        <v>115940000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>115760000000</v>
+        <v>115490000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>109330000000</v>
+        <v>111080000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,157 +2061,157 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>108590000000</v>
+        <v>107870000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>105890000000</v>
+        <v>106310000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>104880000000</v>
+        <v>105650000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>101740000000</v>
+        <v>101850000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100590000000</v>
+        <v>100030000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99750000000</v>
+        <v>98270000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>99150000000</v>
+        <v>96710000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95110000000</v>
+        <v>93670000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92230000000</v>
+        <v>93240000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91960000000</v>
+        <v>92840000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>91350000000</v>
+        <v>90350000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>91120000000</v>
+        <v>87740000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88640000000</v>
+        <v>87660000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,22 +2256,22 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>87810000000</v>
+        <v>87080000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>86330000000</v>
+        <v>85790000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>84470000000</v>
+        <v>85130000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,37 +2301,37 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>83940000000</v>
+        <v>84820000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>80650000000</v>
+        <v>82960000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>80560000000</v>
+        <v>81490000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,52 +2346,52 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>77540000000</v>
+        <v>80140000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>75290000000</v>
+        <v>76520000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75260000000</v>
+        <v>73960000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74660000000</v>
+        <v>73360000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,37 +2406,37 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73710000000</v>
+        <v>72870000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72380000000</v>
+        <v>72120000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>71710000000</v>
+        <v>72000000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,157 +2451,157 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69050000000</v>
+        <v>70560000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68670000000</v>
+        <v>70420000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>68390000000</v>
+        <v>66960000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64230000000</v>
+        <v>61690000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62370000000</v>
+        <v>61390000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61630000000</v>
+        <v>60460000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56450000000</v>
+        <v>54040000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>56240000000</v>
+        <v>52430000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>54490000000</v>
+        <v>52090000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>54390000000</v>
+        <v>50950000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>52480000000</v>
+        <v>50570000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,37 +2616,37 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49150000000</v>
+        <v>49830000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48250000000</v>
+        <v>48310000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48160000000</v>
+        <v>48050000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>48050000000</v>
+        <v>47990000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>47960000000</v>
+        <v>45610000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46180000000</v>
+        <v>45570000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44830000000</v>
+        <v>45490000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,82 +2721,82 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>43250000000</v>
+        <v>41640000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42920000000</v>
+        <v>41040000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40950000000</v>
+        <v>40750000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>40770000000</v>
+        <v>38620000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>38430000000</v>
+        <v>36810000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38410000000</v>
+        <v>36280000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,22 +2811,22 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>37280000000</v>
+        <v>36000000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>36130000000</v>
+        <v>35420000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>35940000000</v>
+        <v>34920000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32210000000</v>
+        <v>32090000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30700000000</v>
+        <v>31110000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29880000000</v>
+        <v>28590000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,52 +2901,52 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28640000000</v>
+        <v>27560000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26280000000</v>
+        <v>24500000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25670000000</v>
+        <v>23790000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>24810000000</v>
+        <v>23510000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22670000000</v>
+        <v>22660000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21500000000</v>
+        <v>20290000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20050000000</v>
+        <v>19250000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19680000000</v>
+        <v>18520000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18840000000</v>
+        <v>18370000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17540000000</v>
+        <v>16810000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14070000000</v>
+        <v>12730000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13700000000</v>
+        <v>12350000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12670000000</v>
+        <v>12320000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12150000000</v>
+        <v>11870000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12150000000</v>
+        <v>11870000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10650000000</v>
+        <v>10940000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10430000000</v>
+        <v>10590000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8360000000</v>
+        <v>7940000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,22 +3171,22 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7070000000</v>
+        <v>6870000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>6930000000</v>
+        <v>6840000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,67 +3201,67 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6840000000</v>
+        <v>6800000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6790000000</v>
+        <v>6470000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6640000000</v>
+        <v>6410000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6460000000</v>
+        <v>6150000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6330000000</v>
+        <v>6130000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5970000000</v>
+        <v>6080000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5910000000</v>
+        <v>5400000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4840000000</v>
+        <v>4860000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4320000000</v>
+        <v>3980000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4270000000</v>
+        <v>3900000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,82 +3351,82 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3910000000</v>
+        <v>3580000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MARA</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>MARA Holdings Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3520000000</v>
+        <v>3390000000</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>MARA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>MARA Holdings Inc</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3460000000</v>
+        <v>3180000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2790000000</v>
+        <v>2620000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2750000000</v>
+        <v>2510000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2740000000</v>
+        <v>2450000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2320000000</v>
+        <v>2210000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2060000000</v>
+        <v>1950000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1930000000</v>
+        <v>1880000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1550000000</v>
+        <v>1430000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1250000000</v>
+        <v>1150000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1090000000</v>
+        <v>1060000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>971160000</v>
+        <v>885720000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>770570000</v>
+        <v>698610000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>349540000</v>
+        <v>317350000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5005220000000</v>
+        <v>4991210000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5333330000000</v>
+        <v>5235240000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4230910000000</v>
+        <v>4245090000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3962940000000</v>
+        <v>4005640000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2740590000000</v>
+        <v>2747920000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2230190000000</v>
+        <v>2189990000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1878890000000</v>
+        <v>1876800000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1652870000000</v>
+        <v>1643700000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1450120000000</v>
+        <v>1431470000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1137860000000</v>
+        <v>1178210000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1034270000000</v>
+        <v>1053630000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,37 +726,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1012950000000</v>
+        <v>1011950000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>931850000000</v>
+        <v>935150000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>921580000000</v>
+        <v>917830000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>891240000000</v>
+        <v>891900000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>730820000000</v>
+        <v>746350000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>727850000000</v>
+        <v>718270000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>635940000000</v>
+        <v>638810000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>611900000000</v>
+        <v>610380000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>528440000000</v>
+        <v>539900000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>500940000000</v>
+        <v>500800000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>482940000000</v>
+        <v>481810000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>448040000000</v>
+        <v>433380000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,67 +906,67 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>438700000000</v>
+        <v>433330000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>435150000000</v>
+        <v>433090000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>394890000000</v>
+        <v>406600000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>394750000000</v>
+        <v>395830000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>363590000000</v>
+        <v>365020000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>363570000000</v>
+        <v>364850000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,37 +996,37 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>359360000000</v>
+        <v>361530000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>359060000000</v>
+        <v>358210000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>355110000000</v>
+        <v>347220000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>354440000000</v>
+        <v>341250000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>344290000000</v>
+        <v>338160000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>322950000000</v>
+        <v>323720000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>320420000000</v>
+        <v>311570000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>318550000000</v>
+        <v>307530000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,52 +1116,52 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>306780000000</v>
+        <v>302880000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>295140000000</v>
+        <v>302340000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>294830000000</v>
+        <v>300990000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>293850000000</v>
+        <v>294980000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>285070000000</v>
+        <v>286000000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>276560000000</v>
+        <v>276460000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,232 +1206,232 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>268870000000</v>
+        <v>275280000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>256300000000</v>
+        <v>261440000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>255860000000</v>
+        <v>259690000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>255260000000</v>
+        <v>259520000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>254490000000</v>
+        <v>258500000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>254190000000</v>
+        <v>257530000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>251320000000</v>
+        <v>254910000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>251290000000</v>
+        <v>251960000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>250830000000</v>
+        <v>250420000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>248910000000</v>
+        <v>248390000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>242830000000</v>
+        <v>246740000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>233350000000</v>
+        <v>234650000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>230370000000</v>
+        <v>229200000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>227120000000</v>
+        <v>227670000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>223340000000</v>
+        <v>227360000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>221950000000</v>
+        <v>227290000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>214690000000</v>
+        <v>220570000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>207290000000</v>
+        <v>211960000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,52 +1476,52 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>205100000000</v>
+        <v>206680000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>202820000000</v>
+        <v>203070000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>199380000000</v>
+        <v>201590000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>194190000000</v>
+        <v>196820000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>190380000000</v>
+        <v>195130000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,67 +1551,67 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>188190000000</v>
+        <v>191110000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184560000000</v>
+        <v>190500000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184330000000</v>
+        <v>184470000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>178180000000</v>
+        <v>182100000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>176160000000</v>
+        <v>181140000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,112 +1626,112 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>175360000000</v>
+        <v>175440000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>174470000000</v>
+        <v>174950000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169260000000</v>
+        <v>171600000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>168640000000</v>
+        <v>168440000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>167400000000</v>
+        <v>164710000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>163480000000</v>
+        <v>162830000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>157950000000</v>
+        <v>162740000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>157950000000</v>
+        <v>161030000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>148460000000</v>
+        <v>151150000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>145950000000</v>
+        <v>149170000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,22 +1776,22 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>141530000000</v>
+        <v>145570000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>136290000000</v>
+        <v>137640000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>135090000000</v>
+        <v>136110000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,22 +1821,22 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>131900000000</v>
+        <v>135610000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131540000000</v>
+        <v>133430000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,142 +1851,142 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>127540000000</v>
+        <v>131230000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>126450000000</v>
+        <v>125230000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>124040000000</v>
+        <v>124580000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>122110000000</v>
+        <v>124210000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>121360000000</v>
+        <v>123730000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>121090000000</v>
+        <v>123290000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120730000000</v>
+        <v>123040000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120540000000</v>
+        <v>122930000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120530000000</v>
+        <v>122100000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120450000000</v>
+        <v>119240000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118220000000</v>
+        <v>118210000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,112 +2016,112 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>115940000000</v>
+        <v>117320000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>115490000000</v>
+        <v>113190000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>111080000000</v>
+        <v>112640000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>107870000000</v>
+        <v>110440000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>106310000000</v>
+        <v>109810000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>105650000000</v>
+        <v>109810000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>101850000000</v>
+        <v>104360000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100030000000</v>
+        <v>101430000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,97 +2136,97 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>98270000000</v>
+        <v>98300000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96710000000</v>
+        <v>97950000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93670000000</v>
+        <v>95600000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93240000000</v>
+        <v>94420000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92840000000</v>
+        <v>94140000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90350000000</v>
+        <v>93460000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>87740000000</v>
+        <v>92910000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,52 +2241,52 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>87660000000</v>
+        <v>89420000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>87080000000</v>
+        <v>89020000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>85790000000</v>
+        <v>88930000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>85130000000</v>
+        <v>88230000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,37 +2301,37 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>84820000000</v>
+        <v>85260000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>82960000000</v>
+        <v>83230000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81490000000</v>
+        <v>82680000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>80140000000</v>
+        <v>81990000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,37 +2361,37 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>76520000000</v>
+        <v>78960000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>73960000000</v>
+        <v>74890000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>73360000000</v>
+        <v>73870000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,52 +2406,52 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72870000000</v>
+        <v>73410000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72120000000</v>
+        <v>71790000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>72000000000</v>
+        <v>71160000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70560000000</v>
+        <v>71150000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>70420000000</v>
+        <v>70980000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,52 +2481,52 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>66960000000</v>
+        <v>66060000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>61690000000</v>
+        <v>63860000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61390000000</v>
+        <v>63430000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60460000000</v>
+        <v>60650000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>54040000000</v>
+        <v>55280000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>52430000000</v>
+        <v>55160000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>52090000000</v>
+        <v>52390000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,52 +2586,52 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50950000000</v>
+        <v>51740000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50570000000</v>
+        <v>51240000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49830000000</v>
+        <v>51220000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48310000000</v>
+        <v>50780000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48050000000</v>
+        <v>49090000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47990000000</v>
+        <v>48900000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45610000000</v>
+        <v>48500000000</v>
       </c>
     </row>
     <row r="147">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45570000000</v>
+        <v>47960000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45490000000</v>
+        <v>47390000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,67 +2721,67 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>41640000000</v>
+        <v>41990000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>41040000000</v>
+        <v>41810000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40750000000</v>
+        <v>40460000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38620000000</v>
+        <v>38840000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>36810000000</v>
+        <v>38700000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>36280000000</v>
+        <v>38440000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>36000000000</v>
+        <v>35940000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>35420000000</v>
+        <v>35580000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>34920000000</v>
+        <v>33060000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32090000000</v>
+        <v>32940000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>31110000000</v>
+        <v>32400000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28590000000</v>
+        <v>30660000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,37 +2901,37 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27560000000</v>
+        <v>28740000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>24500000000</v>
+        <v>25620000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23790000000</v>
+        <v>25100000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23510000000</v>
+        <v>23050000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22660000000</v>
+        <v>22970000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,22 +2976,22 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20290000000</v>
+        <v>22190000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19250000000</v>
+        <v>19490000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,22 +3006,22 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18520000000</v>
+        <v>19370000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18370000000</v>
+        <v>19220000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16810000000</v>
+        <v>17180000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>12730000000</v>
+        <v>13920000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>12350000000</v>
+        <v>12860000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12320000000</v>
+        <v>12280000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11870000000</v>
+        <v>12240000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11870000000</v>
+        <v>12240000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10940000000</v>
+        <v>11220000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10590000000</v>
+        <v>10330000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,97 +3156,97 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7940000000</v>
+        <v>8130000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>6870000000</v>
+        <v>7180000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>6840000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6800000000</v>
+        <v>7120000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6470000000</v>
+        <v>6870000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6410000000</v>
+        <v>6850000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6150000000</v>
+        <v>6320000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,22 +3261,22 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6130000000</v>
+        <v>6260000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6080000000</v>
+        <v>6170000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5400000000</v>
+        <v>5580000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,37 +3306,37 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4860000000</v>
+        <v>4980000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3980000000</v>
+        <v>4220000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3900000000</v>
+        <v>3990000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3580000000</v>
+        <v>3700000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3390000000</v>
+        <v>3550000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3180000000</v>
+        <v>3220000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2620000000</v>
+        <v>2650000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2510000000</v>
+        <v>2640000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2450000000</v>
+        <v>2600000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2210000000</v>
+        <v>2410000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1950000000</v>
+        <v>2040000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1880000000</v>
+        <v>1960000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1430000000</v>
+        <v>1550000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1150000000</v>
+        <v>1190000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1060000000</v>
+        <v>1080000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>885720000</v>
+        <v>890730000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>698610000</v>
+        <v>729750000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>317350000</v>
+        <v>338810000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4991210000000</v>
+        <v>5012520000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5235240000000</v>
+        <v>5160530000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4245090000000</v>
+        <v>4148630000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4005640000000</v>
+        <v>3928480000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2747920000000</v>
+        <v>2696580000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2189990000000</v>
+        <v>2139990000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1876800000000</v>
+        <v>1807010000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1643700000000</v>
+        <v>1569330000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1431470000000</v>
+        <v>1400980000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,37 +696,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1178210000000</v>
+        <v>1183310000000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micron Technology Inc</t>
+          <t>Berkshire Hathaway Inc</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1053630000000</v>
+        <v>1139380000000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc</t>
+          <t>Micron Technology Inc</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1011950000000</v>
+        <v>994340000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>935150000000</v>
+        <v>942610000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>917830000000</v>
+        <v>903040000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>891900000000</v>
+        <v>863170000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>746350000000</v>
+        <v>751690000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>718270000000</v>
+        <v>735950000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>638810000000</v>
+        <v>632670000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>610380000000</v>
+        <v>615870000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>539900000000</v>
+        <v>540870000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>500800000000</v>
+        <v>504370000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,37 +876,37 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>481810000000</v>
+        <v>447040000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>433380000000</v>
+        <v>444530000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>433330000000</v>
+        <v>438300000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,157 +921,157 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>433090000000</v>
+        <v>423390000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>406600000000</v>
+        <v>404010000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>395830000000</v>
+        <v>387730000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>365020000000</v>
+        <v>370120000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>364850000000</v>
+        <v>360320000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>361530000000</v>
+        <v>360080000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>358210000000</v>
+        <v>354650000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>347220000000</v>
+        <v>335910000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>341250000000</v>
+        <v>330300000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>338160000000</v>
+        <v>325620000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>323720000000</v>
+        <v>324810000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>311570000000</v>
+        <v>319830000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>307530000000</v>
+        <v>308910000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>302880000000</v>
+        <v>303780000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>302340000000</v>
+        <v>293680000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,82 +1146,82 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>300990000000</v>
+        <v>287200000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>294980000000</v>
+        <v>283600000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>286000000000</v>
+        <v>279760000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>276460000000</v>
+        <v>275720000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>275280000000</v>
+        <v>271440000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>261440000000</v>
+        <v>261360000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>259690000000</v>
+        <v>258880000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>259520000000</v>
+        <v>256600000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>258500000000</v>
+        <v>256530000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>257530000000</v>
+        <v>255130000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,157 +1296,157 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>254910000000</v>
+        <v>252490000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>251960000000</v>
+        <v>251750000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>250420000000</v>
+        <v>245350000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>248390000000</v>
+        <v>243290000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>246740000000</v>
+        <v>233820000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>234650000000</v>
+        <v>232830000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>229200000000</v>
+        <v>230450000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>227670000000</v>
+        <v>229770000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>227360000000</v>
+        <v>218710000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>227290000000</v>
+        <v>218110000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>220570000000</v>
+        <v>216290000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>211960000000</v>
+        <v>211770000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,127 +1476,127 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>206680000000</v>
+        <v>208440000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>203070000000</v>
+        <v>203160000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>201590000000</v>
+        <v>198100000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>196820000000</v>
+        <v>193670000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>195130000000</v>
+        <v>190950000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>191110000000</v>
+        <v>187780000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>190500000000</v>
+        <v>186090000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184470000000</v>
+        <v>184310000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182100000000</v>
+        <v>183790000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>181140000000</v>
+        <v>181500000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>175440000000</v>
+        <v>179190000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>174950000000</v>
+        <v>173060000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>171600000000</v>
+        <v>171940000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>168440000000</v>
+        <v>170660000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,52 +1686,52 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>164710000000</v>
+        <v>166460000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>162830000000</v>
+        <v>161010000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>162740000000</v>
+        <v>160620000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>161030000000</v>
+        <v>159030000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>151150000000</v>
+        <v>150740000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>149170000000</v>
+        <v>150340000000</v>
       </c>
     </row>
     <row r="86">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>145570000000</v>
+        <v>143690000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>137640000000</v>
+        <v>140550000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>136110000000</v>
+        <v>138810000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,142 +1821,142 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>135610000000</v>
+        <v>132390000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>133430000000</v>
+        <v>129920000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>131230000000</v>
+        <v>127420000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>125230000000</v>
+        <v>126960000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>124580000000</v>
+        <v>126660000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>124210000000</v>
+        <v>125410000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>123730000000</v>
+        <v>124280000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123290000000</v>
+        <v>122810000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123040000000</v>
+        <v>122050000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>122930000000</v>
+        <v>121890000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,127 +1971,127 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>122100000000</v>
+        <v>121200000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>119240000000</v>
+        <v>115250000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118210000000</v>
+        <v>114480000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117320000000</v>
+        <v>113700000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>113190000000</v>
+        <v>111170000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>112640000000</v>
+        <v>110740000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>110440000000</v>
+        <v>109210000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>109810000000</v>
+        <v>108250000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>109810000000</v>
+        <v>105510000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>104360000000</v>
+        <v>104010000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>101430000000</v>
+        <v>99340000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>98300000000</v>
+        <v>97290000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,127 +2151,127 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>97950000000</v>
+        <v>95430000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95600000000</v>
+        <v>92980000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94420000000</v>
+        <v>92880000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>94140000000</v>
+        <v>91500000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>93460000000</v>
+        <v>90700000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>92910000000</v>
+        <v>89880000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>89420000000</v>
+        <v>89060000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>89020000000</v>
+        <v>88730000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>88930000000</v>
+        <v>87040000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>88230000000</v>
+        <v>86890000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>85260000000</v>
+        <v>84970000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,127 +2316,127 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>83230000000</v>
+        <v>82930000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>82680000000</v>
+        <v>81410000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>81990000000</v>
+        <v>79880000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>78960000000</v>
+        <v>79470000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>74890000000</v>
+        <v>75020000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>73870000000</v>
+        <v>74270000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73410000000</v>
+        <v>73850000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>71790000000</v>
+        <v>73670000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>71160000000</v>
+        <v>73470000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,22 +2451,22 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>71150000000</v>
+        <v>70330000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>70980000000</v>
+        <v>70080000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,367 +2481,367 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>66060000000</v>
+        <v>65420000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63860000000</v>
+        <v>63310000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>63430000000</v>
+        <v>62360000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60650000000</v>
+        <v>57750000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55280000000</v>
+        <v>55150000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>55160000000</v>
+        <v>53160000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>52390000000</v>
+        <v>51020000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>51740000000</v>
+        <v>50140000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>51240000000</v>
+        <v>49920000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>51220000000</v>
+        <v>49590000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>50780000000</v>
+        <v>49570000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>49090000000</v>
+        <v>48500000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>48900000000</v>
+        <v>46800000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>48500000000</v>
+        <v>45990000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>47960000000</v>
+        <v>45690000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>47390000000</v>
+        <v>44980000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>41990000000</v>
+        <v>41370000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>41810000000</v>
+        <v>39640000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40460000000</v>
+        <v>37880000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38840000000</v>
+        <v>37820000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>38700000000</v>
+        <v>37530000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38440000000</v>
+        <v>34830000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35940000000</v>
+        <v>33860000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>35580000000</v>
+        <v>33810000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>33060000000</v>
+        <v>32800000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,22 +2856,22 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32940000000</v>
+        <v>32480000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>32400000000</v>
+        <v>30430000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>30660000000</v>
+        <v>30040000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,112 +2901,112 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28740000000</v>
+        <v>27480000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25620000000</v>
+        <v>25290000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>25100000000</v>
+        <v>24970000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23050000000</v>
+        <v>22950000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22970000000</v>
+        <v>20980000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22190000000</v>
+        <v>20780000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19490000000</v>
+        <v>19390000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19370000000</v>
+        <v>18790000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>19220000000</v>
+        <v>18550000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>17180000000</v>
+        <v>16810000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13920000000</v>
+        <v>12670000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>12860000000</v>
+        <v>12410000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>12280000000</v>
+        <v>11990000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,37 +3096,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>12240000000</v>
+        <v>11990000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>12240000000</v>
+        <v>11050000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>11220000000</v>
+        <v>10910000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10330000000</v>
+        <v>9840000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8130000000</v>
+        <v>7510000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,52 +3171,52 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7180000000</v>
+        <v>7190000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7130000000</v>
+        <v>7140000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7120000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6870000000</v>
+        <v>6970000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,37 +3231,37 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6850000000</v>
+        <v>6550000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6320000000</v>
+        <v>6190000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6260000000</v>
+        <v>6140000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6170000000</v>
+        <v>5460000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5580000000</v>
+        <v>5200000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4980000000</v>
+        <v>4760000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4220000000</v>
+        <v>3940000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3990000000</v>
+        <v>3580000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3700000000</v>
+        <v>3520000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3550000000</v>
+        <v>3420000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,37 +3381,37 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3220000000</v>
+        <v>2910000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2650000000</v>
+        <v>2510000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2640000000</v>
+        <v>2450000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2600000000</v>
+        <v>2350000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2410000000</v>
+        <v>2290000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2040000000</v>
+        <v>2000000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1960000000</v>
+        <v>1820000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1550000000</v>
+        <v>1440000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1190000000</v>
+        <v>1070000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1080000000</v>
+        <v>1030000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>890730000</v>
+        <v>814790000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>729750000</v>
+        <v>691630000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>338810000</v>
+        <v>328080000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4148630000000</v>
+        <v>4145080000000</v>
       </c>
     </row>
     <row r="8">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1139380000000</v>
+        <v>1138890000000</v>
       </c>
     </row>
     <row r="16">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>140550000000</v>
+        <v>140620000000</v>
       </c>
     </row>
     <row r="88">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4145080000000</v>
+        <v>4120410000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3928480000000</v>
+        <v>3928490000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2696580000000</v>
+        <v>2696570000000</v>
       </c>
     </row>
     <row r="10">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1183310000000</v>
+        <v>1183320000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1138890000000</v>
+        <v>1138910000000</v>
       </c>
     </row>
     <row r="16">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>354650000000</v>
+        <v>358240000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>335910000000</v>
+        <v>335920000000</v>
       </c>
     </row>
     <row r="37">
@@ -1287,31 +1287,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>252490000000</v>
+        <v>253620000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>251750000000</v>
+        <v>252500000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>245350000000</v>
+        <v>245340000000</v>
       </c>
     </row>
     <row r="57">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187780000000</v>
+        <v>187790000000</v>
       </c>
     </row>
     <row r="72">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>140620000000</v>
+        <v>140550000000</v>
       </c>
     </row>
     <row r="88">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124280000000</v>
+        <v>124270000000</v>
       </c>
     </row>
     <row r="96">
@@ -1947,31 +1947,31 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121890000000</v>
+        <v>121200000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>121200000000</v>
+        <v>119500000000</v>
       </c>
     </row>
     <row r="100">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>104010000000</v>
+        <v>102410000000</v>
       </c>
     </row>
     <row r="109">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>84970000000</v>
+        <v>84960000000</v>
       </c>
     </row>
     <row r="122">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>73470000000</v>
+        <v>73460000000</v>
       </c>
     </row>
     <row r="131">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33810000000</v>
+        <v>33820000000</v>
       </c>
     </row>
     <row r="157">
@@ -2982,91 +2982,91 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19390000000</v>
+        <v>18790000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18790000000</v>
+        <v>18550000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18550000000</v>
+        <v>17680000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>16810000000</v>
+        <v>12670000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>12670000000</v>
+        <v>12410000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>12410000000</v>
+        <v>11990000000</v>
       </c>
     </row>
     <row r="173">
@@ -3087,61 +3087,61 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11990000000</v>
+        <v>11050000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11050000000</v>
+        <v>10620000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10910000000</v>
+        <v>9840000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9840000000</v>
+        <v>9380000000</v>
       </c>
     </row>
     <row r="178">
@@ -3162,106 +3162,106 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7190000000</v>
+        <v>7140000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7140000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7130000000</v>
+        <v>6930000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6970000000</v>
+        <v>6550000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6550000000</v>
+        <v>6190000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6190000000</v>
+        <v>6140000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6140000000</v>
+        <v>5680000000</v>
       </c>
     </row>
     <row r="186">
@@ -3387,31 +3387,31 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2510000000</v>
+        <v>2450000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2450000000</v>
+        <v>2390000000</v>
       </c>
     </row>
     <row r="196">
@@ -3492,31 +3492,31 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>TDOC</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Teladoc Health Inc</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1070000000</v>
+        <v>1030000000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TDOC</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Teladoc Health Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1030000000</v>
+        <v>830330000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>814790000</v>
+        <v>814850000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>691630000</v>
+        <v>691660000</v>
       </c>
     </row>
     <row r="205">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5012520000000</v>
+        <v>5004930000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5160530000000</v>
+        <v>5231870000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4120410000000</v>
+        <v>4160160000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3928490000000</v>
+        <v>3961680000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2696570000000</v>
+        <v>2830860000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2139990000000</v>
+        <v>2179460000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1807010000000</v>
+        <v>1797120000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1569330000000</v>
+        <v>1597210000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1400980000000</v>
+        <v>1453670000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1183320000000</v>
+        <v>1167610000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1138910000000</v>
+        <v>1139360000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>994340000000</v>
+        <v>1023820000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>942610000000</v>
+        <v>941740000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>903040000000</v>
+        <v>886590000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>863170000000</v>
+        <v>878360000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>751690000000</v>
+        <v>752270000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>735950000000</v>
+        <v>733070000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>632670000000</v>
+        <v>634830000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>615870000000</v>
+        <v>611610000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>540870000000</v>
+        <v>539970000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>504370000000</v>
+        <v>499530000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>447040000000</v>
+        <v>466550000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>444530000000</v>
+        <v>443300000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>438300000000</v>
+        <v>441150000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>423390000000</v>
+        <v>419890000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>404010000000</v>
+        <v>401940000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>387730000000</v>
+        <v>391850000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>370120000000</v>
+        <v>366260000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>360320000000</v>
+        <v>365220000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>360080000000</v>
+        <v>354360000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,67 +1011,67 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>358240000000</v>
+        <v>352360000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>335920000000</v>
+        <v>340640000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>330300000000</v>
+        <v>333630000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>325620000000</v>
+        <v>327840000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>324810000000</v>
+        <v>322970000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>319830000000</v>
+        <v>313360000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>308910000000</v>
+        <v>309160000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>303780000000</v>
+        <v>298540000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>293680000000</v>
+        <v>290850000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,37 +1146,37 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>287200000000</v>
+        <v>289570000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>283600000000</v>
+        <v>283810000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>279760000000</v>
+        <v>280300000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>275720000000</v>
+        <v>274950000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,37 +1206,37 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>271440000000</v>
+        <v>270100000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>261360000000</v>
+        <v>260880000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>258880000000</v>
+        <v>258920000000</v>
       </c>
     </row>
     <row r="51">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>256600000000</v>
+        <v>255000000000</v>
       </c>
     </row>
     <row r="52">
@@ -1266,112 +1266,112 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>256530000000</v>
+        <v>254270000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>255130000000</v>
+        <v>252190000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>253620000000</v>
+        <v>251200000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>252500000000</v>
+        <v>247360000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>245340000000</v>
+        <v>243560000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>243290000000</v>
+        <v>241940000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>233820000000</v>
+        <v>233560000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>232830000000</v>
+        <v>232080000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,22 +1386,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>230450000000</v>
+        <v>229800000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>229770000000</v>
+        <v>229740000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>218710000000</v>
+        <v>222710000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>218110000000</v>
+        <v>220090000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>216290000000</v>
+        <v>217150000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>211770000000</v>
+        <v>213670000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>208440000000</v>
+        <v>204130000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>203160000000</v>
+        <v>200070000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,157 +1506,157 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>198100000000</v>
+        <v>199540000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>193670000000</v>
+        <v>198170000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>190950000000</v>
+        <v>189800000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187790000000</v>
+        <v>189230000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>186090000000</v>
+        <v>185300000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184310000000</v>
+        <v>183430000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>183790000000</v>
+        <v>182730000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>181500000000</v>
+        <v>182020000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>179190000000</v>
+        <v>180060000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>173060000000</v>
+        <v>171720000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>171940000000</v>
+        <v>169050000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>170660000000</v>
+        <v>167430000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,37 +1686,37 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166460000000</v>
+        <v>163060000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161010000000</v>
+        <v>158980000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>160620000000</v>
+        <v>157770000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>159030000000</v>
+        <v>154910000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>150740000000</v>
+        <v>153030000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,37 +1761,37 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>150340000000</v>
+        <v>151290000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>143690000000</v>
+        <v>144990000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>140550000000</v>
+        <v>142900000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>138810000000</v>
+        <v>137450000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,37 +1821,37 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>132390000000</v>
+        <v>132990000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>129920000000</v>
+        <v>131840000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>127420000000</v>
+        <v>128550000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,52 +1866,52 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>126960000000</v>
+        <v>127320000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>126660000000</v>
+        <v>126530000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>125410000000</v>
+        <v>126120000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124270000000</v>
+        <v>123710000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>122810000000</v>
+        <v>122170000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122050000000</v>
+        <v>120170000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121200000000</v>
+        <v>118670000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119500000000</v>
+        <v>117930000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,37 +1986,37 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>115250000000</v>
+        <v>115850000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>114480000000</v>
+        <v>114340000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113700000000</v>
+        <v>113740000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,52 +2031,52 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>111170000000</v>
+        <v>111570000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>110740000000</v>
+        <v>111260000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>109210000000</v>
+        <v>109920000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>108250000000</v>
+        <v>106800000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>105510000000</v>
+        <v>105960000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>102410000000</v>
+        <v>103450000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99340000000</v>
+        <v>98480000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>97290000000</v>
+        <v>96270000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,22 +2151,22 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>95430000000</v>
+        <v>96170000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>92980000000</v>
+        <v>93490000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,52 +2181,52 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>92880000000</v>
+        <v>93300000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91500000000</v>
+        <v>93270000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90700000000</v>
+        <v>90580000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89880000000</v>
+        <v>90130000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,37 +2241,37 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>89060000000</v>
+        <v>90060000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>88730000000</v>
+        <v>89630000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87040000000</v>
+        <v>88920000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>86890000000</v>
+        <v>87020000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>84960000000</v>
+        <v>83550000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>82930000000</v>
+        <v>82920000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,82 +2331,82 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81410000000</v>
+        <v>80510000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>79880000000</v>
+        <v>79340000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>79470000000</v>
+        <v>78880000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75020000000</v>
+        <v>75410000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74270000000</v>
+        <v>74450000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>73850000000</v>
+        <v>72860000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,22 +2421,22 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73670000000</v>
+        <v>72610000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>73460000000</v>
+        <v>72540000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70330000000</v>
+        <v>70090000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>70080000000</v>
+        <v>69640000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65420000000</v>
+        <v>65520000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63310000000</v>
+        <v>62790000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62360000000</v>
+        <v>62700000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>57750000000</v>
+        <v>57410000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,67 +2541,67 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55150000000</v>
+        <v>55270000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>53160000000</v>
+        <v>50310000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>51020000000</v>
+        <v>50270000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50140000000</v>
+        <v>50240000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49920000000</v>
+        <v>50160000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49590000000</v>
+        <v>49720000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>49570000000</v>
+        <v>48570000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,67 +2646,67 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48500000000</v>
+        <v>48340000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46800000000</v>
+        <v>47040000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45990000000</v>
+        <v>46560000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45690000000</v>
+        <v>46280000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44980000000</v>
+        <v>44440000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>41370000000</v>
+        <v>40970000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,52 +2736,52 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>39640000000</v>
+        <v>39660000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>37880000000</v>
+        <v>39510000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>37820000000</v>
+        <v>38330000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>37530000000</v>
+        <v>37770000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,37 +2796,37 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>34830000000</v>
+        <v>35560000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>33860000000</v>
+        <v>34660000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33820000000</v>
+        <v>33710000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32800000000</v>
+        <v>32890000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32480000000</v>
+        <v>32210000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30430000000</v>
+        <v>30740000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>30040000000</v>
+        <v>29850000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27480000000</v>
+        <v>28470000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25290000000</v>
+        <v>25360000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24970000000</v>
+        <v>24560000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>22950000000</v>
+        <v>23100000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>20980000000</v>
+        <v>21090000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20780000000</v>
+        <v>20760000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>18790000000</v>
+        <v>18470000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18550000000</v>
+        <v>18460000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17680000000</v>
+        <v>17430000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>12670000000</v>
+        <v>13220000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>12410000000</v>
+        <v>12650000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>11990000000</v>
+        <v>11710000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11990000000</v>
+        <v>11710000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11050000000</v>
+        <v>11180000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10620000000</v>
+        <v>10910000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>9840000000</v>
+        <v>10040000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9380000000</v>
+        <v>9810000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,37 +3156,37 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7510000000</v>
+        <v>7560000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7140000000</v>
+        <v>7520000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7130000000</v>
+        <v>7160000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6930000000</v>
+        <v>6920000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,37 +3216,37 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6550000000</v>
+        <v>6570000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6190000000</v>
+        <v>6110000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6140000000</v>
+        <v>5990000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5680000000</v>
+        <v>5910000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5460000000</v>
+        <v>5820000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5200000000</v>
+        <v>5070000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4760000000</v>
+        <v>4840000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3940000000</v>
+        <v>3900000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3580000000</v>
+        <v>3660000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3520000000</v>
+        <v>3530000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3420000000</v>
+        <v>3340000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2910000000</v>
+        <v>2850000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2450000000</v>
+        <v>2480000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,37 +3411,37 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2390000000</v>
+        <v>2340000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2350000000</v>
+        <v>2260000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2290000000</v>
+        <v>2250000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2000000000</v>
+        <v>1970000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1820000000</v>
+        <v>1810000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1440000000</v>
+        <v>1450000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1030000000</v>
+        <v>1040000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>830330000</v>
+        <v>838920000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>814850000</v>
+        <v>819340000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>691660000</v>
+        <v>698640000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>328080000</v>
+        <v>315050000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5004930000000</v>
+        <v>4954720000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5231870000000</v>
+        <v>5216930000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4160160000000</v>
+        <v>4140820000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3961680000000</v>
+        <v>3949420000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2830860000000</v>
+        <v>2832810000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2179460000000</v>
+        <v>2204670000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1797120000000</v>
+        <v>1768610000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1597210000000</v>
+        <v>1596160000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1453670000000</v>
+        <v>1477170000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1167610000000</v>
+        <v>1208380000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1139360000000</v>
+        <v>1155770000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1023820000000</v>
+        <v>1013830000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>941740000000</v>
+        <v>934990000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>886590000000</v>
+        <v>891180000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>878360000000</v>
+        <v>872950000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>752270000000</v>
+        <v>759090000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>733070000000</v>
+        <v>731340000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>634830000000</v>
+        <v>628560000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>611610000000</v>
+        <v>625030000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>539970000000</v>
+        <v>543490000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>499530000000</v>
+        <v>510840000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>466550000000</v>
+        <v>462830000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>443300000000</v>
+        <v>445950000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>441150000000</v>
+        <v>440740000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>419890000000</v>
+        <v>420710000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>401940000000</v>
+        <v>402250000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>391850000000</v>
+        <v>396530000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>366260000000</v>
+        <v>376330000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>365220000000</v>
+        <v>370050000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>354360000000</v>
+        <v>365880000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,37 +1011,37 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>352360000000</v>
+        <v>350570000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>340640000000</v>
+        <v>333370000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>333630000000</v>
+        <v>329690000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,22 +1056,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>327840000000</v>
+        <v>321390000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>322970000000</v>
+        <v>314380000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,22 +1086,22 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>313360000000</v>
+        <v>311570000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>309160000000</v>
+        <v>311130000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,82 +1116,82 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>298540000000</v>
+        <v>300590000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>290850000000</v>
+        <v>293470000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>289570000000</v>
+        <v>286020000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>283810000000</v>
+        <v>283330000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>280300000000</v>
+        <v>281250000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>274950000000</v>
+        <v>278350000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>270100000000</v>
+        <v>270190000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,82 +1221,82 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>260880000000</v>
+        <v>264290000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>258920000000</v>
+        <v>261820000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>255000000000</v>
+        <v>260580000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>254270000000</v>
+        <v>257630000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>252190000000</v>
+        <v>254150000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>251200000000</v>
+        <v>253680000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,22 +1311,22 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>247360000000</v>
+        <v>246730000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>243560000000</v>
+        <v>237310000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,37 +1341,37 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>241940000000</v>
+        <v>237120000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>233560000000</v>
+        <v>236090000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>232080000000</v>
+        <v>232810000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,22 +1386,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>229800000000</v>
+        <v>232730000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>229740000000</v>
+        <v>231360000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>222710000000</v>
+        <v>227920000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,37 +1431,37 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>220090000000</v>
+        <v>223210000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>217150000000</v>
+        <v>214980000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>213670000000</v>
+        <v>211070000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>204130000000</v>
+        <v>205500000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>200070000000</v>
+        <v>200360000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>199540000000</v>
+        <v>199520000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>198170000000</v>
+        <v>197340000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>189800000000</v>
+        <v>194070000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>189230000000</v>
+        <v>192820000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,7 +1566,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>185300000000</v>
+        <v>187630000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>183430000000</v>
+        <v>185050000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182730000000</v>
+        <v>183380000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>182020000000</v>
+        <v>182630000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>180060000000</v>
+        <v>177280000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>171720000000</v>
+        <v>174450000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>169050000000</v>
+        <v>170460000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>167430000000</v>
+        <v>169210000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163060000000</v>
+        <v>164500000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,82 +1701,82 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>158980000000</v>
+        <v>160480000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>157770000000</v>
+        <v>159980000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>154910000000</v>
+        <v>157640000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>153030000000</v>
+        <v>157180000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>151290000000</v>
+        <v>154740000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>144990000000</v>
+        <v>150540000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>142900000000</v>
+        <v>140810000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>137450000000</v>
+        <v>138020000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>132990000000</v>
+        <v>137020000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>131840000000</v>
+        <v>136370000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,127 +1851,127 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>128550000000</v>
+        <v>131660000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>127320000000</v>
+        <v>129160000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>126530000000</v>
+        <v>128960000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126120000000</v>
+        <v>126640000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>123710000000</v>
+        <v>125990000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>122170000000</v>
+        <v>124630000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>120170000000</v>
+        <v>123550000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>118670000000</v>
+        <v>123170000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>117930000000</v>
+        <v>121050000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,37 +1986,37 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>115850000000</v>
+        <v>116190000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>114340000000</v>
+        <v>116000000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113740000000</v>
+        <v>113930000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>111570000000</v>
+        <v>113280000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>111260000000</v>
+        <v>112760000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>109920000000</v>
+        <v>111390000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,37 +2076,37 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>106800000000</v>
+        <v>108310000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>105960000000</v>
+        <v>105950000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103450000000</v>
+        <v>103860000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,52 +2121,52 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>98480000000</v>
+        <v>100840000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>96270000000</v>
+        <v>99920000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96170000000</v>
+        <v>97430000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>93490000000</v>
+        <v>96650000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93300000000</v>
+        <v>95460000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,22 +2196,22 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93270000000</v>
+        <v>95280000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90580000000</v>
+        <v>92080000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>90130000000</v>
+        <v>92070000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>90060000000</v>
+        <v>91180000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,37 +2256,37 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>89630000000</v>
+        <v>90950000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>88920000000</v>
+        <v>89600000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>87020000000</v>
+        <v>89020000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>83550000000</v>
+        <v>88380000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>82920000000</v>
+        <v>83820000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>80510000000</v>
+        <v>83130000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>79340000000</v>
+        <v>81020000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>78880000000</v>
+        <v>78370000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,97 +2376,97 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>75410000000</v>
+        <v>76980000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74450000000</v>
+        <v>75860000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>72860000000</v>
+        <v>75360000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>72610000000</v>
+        <v>74180000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>72540000000</v>
+        <v>72890000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70090000000</v>
+        <v>69960000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>69640000000</v>
+        <v>67640000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65520000000</v>
+        <v>65680000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62790000000</v>
+        <v>63750000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62700000000</v>
+        <v>62900000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>57410000000</v>
+        <v>60240000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55270000000</v>
+        <v>56260000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>50310000000</v>
+        <v>51330000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>50270000000</v>
+        <v>50890000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,112 +2586,112 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50240000000</v>
+        <v>50450000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50160000000</v>
+        <v>49410000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49720000000</v>
+        <v>49160000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48570000000</v>
+        <v>48880000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48340000000</v>
+        <v>48450000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47040000000</v>
+        <v>46920000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46560000000</v>
+        <v>46610000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46280000000</v>
+        <v>45600000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44440000000</v>
+        <v>45080000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>40970000000</v>
+        <v>43020000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>39660000000</v>
+        <v>40460000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39510000000</v>
+        <v>39730000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38330000000</v>
+        <v>38450000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>37770000000</v>
+        <v>37520000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>35560000000</v>
+        <v>36390000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34660000000</v>
+        <v>34980000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33710000000</v>
+        <v>34270000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32890000000</v>
+        <v>33070000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32210000000</v>
+        <v>32180000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30740000000</v>
+        <v>30460000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29850000000</v>
+        <v>29950000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28470000000</v>
+        <v>28440000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25360000000</v>
+        <v>25660000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24560000000</v>
+        <v>24920000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,127 +2946,127 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23100000000</v>
+        <v>23400000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21090000000</v>
+        <v>21910000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20760000000</v>
+        <v>21330000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>18470000000</v>
+        <v>19380000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18460000000</v>
+        <v>18960000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17430000000</v>
+        <v>18750000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>13220000000</v>
+        <v>18220000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>12650000000</v>
+        <v>13420000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>11710000000</v>
+        <v>13010000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,112 +3081,112 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11710000000</v>
+        <v>11790000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11180000000</v>
+        <v>11790000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10910000000</v>
+        <v>11110000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Oscar Health Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10040000000</v>
+        <v>10760000000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Oscar Health Inc</t>
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9810000000</v>
+        <v>10390000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7560000000</v>
+        <v>7660000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7520000000</v>
+        <v>7660000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7160000000</v>
+        <v>7580000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,67 +3201,67 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6920000000</v>
+        <v>7300000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6570000000</v>
+        <v>7240000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6110000000</v>
+        <v>6820000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>5990000000</v>
+        <v>6210000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5910000000</v>
+        <v>5980000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5820000000</v>
+        <v>5850000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5070000000</v>
+        <v>5110000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4840000000</v>
+        <v>4820000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,37 +3321,37 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3900000000</v>
+        <v>3890000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3660000000</v>
+        <v>3550000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3530000000</v>
+        <v>3520000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3340000000</v>
+        <v>3510000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2850000000</v>
+        <v>2890000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2480000000</v>
+        <v>2590000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2340000000</v>
+        <v>2400000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2260000000</v>
+        <v>2300000000</v>
       </c>
     </row>
     <row r="197">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1970000000</v>
+        <v>2010000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1810000000</v>
+        <v>1880000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1450000000</v>
+        <v>1470000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1040000000</v>
+        <v>1130000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>838920000</v>
+        <v>1090000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>819340000</v>
+        <v>818290000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>698640000</v>
+        <v>695930000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>315050000</v>
+        <v>311220000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4954720000000</v>
+        <v>5020250000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5216930000000</v>
+        <v>5349480000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4140820000000</v>
+        <v>4073070000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3949420000000</v>
+        <v>3957440000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2832810000000</v>
+        <v>2830010000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2204670000000</v>
+        <v>2239990000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1768610000000</v>
+        <v>1776940000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1596160000000</v>
+        <v>1612530000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1477170000000</v>
+        <v>1527610000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1208380000000</v>
+        <v>1196230000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1155770000000</v>
+        <v>1153740000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1013830000000</v>
+        <v>1033750000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>934990000000</v>
+        <v>934600000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>891180000000</v>
+        <v>902300000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>872950000000</v>
+        <v>891000000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>759090000000</v>
+        <v>761480000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>731340000000</v>
+        <v>732290000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>628560000000</v>
+        <v>646230000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>625030000000</v>
+        <v>621220000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>543490000000</v>
+        <v>545420000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>510840000000</v>
+        <v>503270000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>462830000000</v>
+        <v>484740000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>445950000000</v>
+        <v>448070000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>440740000000</v>
+        <v>442380000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>420710000000</v>
+        <v>422880000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>402250000000</v>
+        <v>398760000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>396530000000</v>
+        <v>390460000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,37 +966,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>376330000000</v>
+        <v>374300000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>370050000000</v>
+        <v>369780000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>365880000000</v>
+        <v>364290000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>350570000000</v>
+        <v>351530000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>333370000000</v>
+        <v>340260000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,7 +1041,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>329690000000</v>
+        <v>326380000000</v>
       </c>
     </row>
     <row r="38">
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>321390000000</v>
+        <v>324530000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,97 +1071,97 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>314380000000</v>
+        <v>313410000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>311570000000</v>
+        <v>308930000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>311130000000</v>
+        <v>307760000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>300590000000</v>
+        <v>306990000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>293470000000</v>
+        <v>300080000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>286020000000</v>
+        <v>293710000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>283330000000</v>
+        <v>284050000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,52 +1176,52 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>281250000000</v>
+        <v>281780000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>278350000000</v>
+        <v>270820000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>270190000000</v>
+        <v>268620000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>264290000000</v>
+        <v>263430000000</v>
       </c>
     </row>
     <row r="50">
@@ -1236,67 +1236,67 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>261820000000</v>
+        <v>261250000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>260580000000</v>
+        <v>259960000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>257630000000</v>
+        <v>259750000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>254150000000</v>
+        <v>258230000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>253680000000</v>
+        <v>256610000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,37 +1311,37 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>246730000000</v>
+        <v>247400000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>237310000000</v>
+        <v>246600000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>237120000000</v>
+        <v>245070000000</v>
       </c>
     </row>
     <row r="58">
@@ -1356,37 +1356,37 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>236090000000</v>
+        <v>242000000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>232810000000</v>
+        <v>236980000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>232730000000</v>
+        <v>236910000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>231360000000</v>
+        <v>230750000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>227920000000</v>
+        <v>230750000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>223210000000</v>
+        <v>224250000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>214980000000</v>
+        <v>218540000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>211070000000</v>
+        <v>213280000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>205500000000</v>
+        <v>207750000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,67 +1491,67 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>200360000000</v>
+        <v>200930000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>199520000000</v>
+        <v>199190000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>197340000000</v>
+        <v>198980000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>194070000000</v>
+        <v>193100000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>192820000000</v>
+        <v>190420000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,82 +1566,82 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>187630000000</v>
+        <v>190030000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>185050000000</v>
+        <v>186780000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>183380000000</v>
+        <v>183560000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>182630000000</v>
+        <v>180980000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>177280000000</v>
+        <v>174260000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>174450000000</v>
+        <v>173920000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>170460000000</v>
+        <v>171630000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,172 +1671,172 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>169210000000</v>
+        <v>164920000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>164500000000</v>
+        <v>164400000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>160480000000</v>
+        <v>163290000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>159980000000</v>
+        <v>158480000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>157640000000</v>
+        <v>151970000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>157180000000</v>
+        <v>151250000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>154740000000</v>
+        <v>150140000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>150540000000</v>
+        <v>142000000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>140810000000</v>
+        <v>141690000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>138020000000</v>
+        <v>138120000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137020000000</v>
+        <v>136940000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>136370000000</v>
+        <v>136070000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>131660000000</v>
+        <v>130690000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>129160000000</v>
+        <v>130640000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128960000000</v>
+        <v>128630000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>126640000000</v>
+        <v>127280000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,37 +1911,37 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>125990000000</v>
+        <v>124850000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>124630000000</v>
+        <v>123680000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123550000000</v>
+        <v>123280000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>123170000000</v>
+        <v>119000000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,52 +1971,52 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>121050000000</v>
+        <v>119000000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>116190000000</v>
+        <v>116700000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116000000000</v>
+        <v>116220000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113930000000</v>
+        <v>113860000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,22 +2031,22 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>113280000000</v>
+        <v>112950000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>112760000000</v>
+        <v>112050000000</v>
       </c>
     </row>
     <row r="105">
@@ -2061,52 +2061,52 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>111390000000</v>
+        <v>110280000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>108310000000</v>
+        <v>109390000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>105950000000</v>
+        <v>108160000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103860000000</v>
+        <v>104000000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100840000000</v>
+        <v>99460000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99920000000</v>
+        <v>99270000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>97430000000</v>
+        <v>98180000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,52 +2166,52 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>96650000000</v>
+        <v>98140000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>95460000000</v>
+        <v>98060000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>95280000000</v>
+        <v>94150000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92080000000</v>
+        <v>94040000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>92070000000</v>
+        <v>92000000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>91180000000</v>
+        <v>90610000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>90950000000</v>
+        <v>90120000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,37 +2271,37 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>89600000000</v>
+        <v>89690000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>89020000000</v>
+        <v>89650000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>88380000000</v>
+        <v>88530000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>83820000000</v>
+        <v>84710000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,37 +2331,37 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>83130000000</v>
+        <v>82950000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>81020000000</v>
+        <v>81680000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>78370000000</v>
+        <v>80430000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,7 +2376,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>76980000000</v>
+        <v>77150000000</v>
       </c>
     </row>
     <row r="127">
@@ -2391,37 +2391,37 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>75860000000</v>
+        <v>76620000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>75360000000</v>
+        <v>75840000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>74180000000</v>
+        <v>74460000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,7 +2436,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>72890000000</v>
+        <v>72700000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69960000000</v>
+        <v>69230000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67640000000</v>
+        <v>66780000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,52 +2481,52 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65680000000</v>
+        <v>65960000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63750000000</v>
+        <v>64780000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62900000000</v>
+        <v>63270000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>60240000000</v>
+        <v>62680000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,52 +2541,52 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56260000000</v>
+        <v>55740000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>51330000000</v>
+        <v>52410000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>50890000000</v>
+        <v>51170000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50450000000</v>
+        <v>50950000000</v>
       </c>
     </row>
     <row r="141">
@@ -2601,37 +2601,37 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49410000000</v>
+        <v>50320000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49160000000</v>
+        <v>48930000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48880000000</v>
+        <v>48910000000</v>
       </c>
     </row>
     <row r="144">
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>48450000000</v>
+        <v>47450000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,52 +2661,52 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46920000000</v>
+        <v>46990000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46610000000</v>
+        <v>46720000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>45600000000</v>
+        <v>46640000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>45080000000</v>
+        <v>44190000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>43020000000</v>
+        <v>43940000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>40460000000</v>
+        <v>42710000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39730000000</v>
+        <v>40960000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38450000000</v>
+        <v>37720000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>37520000000</v>
+        <v>37560000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,22 +2796,22 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>36390000000</v>
+        <v>36710000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34980000000</v>
+        <v>35580000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34270000000</v>
+        <v>34100000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,37 +2841,37 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>33070000000</v>
+        <v>32900000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32180000000</v>
+        <v>32120000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30460000000</v>
+        <v>31020000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29950000000</v>
+        <v>29490000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28440000000</v>
+        <v>29010000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25660000000</v>
+        <v>25640000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24920000000</v>
+        <v>24800000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,67 +2946,67 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23400000000</v>
+        <v>23430000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21910000000</v>
+        <v>23370000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21330000000</v>
+        <v>22890000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19380000000</v>
+        <v>19240000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18960000000</v>
+        <v>18890000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18750000000</v>
+        <v>18790000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18220000000</v>
+        <v>18260000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13420000000</v>
+        <v>13860000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13010000000</v>
+        <v>13000000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11790000000</v>
+        <v>11500000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,37 +3096,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11790000000</v>
+        <v>11500000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11110000000</v>
+        <v>11260000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10760000000</v>
+        <v>11020000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,82 +3141,82 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10390000000</v>
+        <v>10330000000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>SentinelOne Inc</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7660000000</v>
+        <v>7930000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SentinelOne Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7660000000</v>
+        <v>7380000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7580000000</v>
+        <v>7250000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7300000000</v>
+        <v>7160000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7240000000</v>
+        <v>7080000000</v>
       </c>
     </row>
     <row r="183">
@@ -3237,46 +3237,46 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6210000000</v>
+        <v>6340000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5980000000</v>
+        <v>5970000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5850000000</v>
+        <v>5970000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5110000000</v>
+        <v>5160000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4820000000</v>
+        <v>4880000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,37 +3321,37 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3890000000</v>
+        <v>4020000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3550000000</v>
+        <v>3710000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3520000000</v>
+        <v>3650000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3510000000</v>
+        <v>3500000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2890000000</v>
+        <v>3010000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2590000000</v>
+        <v>2510000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2400000000</v>
+        <v>2360000000</v>
       </c>
     </row>
     <row r="196">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2250000000</v>
+        <v>2230000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2010000000</v>
+        <v>2000000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1880000000</v>
+        <v>1900000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1470000000</v>
+        <v>1540000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1130000000</v>
+        <v>1140000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1090000000</v>
+        <v>1110000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>818290000</v>
+        <v>848260000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>695930000</v>
+        <v>715800000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>311220000</v>
+        <v>332680000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5020250000000</v>
+        <v>5081990000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5349480000000</v>
+        <v>5114260000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4073070000000</v>
+        <v>3947650000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3957440000000</v>
+        <v>3869760000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2830010000000</v>
+        <v>2700680000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2239990000000</v>
+        <v>2138650000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1776940000000</v>
+        <v>1652950000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1612530000000</v>
+        <v>1543030000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1527610000000</v>
+        <v>1480610000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1196230000000</v>
+        <v>1230060000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1153740000000</v>
+        <v>1172310000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1033750000000</v>
+        <v>969050000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>934600000000</v>
+        <v>960940000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>902300000000</v>
+        <v>894590000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>891000000000</v>
+        <v>829180000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>761480000000</v>
+        <v>773590000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,37 +801,37 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>732290000000</v>
+        <v>732870000000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASML Holding NV</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>646230000000</v>
+        <v>644910000000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>ASML Holding NV</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>621220000000</v>
+        <v>601460000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>545420000000</v>
+        <v>554700000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>503270000000</v>
+        <v>503960000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,37 +876,37 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>484740000000</v>
+        <v>471460000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>448070000000</v>
+        <v>451200000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>442380000000</v>
+        <v>447870000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>422880000000</v>
+        <v>413540000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,22 +936,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>398760000000</v>
+        <v>410200000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>390460000000</v>
+        <v>384610000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,37 +966,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>374300000000</v>
+        <v>381460000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>369780000000</v>
+        <v>379600000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>364290000000</v>
+        <v>363270000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,157 +1011,157 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>351530000000</v>
+        <v>353610000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>340260000000</v>
+        <v>326970000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>326380000000</v>
+        <v>323630000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>324530000000</v>
+        <v>314430000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>313410000000</v>
+        <v>303330000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>308930000000</v>
+        <v>300940000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>307760000000</v>
+        <v>298060000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>306990000000</v>
+        <v>290320000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>300080000000</v>
+        <v>288940000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>293710000000</v>
+        <v>288020000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>284050000000</v>
+        <v>287990000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>281780000000</v>
+        <v>286060000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>270820000000</v>
+        <v>279190000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,82 +1206,82 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>268620000000</v>
+        <v>277690000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>263430000000</v>
+        <v>267640000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>261250000000</v>
+        <v>262750000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>259960000000</v>
+        <v>259520000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>259750000000</v>
+        <v>255250000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>258230000000</v>
+        <v>253300000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>256610000000</v>
+        <v>250150000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,157 +1311,157 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>247400000000</v>
+        <v>249170000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>246600000000</v>
+        <v>243640000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>245070000000</v>
+        <v>241810000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>242000000000</v>
+        <v>237520000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>236980000000</v>
+        <v>235270000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>236910000000</v>
+        <v>234730000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>230750000000</v>
+        <v>224390000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>230750000000</v>
+        <v>220370000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>224250000000</v>
+        <v>219590000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>218540000000</v>
+        <v>217200000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>213280000000</v>
+        <v>205990000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>207750000000</v>
+        <v>205500000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,82 +1491,82 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>200930000000</v>
+        <v>202310000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>199190000000</v>
+        <v>195340000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>198980000000</v>
+        <v>194910000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>193100000000</v>
+        <v>192920000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>190420000000</v>
+        <v>189190000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>190030000000</v>
+        <v>187800000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,37 +1581,37 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>186780000000</v>
+        <v>184780000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>183560000000</v>
+        <v>184550000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>180980000000</v>
+        <v>182240000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>174260000000</v>
+        <v>178770000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>173920000000</v>
+        <v>177380000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,52 +1656,52 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>171630000000</v>
+        <v>173540000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>164920000000</v>
+        <v>170840000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>164400000000</v>
+        <v>170330000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>163290000000</v>
+        <v>161510000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,82 +1716,82 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>158480000000</v>
+        <v>158130000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>151970000000</v>
+        <v>156800000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>151250000000</v>
+        <v>155820000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>150140000000</v>
+        <v>152930000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>142000000000</v>
+        <v>148230000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>141690000000</v>
+        <v>147470000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>138120000000</v>
+        <v>141080000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,82 +1821,82 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>136940000000</v>
+        <v>140410000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>136070000000</v>
+        <v>136150000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>130690000000</v>
+        <v>133570000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>130640000000</v>
+        <v>133430000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>128630000000</v>
+        <v>132580000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>127280000000</v>
+        <v>131930000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,127 +1911,127 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>124850000000</v>
+        <v>128690000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>123680000000</v>
+        <v>127020000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123280000000</v>
+        <v>123560000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>119000000000</v>
+        <v>122770000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119000000000</v>
+        <v>122020000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>116700000000</v>
+        <v>121050000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116220000000</v>
+        <v>120170000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113860000000</v>
+        <v>116180000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>112950000000</v>
+        <v>114660000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,22 +2046,22 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>112050000000</v>
+        <v>112690000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>110280000000</v>
+        <v>110770000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,202 +2076,202 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>109390000000</v>
+        <v>108110000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>108160000000</v>
+        <v>106800000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>104000000000</v>
+        <v>105300000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99460000000</v>
+        <v>105240000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99270000000</v>
+        <v>101170000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>98180000000</v>
+        <v>96570000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>98140000000</v>
+        <v>94840000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>98060000000</v>
+        <v>94760000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>94150000000</v>
+        <v>94000000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>94040000000</v>
+        <v>93510000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>92000000000</v>
+        <v>92550000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>90610000000</v>
+        <v>92520000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>90120000000</v>
+        <v>91980000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>89690000000</v>
+        <v>90720000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,247 +2286,247 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>89650000000</v>
+        <v>88440000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>88530000000</v>
+        <v>86370000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>84710000000</v>
+        <v>84330000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>82950000000</v>
+        <v>83470000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>81680000000</v>
+        <v>80900000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>80430000000</v>
+        <v>78470000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>77150000000</v>
+        <v>77640000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>76620000000</v>
+        <v>76530000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>75840000000</v>
+        <v>75300000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>74460000000</v>
+        <v>73540000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>72700000000</v>
+        <v>71830000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69230000000</v>
+        <v>71150000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66780000000</v>
+        <v>67810000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65960000000</v>
+        <v>65130000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64780000000</v>
+        <v>63340000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>63270000000</v>
+        <v>62480000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>62680000000</v>
+        <v>61540000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,127 +2541,127 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55740000000</v>
+        <v>56920000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>52410000000</v>
+        <v>53280000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>51170000000</v>
+        <v>51930000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50950000000</v>
+        <v>50610000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>50320000000</v>
+        <v>49220000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>48930000000</v>
+        <v>47610000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48910000000</v>
+        <v>47470000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47450000000</v>
+        <v>47270000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46990000000</v>
+        <v>44730000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,52 +2676,52 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46720000000</v>
+        <v>44610000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>46640000000</v>
+        <v>44350000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>44190000000</v>
+        <v>43270000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>43940000000</v>
+        <v>42910000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,52 +2736,52 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42710000000</v>
+        <v>40680000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40960000000</v>
+        <v>39030000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>37720000000</v>
+        <v>38950000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>37560000000</v>
+        <v>38770000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>36710000000</v>
+        <v>36410000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,67 +2811,67 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35580000000</v>
+        <v>35610000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34100000000</v>
+        <v>33880000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32900000000</v>
+        <v>30880000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32120000000</v>
+        <v>30670000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>31020000000</v>
+        <v>30650000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29490000000</v>
+        <v>28910000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>29010000000</v>
+        <v>28070000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25640000000</v>
+        <v>27020000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24800000000</v>
+        <v>24430000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23430000000</v>
+        <v>23770000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23370000000</v>
+        <v>22150000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,67 +2976,67 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22890000000</v>
+        <v>22100000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19240000000</v>
+        <v>19690000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18890000000</v>
+        <v>19080000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18790000000</v>
+        <v>18630000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18260000000</v>
+        <v>18400000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13860000000</v>
+        <v>13380000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>13000000000</v>
+        <v>12990000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11500000000</v>
+        <v>11620000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,37 +3096,37 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11500000000</v>
+        <v>11620000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11260000000</v>
+        <v>11340000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>11020000000</v>
+        <v>10320000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10330000000</v>
+        <v>10290000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,67 +3156,67 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7930000000</v>
+        <v>7830000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7380000000</v>
+        <v>7690000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7250000000</v>
+        <v>7290000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7160000000</v>
+        <v>7290000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7080000000</v>
+        <v>7180000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,22 +3231,22 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6820000000</v>
+        <v>6800000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6340000000</v>
+        <v>5980000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,22 +3261,22 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5970000000</v>
+        <v>5910000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5970000000</v>
+        <v>5770000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5160000000</v>
+        <v>5020000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4880000000</v>
+        <v>4830000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4020000000</v>
+        <v>3830000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,37 +3336,37 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3710000000</v>
+        <v>3580000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3650000000</v>
+        <v>3510000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3500000000</v>
+        <v>3510000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3010000000</v>
+        <v>2800000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,37 +3396,37 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2510000000</v>
+        <v>2500000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2360000000</v>
+        <v>2320000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2300000000</v>
+        <v>2310000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2230000000</v>
+        <v>2130000000</v>
       </c>
     </row>
     <row r="198">
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2000000000</v>
+        <v>2070000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1900000000</v>
+        <v>1930000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1540000000</v>
+        <v>1490000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1140000000</v>
+        <v>1150000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1110000000</v>
+        <v>1050000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>848260000</v>
+        <v>812790000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>715800000</v>
+        <v>672840000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>332680000</v>
+        <v>320420000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5081990000000</v>
+        <v>5074760000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5114260000000</v>
+        <v>5084140000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3947650000000</v>
+        <v>3903280000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3869760000000</v>
+        <v>3895230000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2700680000000</v>
+        <v>2675010000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2138650000000</v>
+        <v>2170590000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1652950000000</v>
+        <v>1636690000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1543030000000</v>
+        <v>1535580000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1480610000000</v>
+        <v>1471290000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1230060000000</v>
+        <v>1198780000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1172310000000</v>
+        <v>1160690000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>969050000000</v>
+        <v>992880000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>960940000000</v>
+        <v>951180000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>894590000000</v>
+        <v>881400000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>829180000000</v>
+        <v>843650000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>773590000000</v>
+        <v>761610000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>732870000000</v>
+        <v>753340000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>644910000000</v>
+        <v>635070000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>601460000000</v>
+        <v>605800000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>554700000000</v>
+        <v>546280000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>503960000000</v>
+        <v>504760000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,37 +876,37 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>471460000000</v>
+        <v>472800000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>451200000000</v>
+        <v>460770000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>447870000000</v>
+        <v>444600000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>413540000000</v>
+        <v>419890000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,22 +936,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>410200000000</v>
+        <v>398890000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>384610000000</v>
+        <v>381470000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,22 +966,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>381460000000</v>
+        <v>375280000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>379600000000</v>
+        <v>374000000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>363270000000</v>
+        <v>358410000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>353610000000</v>
+        <v>350010000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>326970000000</v>
+        <v>319090000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,37 +1041,37 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>323630000000</v>
+        <v>315800000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>314430000000</v>
+        <v>311290000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>303330000000</v>
+        <v>310900000000</v>
       </c>
     </row>
     <row r="40">
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>300940000000</v>
+        <v>307710000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,37 +1101,37 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>298060000000</v>
+        <v>299380000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>290320000000</v>
+        <v>295170000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>288940000000</v>
+        <v>290210000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,22 +1146,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>288020000000</v>
+        <v>287950000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>287990000000</v>
+        <v>281900000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>286060000000</v>
+        <v>276630000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>279190000000</v>
+        <v>270400000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>277690000000</v>
+        <v>268860000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,67 +1221,67 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>267640000000</v>
+        <v>265960000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>262750000000</v>
+        <v>263730000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>259520000000</v>
+        <v>259990000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>255250000000</v>
+        <v>257760000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>253300000000</v>
+        <v>254970000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,67 +1296,67 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>250150000000</v>
+        <v>249140000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>249170000000</v>
+        <v>247880000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>243640000000</v>
+        <v>247310000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>241810000000</v>
+        <v>238890000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>237520000000</v>
+        <v>237480000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>235270000000</v>
+        <v>234560000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>234730000000</v>
+        <v>233030000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>224390000000</v>
+        <v>224630000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,82 +1416,82 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>220370000000</v>
+        <v>217060000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>219590000000</v>
+        <v>217030000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>217200000000</v>
+        <v>211520000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>205990000000</v>
+        <v>206360000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>205500000000</v>
+        <v>204570000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>202310000000</v>
+        <v>202330000000</v>
       </c>
     </row>
     <row r="68">
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>195340000000</v>
+        <v>194290000000</v>
       </c>
     </row>
     <row r="69">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>194910000000</v>
+        <v>193480000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,22 +1536,22 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>192920000000</v>
+        <v>190020000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>189190000000</v>
+        <v>187840000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,82 +1566,82 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>187800000000</v>
+        <v>185550000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184780000000</v>
+        <v>185020000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>184550000000</v>
+        <v>181690000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>182240000000</v>
+        <v>179440000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>178770000000</v>
+        <v>178930000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>177380000000</v>
+        <v>175820000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>173540000000</v>
+        <v>174220000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,82 +1671,82 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>170840000000</v>
+        <v>172190000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>170330000000</v>
+        <v>162160000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>161510000000</v>
+        <v>157190000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Charles Schwab Corp</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>158130000000</v>
+        <v>156780000000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Charles Schwab Corp</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>156800000000</v>
+        <v>156640000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>155820000000</v>
+        <v>148870000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,52 +1761,52 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>152930000000</v>
+        <v>147390000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>148230000000</v>
+        <v>145560000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>147470000000</v>
+        <v>140990000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>141080000000</v>
+        <v>139440000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,22 +1821,22 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>140410000000</v>
+        <v>137000000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>136150000000</v>
+        <v>136240000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,7 +1851,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>133570000000</v>
+        <v>132750000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,37 +1866,37 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>133430000000</v>
+        <v>132530000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>132580000000</v>
+        <v>130660000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>131930000000</v>
+        <v>128640000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>128690000000</v>
+        <v>125590000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,37 +1926,37 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>127020000000</v>
+        <v>124080000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>123560000000</v>
+        <v>122560000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>122770000000</v>
+        <v>122050000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,112 +1971,112 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>122020000000</v>
+        <v>120520000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>121050000000</v>
+        <v>120280000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>120170000000</v>
+        <v>117090000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116180000000</v>
+        <v>115990000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>114660000000</v>
+        <v>114910000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>112690000000</v>
+        <v>114810000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>110770000000</v>
+        <v>112510000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>108110000000</v>
+        <v>111470000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,37 +2091,37 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>106800000000</v>
+        <v>106550000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>105300000000</v>
+        <v>103000000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>105240000000</v>
+        <v>102680000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,67 +2136,67 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>101170000000</v>
+        <v>101550000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96570000000</v>
+        <v>96820000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>94840000000</v>
+        <v>95050000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94760000000</v>
+        <v>94230000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>94000000000</v>
+        <v>93900000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,22 +2211,22 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>93510000000</v>
+        <v>92830000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>92550000000</v>
+        <v>91770000000</v>
       </c>
     </row>
     <row r="117">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>92520000000</v>
+        <v>91770000000</v>
       </c>
     </row>
     <row r="118">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>91980000000</v>
+        <v>91360000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>90720000000</v>
+        <v>89630000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>88440000000</v>
+        <v>87090000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>86370000000</v>
+        <v>85980000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>84330000000</v>
+        <v>82880000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,7 +2331,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>83470000000</v>
+        <v>81110000000</v>
       </c>
     </row>
     <row r="124">
@@ -2346,52 +2346,52 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>80900000000</v>
+        <v>79890000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>78470000000</v>
+        <v>78750000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>77640000000</v>
+        <v>78340000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>76530000000</v>
+        <v>74970000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,52 +2406,52 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>75300000000</v>
+        <v>74810000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73540000000</v>
+        <v>73950000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>71830000000</v>
+        <v>73230000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>71150000000</v>
+        <v>69400000000</v>
       </c>
     </row>
     <row r="132">
@@ -2466,52 +2466,52 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67810000000</v>
+        <v>66630000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>65130000000</v>
+        <v>64150000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>63340000000</v>
+        <v>64040000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62480000000</v>
+        <v>62640000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61540000000</v>
+        <v>61630000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56920000000</v>
+        <v>55400000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>53280000000</v>
+        <v>52710000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>51930000000</v>
+        <v>51340000000</v>
       </c>
     </row>
     <row r="140">
@@ -2601,52 +2601,52 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49220000000</v>
+        <v>48780000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47610000000</v>
+        <v>47040000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47470000000</v>
+        <v>46260000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47270000000</v>
+        <v>45940000000</v>
       </c>
     </row>
     <row r="145">
@@ -2661,37 +2661,37 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44730000000</v>
+        <v>44610000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44610000000</v>
+        <v>44020000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>44350000000</v>
+        <v>43390000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>43270000000</v>
+        <v>43150000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,37 +2721,37 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>42910000000</v>
+        <v>42310000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>40680000000</v>
+        <v>41600000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39030000000</v>
+        <v>40680000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,22 +2766,22 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>38950000000</v>
+        <v>40200000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>38770000000</v>
+        <v>39370000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>36410000000</v>
+        <v>35110000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35610000000</v>
+        <v>34820000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,82 +2826,82 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33880000000</v>
+        <v>33480000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>30880000000</v>
+        <v>31480000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30670000000</v>
+        <v>30500000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30650000000</v>
+        <v>29910000000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ZM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Zoom Communications Inc</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28910000000</v>
+        <v>27940000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ZM</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Zoom Communications Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>28070000000</v>
+        <v>27750000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>27020000000</v>
+        <v>26510000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24430000000</v>
+        <v>23650000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23770000000</v>
+        <v>23550000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22150000000</v>
+        <v>21920000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22100000000</v>
+        <v>21640000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19690000000</v>
+        <v>19130000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19080000000</v>
+        <v>18880000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18630000000</v>
+        <v>18600000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18400000000</v>
+        <v>18480000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13380000000</v>
+        <v>13430000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>12990000000</v>
+        <v>12640000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11620000000</v>
+        <v>11380000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11620000000</v>
+        <v>11380000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11340000000</v>
+        <v>10870000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10320000000</v>
+        <v>10080000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>10290000000</v>
+        <v>9570000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>7830000000</v>
+        <v>8350000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7690000000</v>
+        <v>7460000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,37 +3186,37 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7290000000</v>
+        <v>7250000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7290000000</v>
+        <v>7200000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7180000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6800000000</v>
+        <v>6470000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>5980000000</v>
+        <v>6260000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5910000000</v>
+        <v>5560000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5770000000</v>
+        <v>5520000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5020000000</v>
+        <v>4900000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,67 +3306,67 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4830000000</v>
+        <v>4780000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3830000000</v>
+        <v>3890000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3580000000</v>
+        <v>3850000000</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LMND</t>
+          <t>ONDS</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lemonade Inc</t>
+          <t>Ondas Inc</t>
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3510000000</v>
+        <v>3610000000</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ONDS</t>
+          <t>LMND</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Ondas Inc</t>
+          <t>Lemonade Inc</t>
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3510000000</v>
+        <v>3480000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2800000000</v>
+        <v>2710000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,33 +3396,33 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2500000000</v>
+        <v>2450000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2320000000</v>
+        <v>2310000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
@@ -3441,37 +3441,37 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2130000000</v>
+        <v>2100000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>C3.ai Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2070000000</v>
+        <v>2000000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>C3.ai Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1930000000</v>
+        <v>1940000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1490000000</v>
+        <v>1480000000</v>
       </c>
     </row>
     <row r="201">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1050000000</v>
+        <v>1030000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>812790000</v>
+        <v>850260000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>672840000</v>
+        <v>652970000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>320420000</v>
+        <v>298190000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3903280000000</v>
+        <v>3899970000000</v>
       </c>
     </row>
     <row r="8">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1471290000000</v>
+        <v>1471300000000</v>
       </c>
     </row>
     <row r="14">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1160690000000</v>
+        <v>1160820000000</v>
       </c>
     </row>
     <row r="16">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>374000000000</v>
+        <v>373210000000</v>
       </c>
     </row>
     <row r="34">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>287950000000</v>
+        <v>287430000000</v>
       </c>
     </row>
     <row r="45">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>238890000000</v>
+        <v>239640000000</v>
       </c>
     </row>
     <row r="58">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139440000000</v>
+        <v>139570000000</v>
       </c>
     </row>
     <row r="89">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5074760000000</v>
+        <v>5074770000000</v>
       </c>
     </row>
     <row r="6">
@@ -582,31 +582,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3899970000000</v>
+        <v>3895240000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3895230000000</v>
+        <v>3880330000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2675010000000</v>
+        <v>2675000000000</v>
       </c>
     </row>
     <row r="10">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1471300000000</v>
+        <v>1471290000000</v>
       </c>
     </row>
     <row r="14">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1160820000000</v>
+        <v>1160680000000</v>
       </c>
     </row>
     <row r="16">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>761610000000</v>
+        <v>761600000000</v>
       </c>
     </row>
     <row r="21">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>381470000000</v>
+        <v>381480000000</v>
       </c>
     </row>
     <row r="32">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>373210000000</v>
+        <v>374000000000</v>
       </c>
     </row>
     <row r="34">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>287430000000</v>
+        <v>287950000000</v>
       </c>
     </row>
     <row r="45">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>239640000000</v>
+        <v>238890000000</v>
       </c>
     </row>
     <row r="58">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>174220000000</v>
+        <v>174210000000</v>
       </c>
     </row>
     <row r="79">
@@ -1761,7 +1761,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>147390000000</v>
+        <v>147310000000</v>
       </c>
     </row>
     <row r="86">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139570000000</v>
+        <v>139440000000</v>
       </c>
     </row>
     <row r="89">
@@ -1932,61 +1932,61 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122560000000</v>
+        <v>122050000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>122050000000</v>
+        <v>120520000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120520000000</v>
+        <v>120280000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120280000000</v>
+        <v>120170000000</v>
       </c>
     </row>
     <row r="101">
@@ -2097,46 +2097,46 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103000000000</v>
+        <v>102680000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>102680000000</v>
+        <v>101540000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>101550000000</v>
+        <v>101420000000</v>
       </c>
     </row>
     <row r="111">
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95050000000</v>
+        <v>95060000000</v>
       </c>
     </row>
     <row r="113">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73950000000</v>
+        <v>73940000000</v>
       </c>
     </row>
     <row r="130">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>43150000000</v>
+        <v>43160000000</v>
       </c>
     </row>
     <row r="149">
@@ -2982,91 +2982,91 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>19130000000</v>
+        <v>18880000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18880000000</v>
+        <v>18480000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18600000000</v>
+        <v>17440000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18480000000</v>
+        <v>13430000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13430000000</v>
+        <v>12640000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>12640000000</v>
+        <v>11380000000</v>
       </c>
     </row>
     <row r="173">
@@ -3087,31 +3087,31 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11380000000</v>
+        <v>10870000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10870000000</v>
+        <v>10380000000</v>
       </c>
     </row>
     <row r="176">
@@ -3171,82 +3171,82 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7460000000</v>
+        <v>7420000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7250000000</v>
+        <v>7200000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7200000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>7130000000</v>
+        <v>6470000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6470000000</v>
+        <v>6260000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6260000000</v>
+        <v>5720000000</v>
       </c>
     </row>
     <row r="185">
@@ -3402,12 +3402,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
@@ -3417,16 +3417,16 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2310000000</v>
+        <v>2210000000</v>
       </c>
     </row>
     <row r="197">
@@ -3507,31 +3507,31 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1030000000</v>
+        <v>850320000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>850260000</v>
+        <v>800260000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>652970000</v>
+        <v>652990000</v>
       </c>
     </row>
     <row r="205">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5074770000000</v>
+        <v>5019090000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5084140000000</v>
+        <v>5205600000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3895240000000</v>
+        <v>3955320000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3880330000000</v>
+        <v>3842540000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2675000000000</v>
+        <v>2686760000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2170590000000</v>
+        <v>2200990000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1636690000000</v>
+        <v>1611860000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1535580000000</v>
+        <v>1571340000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1471290000000</v>
+        <v>1547970000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1198780000000</v>
+        <v>1204130000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1160680000000</v>
+        <v>1174310000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>992880000000</v>
+        <v>1022460000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>951180000000</v>
+        <v>954350000000</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>881400000000</v>
+        <v>887940000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,37 +771,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>843650000000</v>
+        <v>867300000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>761600000000</v>
+        <v>758810000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>753340000000</v>
+        <v>754580000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>635070000000</v>
+        <v>641070000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>605800000000</v>
+        <v>613160000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>546280000000</v>
+        <v>537430000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>504760000000</v>
+        <v>506700000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>472800000000</v>
+        <v>477820000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>460770000000</v>
+        <v>458400000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>444600000000</v>
+        <v>445420000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>419890000000</v>
+        <v>434630000000</v>
       </c>
     </row>
     <row r="30">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>398890000000</v>
+        <v>398850000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,112 +951,112 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>381480000000</v>
+        <v>381170000000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Procter &amp; Gamble Co</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>375280000000</v>
+        <v>371440000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble Co</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>374000000000</v>
+        <v>368640000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>358410000000</v>
+        <v>349730000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>350010000000</v>
+        <v>346910000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>319090000000</v>
+        <v>319400000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>315800000000</v>
+        <v>318640000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>311290000000</v>
+        <v>318160000000</v>
       </c>
     </row>
     <row r="39">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>310900000000</v>
+        <v>314640000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>307710000000</v>
+        <v>307590000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>299380000000</v>
+        <v>303920000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,37 +1116,37 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>295170000000</v>
+        <v>298050000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>290210000000</v>
+        <v>297210000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>287950000000</v>
+        <v>296980000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>281900000000</v>
+        <v>288180000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,22 +1176,22 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>276630000000</v>
+        <v>281560000000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Texas Instruments Inc</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>270400000000</v>
+        <v>272260000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,67 +1206,67 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>268860000000</v>
+        <v>269320000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>265960000000</v>
+        <v>268100000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>263730000000</v>
+        <v>266850000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Texas Instruments Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>259990000000</v>
+        <v>266490000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>257760000000</v>
+        <v>262390000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>254970000000</v>
+        <v>260100000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>249140000000</v>
+        <v>253240000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>247880000000</v>
+        <v>249400000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,52 +1326,52 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>247310000000</v>
+        <v>248090000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>238890000000</v>
+        <v>240380000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>237480000000</v>
+        <v>238770000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>234560000000</v>
+        <v>238540000000</v>
       </c>
     </row>
     <row r="60">
@@ -1386,22 +1386,22 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>233030000000</v>
+        <v>234040000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>224630000000</v>
+        <v>233980000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>217060000000</v>
+        <v>227740000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>217030000000</v>
+        <v>216350000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>211520000000</v>
+        <v>212760000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,7 +1461,7 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>206360000000</v>
+        <v>208540000000</v>
       </c>
     </row>
     <row r="66">
@@ -1476,7 +1476,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>204570000000</v>
+        <v>203780000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,142 +1491,142 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>202330000000</v>
+        <v>203040000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>194290000000</v>
+        <v>196770000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>193480000000</v>
+        <v>194720000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>190020000000</v>
+        <v>191780000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>187840000000</v>
+        <v>190630000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>185550000000</v>
+        <v>184600000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>185020000000</v>
+        <v>183220000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>181690000000</v>
+        <v>181480000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>179440000000</v>
+        <v>181470000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>178930000000</v>
+        <v>179070000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>175820000000</v>
+        <v>177500000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>174210000000</v>
+        <v>172890000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>172190000000</v>
+        <v>172060000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>162160000000</v>
+        <v>163900000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>157190000000</v>
+        <v>157610000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>156780000000</v>
+        <v>156550000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>156640000000</v>
+        <v>155170000000</v>
       </c>
     </row>
     <row r="84">
@@ -1746,67 +1746,67 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>148870000000</v>
+        <v>148830000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>147310000000</v>
+        <v>146910000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>145560000000</v>
+        <v>146600000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>140990000000</v>
+        <v>146050000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139440000000</v>
+        <v>140460000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137000000000</v>
+        <v>137630000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,22 +1836,22 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>136240000000</v>
+        <v>135070000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>132750000000</v>
+        <v>133310000000</v>
       </c>
     </row>
     <row r="92">
@@ -1866,37 +1866,37 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>132530000000</v>
+        <v>133220000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>130660000000</v>
+        <v>132850000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>128640000000</v>
+        <v>130920000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>125590000000</v>
+        <v>125850000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>124080000000</v>
+        <v>122930000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,82 +1941,82 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122050000000</v>
+        <v>121250000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120520000000</v>
+        <v>120040000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120280000000</v>
+        <v>119320000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>120170000000</v>
+        <v>118170000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>117090000000</v>
+        <v>118170000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>115990000000</v>
+        <v>117840000000</v>
       </c>
     </row>
     <row r="103">
@@ -2031,52 +2031,52 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>114910000000</v>
+        <v>117070000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>114810000000</v>
+        <v>115070000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>112510000000</v>
+        <v>111210000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>111470000000</v>
+        <v>111210000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,22 +2091,22 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>106550000000</v>
+        <v>110030000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>102680000000</v>
+        <v>100850000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,22 +2121,22 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>101540000000</v>
+        <v>100730000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>101420000000</v>
+        <v>100650000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,67 +2151,67 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96820000000</v>
+        <v>100630000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95060000000</v>
+        <v>95480000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94230000000</v>
+        <v>93190000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93900000000</v>
+        <v>93020000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92830000000</v>
+        <v>92590000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,82 +2226,82 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>91770000000</v>
+        <v>90830000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>91770000000</v>
+        <v>89850000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>91360000000</v>
+        <v>89290000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>89630000000</v>
+        <v>87260000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>87090000000</v>
+        <v>85350000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>85980000000</v>
+        <v>84600000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>82880000000</v>
+        <v>83150000000</v>
       </c>
     </row>
     <row r="123">
@@ -2331,112 +2331,112 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>81110000000</v>
+        <v>80800000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>79890000000</v>
+        <v>80320000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>78750000000</v>
+        <v>79390000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>78340000000</v>
+        <v>78780000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive Co</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>74970000000</v>
+        <v>76910000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>74810000000</v>
+        <v>75050000000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Colgate-Palmolive Co</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73940000000</v>
+        <v>74220000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>73230000000</v>
+        <v>67540000000</v>
       </c>
     </row>
     <row r="131">
@@ -2451,22 +2451,22 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>69400000000</v>
+        <v>67480000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>66630000000</v>
+        <v>64370000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,37 +2481,37 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64150000000</v>
+        <v>64050000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>64040000000</v>
+        <v>62580000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>62640000000</v>
+        <v>60820000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>61630000000</v>
+        <v>59010000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,37 +2541,37 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55400000000</v>
+        <v>56310000000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Edwards Lifesciences Corp</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>52710000000</v>
+        <v>52200000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences Corp</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>51340000000</v>
+        <v>52140000000</v>
       </c>
     </row>
     <row r="140">
@@ -2586,33 +2586,33 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50610000000</v>
+        <v>50250000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>48780000000</v>
+        <v>47570000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46260000000</v>
+        <v>46180000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45940000000</v>
+        <v>45020000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44610000000</v>
+        <v>44790000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,37 +2676,37 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44020000000</v>
+        <v>44160000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>43390000000</v>
+        <v>42470000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>43160000000</v>
+        <v>42110000000</v>
       </c>
     </row>
     <row r="149">
@@ -2721,22 +2721,22 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>42310000000</v>
+        <v>41960000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>41600000000</v>
+        <v>41670000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40680000000</v>
+        <v>40930000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>40200000000</v>
+        <v>40490000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>39370000000</v>
+        <v>39430000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>35110000000</v>
+        <v>36120000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>34820000000</v>
+        <v>35950000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33480000000</v>
+        <v>33460000000</v>
       </c>
     </row>
     <row r="157">
@@ -2841,37 +2841,37 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>31480000000</v>
+        <v>32210000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30500000000</v>
+        <v>30440000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>29910000000</v>
+        <v>30360000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>27940000000</v>
+        <v>28610000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>27750000000</v>
+        <v>26640000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>26510000000</v>
+        <v>25700000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23650000000</v>
+        <v>23450000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,37 +2946,37 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23550000000</v>
+        <v>23350000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21920000000</v>
+        <v>21480000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21640000000</v>
+        <v>20370000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>18880000000</v>
+        <v>18680000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18480000000</v>
+        <v>18070000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>17440000000</v>
+        <v>16410000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>13430000000</v>
+        <v>13210000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>12640000000</v>
+        <v>12020000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>11380000000</v>
+        <v>11050000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,7 +3081,7 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11380000000</v>
+        <v>11050000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>10870000000</v>
+        <v>10880000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10380000000</v>
+        <v>10530000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10080000000</v>
+        <v>10290000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9570000000</v>
+        <v>9600000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8350000000</v>
+        <v>8880000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7420000000</v>
+        <v>7340000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7200000000</v>
+        <v>7120000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7130000000</v>
+        <v>7120000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6470000000</v>
+        <v>6440000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6260000000</v>
+        <v>6380000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>5720000000</v>
+        <v>5800000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5560000000</v>
+        <v>5660000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5520000000</v>
+        <v>5390000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4900000000</v>
+        <v>4830000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4780000000</v>
+        <v>4740000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3890000000</v>
+        <v>4080000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3850000000</v>
+        <v>3820000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3610000000</v>
+        <v>3590000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3480000000</v>
+        <v>3490000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2710000000</v>
+        <v>2640000000</v>
       </c>
     </row>
     <row r="194">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2310000000</v>
+        <v>2240000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,37 +3426,37 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2210000000</v>
+        <v>2160000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>C3.ai Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2100000000</v>
+        <v>2060000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>C3.ai Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2000000000</v>
+        <v>2010000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1940000000</v>
+        <v>2000000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1480000000</v>
+        <v>1450000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1150000000</v>
+        <v>1130000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>850320000</v>
+        <v>830340000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>800260000</v>
+        <v>787380000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>652990000</v>
+        <v>636880000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>298190000</v>
+        <v>309690000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5019090000000</v>
+        <v>5065640000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5205600000000</v>
+        <v>5252350000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3955320000000</v>
+        <v>3945880000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3842540000000</v>
+        <v>3892470000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2686760000000</v>
+        <v>2730020000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,52 +636,52 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2200990000000</v>
+        <v>2265820000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1611860000000</v>
+        <v>1634160000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1571340000000</v>
+        <v>1610590000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1547970000000</v>
+        <v>1585360000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1204130000000</v>
+        <v>1206740000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1174310000000</v>
+        <v>1161940000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1022460000000</v>
+        <v>1050820000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,67 +741,67 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>954350000000</v>
+        <v>946650000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>887940000000</v>
+        <v>914610000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>867300000000</v>
+        <v>892590000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>758810000000</v>
+        <v>750290000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>754580000000</v>
+        <v>739770000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>641070000000</v>
+        <v>646920000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>613160000000</v>
+        <v>630380000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>537430000000</v>
+        <v>534230000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>506700000000</v>
+        <v>506080000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>477820000000</v>
+        <v>477560000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>458400000000</v>
+        <v>450930000000</v>
       </c>
     </row>
     <row r="28">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>445420000000</v>
+        <v>439640000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,37 +921,37 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>434630000000</v>
+        <v>439130000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>398850000000</v>
+        <v>394690000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>381170000000</v>
+        <v>392310000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>371440000000</v>
+        <v>369060000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>368640000000</v>
+        <v>368360000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>349730000000</v>
+        <v>350840000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>346910000000</v>
+        <v>349890000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,82 +1026,82 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>319400000000</v>
+        <v>328590000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>318640000000</v>
+        <v>327890000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>318160000000</v>
+        <v>319150000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>314640000000</v>
+        <v>317760000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>307590000000</v>
+        <v>315810000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>303920000000</v>
+        <v>314210000000</v>
       </c>
     </row>
     <row r="42">
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>298050000000</v>
+        <v>307590000000</v>
       </c>
     </row>
     <row r="43">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>297210000000</v>
+        <v>300860000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>296980000000</v>
+        <v>297870000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>288180000000</v>
+        <v>293550000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>281560000000</v>
+        <v>287140000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,97 +1191,97 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>272260000000</v>
+        <v>282270000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>269320000000</v>
+        <v>274430000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>268100000000</v>
+        <v>266220000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>266850000000</v>
+        <v>265480000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>266490000000</v>
+        <v>263780000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>262390000000</v>
+        <v>262600000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>260100000000</v>
+        <v>256730000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>253240000000</v>
+        <v>256240000000</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>249400000000</v>
+        <v>249370000000</v>
       </c>
     </row>
     <row r="56">
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>248090000000</v>
+        <v>248120000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,52 +1341,52 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>240380000000</v>
+        <v>242180000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>238770000000</v>
+        <v>242010000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>238540000000</v>
+        <v>238390000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>234040000000</v>
+        <v>236520000000</v>
       </c>
     </row>
     <row r="61">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>233980000000</v>
+        <v>234480000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>227740000000</v>
+        <v>232760000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>216350000000</v>
+        <v>213300000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,82 +1446,82 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>212760000000</v>
+        <v>209820000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>208540000000</v>
+        <v>205800000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>203780000000</v>
+        <v>205400000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>203040000000</v>
+        <v>200530000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>196770000000</v>
+        <v>198250000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>194720000000</v>
+        <v>197250000000</v>
       </c>
     </row>
     <row r="70">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>191780000000</v>
+        <v>196660000000</v>
       </c>
     </row>
     <row r="71">
@@ -1551,22 +1551,22 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>190630000000</v>
+        <v>190330000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>184600000000</v>
+        <v>188590000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,52 +1581,52 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>183220000000</v>
+        <v>184580000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>181480000000</v>
+        <v>182520000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>181470000000</v>
+        <v>181930000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>179070000000</v>
+        <v>178400000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,37 +1641,37 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>177500000000</v>
+        <v>176540000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>172890000000</v>
+        <v>172860000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>172060000000</v>
+        <v>172450000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163900000000</v>
+        <v>163220000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>157610000000</v>
+        <v>157500000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>156550000000</v>
+        <v>154560000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,82 +1731,82 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>155170000000</v>
+        <v>154430000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>148830000000</v>
+        <v>143990000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>146910000000</v>
+        <v>143910000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>146600000000</v>
+        <v>142570000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>146050000000</v>
+        <v>141060000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>140460000000</v>
+        <v>138990000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137630000000</v>
+        <v>137440000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,52 +1836,52 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>135070000000</v>
+        <v>134360000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>133310000000</v>
+        <v>132920000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>133220000000</v>
+        <v>132340000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>132850000000</v>
+        <v>131100000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>130920000000</v>
+        <v>129390000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>125850000000</v>
+        <v>125730000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,112 +1926,112 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>122930000000</v>
+        <v>122710000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>121250000000</v>
+        <v>122580000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120040000000</v>
+        <v>120180000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119320000000</v>
+        <v>119040000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>118170000000</v>
+        <v>117470000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>118170000000</v>
+        <v>116720000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>117840000000</v>
+        <v>116150000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>117070000000</v>
+        <v>114360000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,37 +2046,37 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>115070000000</v>
+        <v>112810000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>111210000000</v>
+        <v>111590000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>111210000000</v>
+        <v>111190000000</v>
       </c>
     </row>
     <row r="107">
@@ -2091,7 +2091,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>110030000000</v>
+        <v>108790000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,97 +2106,97 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>100850000000</v>
+        <v>101090000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100730000000</v>
+        <v>100840000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>100650000000</v>
+        <v>98610000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>100630000000</v>
+        <v>97420000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95480000000</v>
+        <v>96660000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93190000000</v>
+        <v>93080000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>93020000000</v>
+        <v>91070000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,82 +2211,82 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>92590000000</v>
+        <v>90670000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>90830000000</v>
+        <v>90260000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>89850000000</v>
+        <v>88660000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>89290000000</v>
+        <v>87950000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87260000000</v>
+        <v>87770000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>85350000000</v>
+        <v>87260000000</v>
       </c>
     </row>
     <row r="121">
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>84600000000</v>
+        <v>85200000000</v>
       </c>
     </row>
     <row r="122">
@@ -2316,97 +2316,97 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>83150000000</v>
+        <v>84020000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>80800000000</v>
+        <v>83030000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>80320000000</v>
+        <v>80290000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>79390000000</v>
+        <v>80260000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>78780000000</v>
+        <v>79140000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>76910000000</v>
+        <v>78820000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>75050000000</v>
+        <v>78310000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,33 +2421,33 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>74220000000</v>
+        <v>73480000000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>67540000000</v>
+        <v>67940000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -2457,16 +2457,16 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>General Motors Company</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>64370000000</v>
+        <v>67240000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>64050000000</v>
+        <v>62710000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62580000000</v>
+        <v>62090000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>60820000000</v>
+        <v>59900000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59010000000</v>
+        <v>59680000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>56310000000</v>
+        <v>55790000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>52200000000</v>
+        <v>52350000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,127 +2571,127 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>52140000000</v>
+        <v>50600000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50250000000</v>
+        <v>49740000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>47570000000</v>
+        <v>49520000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47040000000</v>
+        <v>49220000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>46180000000</v>
+        <v>47980000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>45020000000</v>
+        <v>46690000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>44790000000</v>
+        <v>46340000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44160000000</v>
+        <v>44980000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>42470000000</v>
+        <v>43030000000</v>
       </c>
     </row>
     <row r="148">
@@ -2706,37 +2706,37 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>42110000000</v>
+        <v>42500000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>41960000000</v>
+        <v>42420000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>41670000000</v>
+        <v>42370000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40930000000</v>
+        <v>42200000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>40490000000</v>
+        <v>39260000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>39430000000</v>
+        <v>39090000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>36120000000</v>
+        <v>37300000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,52 +2811,52 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35950000000</v>
+        <v>35410000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>33460000000</v>
+        <v>34900000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32210000000</v>
+        <v>32860000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>30440000000</v>
+        <v>32330000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30360000000</v>
+        <v>30750000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28610000000</v>
+        <v>28420000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26640000000</v>
+        <v>26250000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25700000000</v>
+        <v>25210000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>23450000000</v>
+        <v>24640000000</v>
       </c>
     </row>
     <row r="164">
@@ -2946,7 +2946,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23350000000</v>
+        <v>23270000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,37 +2961,37 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>21480000000</v>
+        <v>23050000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>20370000000</v>
+        <v>21180000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>18680000000</v>
+        <v>20810000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18070000000</v>
+        <v>18900000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,112 +3021,112 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>16410000000</v>
+        <v>18480000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>IonQ Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>13210000000</v>
+        <v>18480000000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>IonQ Inc</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>12020000000</v>
+        <v>14150000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>11050000000</v>
+        <v>11650000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11050000000</v>
+        <v>11100000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>10880000000</v>
+        <v>11090000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>10530000000</v>
+        <v>11090000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10290000000</v>
+        <v>10940000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9600000000</v>
+        <v>9680000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,127 +3156,127 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8880000000</v>
+        <v>8930000000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>BROS</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Dutch Bros Inc</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7340000000</v>
+        <v>7270000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7120000000</v>
+        <v>7250000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7120000000</v>
+        <v>7080000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HIMS</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Hims &amp; Hers Health Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6440000000</v>
+        <v>6950000000</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>AVAV</t>
+          <t>HIMS</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AeroVironment Inc</t>
+          <t>Hims &amp; Hers Health Inc</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6380000000</v>
+        <v>6510000000</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>BROS</t>
+          <t>AVAV</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Dutch Bros Inc</t>
+          <t>AeroVironment Inc</t>
         </is>
       </c>
       <c r="L184" t="n">
-        <v>5800000000</v>
+        <v>6440000000</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MBLY</t>
+          <t>APLD</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Mobileye Global Inc</t>
+          <t>Applied Digital Corp</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5660000000</v>
+        <v>5900000000</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>APLD</t>
+          <t>MBLY</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Applied Digital Corp</t>
+          <t>Mobileye Global Inc</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5390000000</v>
+        <v>5840000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4830000000</v>
+        <v>5080000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4740000000</v>
+        <v>4980000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4080000000</v>
+        <v>4360000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>3820000000</v>
+        <v>4150000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3590000000</v>
+        <v>3870000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3490000000</v>
+        <v>3550000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,18 +3381,18 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2640000000</v>
+        <v>2740000000</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>NuScale Power Corp</t>
         </is>
       </c>
       <c r="L194" t="n">
@@ -3402,76 +3402,76 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2240000000</v>
+        <v>2420000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>NuScale Power Corp</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2160000000</v>
+        <v>2310000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>C3.ai Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2060000000</v>
+        <v>2240000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2010000000</v>
+        <v>1990000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>C3.ai Inc</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2000000000</v>
+        <v>1980000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1450000000</v>
+        <v>1550000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,37 +3501,37 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1130000000</v>
+        <v>1170000000</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>UMAC</t>
+          <t>FLNC</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Unusual Machines Inc</t>
+          <t>Fluence Energy Inc</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>830340000</v>
+        <v>1110000000</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>FLNC</t>
+          <t>UMAC</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Fluence Energy Inc</t>
+          <t>Unusual Machines Inc</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>787380000</v>
+        <v>892730000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>636880000</v>
+        <v>662640000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>309690000</v>
+        <v>315810000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5065640000000</v>
+        <v>5017920000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,37 +576,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5252350000000</v>
+        <v>5190660000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3945880000000</v>
+        <v>3962250000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3892470000000</v>
+        <v>3943510000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2730020000000</v>
+        <v>2746200000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2265820000000</v>
+        <v>2279510000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1634160000000</v>
+        <v>1679410000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1610590000000</v>
+        <v>1597780000000</v>
       </c>
     </row>
     <row r="13">
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1585360000000</v>
+        <v>1565670000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1206740000000</v>
+        <v>1212750000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1161940000000</v>
+        <v>1154580000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,37 +726,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1050820000000</v>
+        <v>1112450000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>946650000000</v>
+        <v>944290000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>914610000000</v>
+        <v>942290000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,37 +771,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>892590000000</v>
+        <v>901920000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>750290000000</v>
+        <v>748450000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>739770000000</v>
+        <v>747940000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>646920000000</v>
+        <v>652480000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>630380000000</v>
+        <v>640900000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>534230000000</v>
+        <v>534640000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>506080000000</v>
+        <v>505380000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>477560000000</v>
+        <v>472950000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,52 +891,52 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>450930000000</v>
+        <v>452850000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>439640000000</v>
+        <v>437050000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>439130000000</v>
+        <v>435480000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>394690000000</v>
+        <v>434830000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>392310000000</v>
+        <v>394670000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>369060000000</v>
+        <v>366810000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>368360000000</v>
+        <v>365410000000</v>
       </c>
     </row>
     <row r="34">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>350840000000</v>
+        <v>352020000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,22 +1011,22 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>349890000000</v>
+        <v>347700000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>328590000000</v>
+        <v>330140000000</v>
       </c>
     </row>
     <row r="37">
@@ -1041,97 +1041,97 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>327890000000</v>
+        <v>327920000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>319150000000</v>
+        <v>322690000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>317760000000</v>
+        <v>317060000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>315810000000</v>
+        <v>316830000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>314210000000</v>
+        <v>315850000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>307590000000</v>
+        <v>313960000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>300860000000</v>
+        <v>311170000000</v>
       </c>
     </row>
     <row r="44">
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>297870000000</v>
+        <v>299030000000</v>
       </c>
     </row>
     <row r="45">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>293550000000</v>
+        <v>298610000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>287140000000</v>
+        <v>285710000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>282270000000</v>
+        <v>283110000000</v>
       </c>
     </row>
     <row r="48">
@@ -1206,202 +1206,202 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>274430000000</v>
+        <v>273040000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>266220000000</v>
+        <v>269380000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>265480000000</v>
+        <v>267490000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>263780000000</v>
+        <v>264270000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>262600000000</v>
+        <v>262890000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Netflix Inc</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>256730000000</v>
+        <v>260360000000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Netflix Inc</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>256240000000</v>
+        <v>254550000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>249370000000</v>
+        <v>251940000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>248120000000</v>
+        <v>251160000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>242180000000</v>
+        <v>251150000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>242010000000</v>
+        <v>244270000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>238390000000</v>
+        <v>239320000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>236520000000</v>
+        <v>234250000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>234480000000</v>
+        <v>233850000000</v>
       </c>
     </row>
     <row r="62">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>232760000000</v>
+        <v>230740000000</v>
       </c>
     </row>
     <row r="63">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>213300000000</v>
+        <v>216400000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>209820000000</v>
+        <v>213200000000</v>
       </c>
     </row>
     <row r="65">
@@ -1461,112 +1461,112 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>205800000000</v>
+        <v>208190000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>205400000000</v>
+        <v>207200000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>200530000000</v>
+        <v>206580000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>198250000000</v>
+        <v>203030000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>197250000000</v>
+        <v>199260000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>196660000000</v>
+        <v>197400000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>190330000000</v>
+        <v>195380000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>188590000000</v>
+        <v>188280000000</v>
       </c>
     </row>
     <row r="73">
@@ -1581,37 +1581,37 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>184580000000</v>
+        <v>188130000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182520000000</v>
+        <v>180740000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>181930000000</v>
+        <v>179400000000</v>
       </c>
     </row>
     <row r="76">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>178400000000</v>
+        <v>177610000000</v>
       </c>
     </row>
     <row r="77">
@@ -1641,37 +1641,37 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>176540000000</v>
+        <v>177260000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>172860000000</v>
+        <v>172740000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>172450000000</v>
+        <v>169920000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>163220000000</v>
+        <v>164680000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>157500000000</v>
+        <v>158840000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>154560000000</v>
+        <v>153970000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,22 +1731,22 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>154430000000</v>
+        <v>153500000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>143990000000</v>
+        <v>148390000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,52 +1761,52 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>143910000000</v>
+        <v>145480000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>142570000000</v>
+        <v>144440000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>141060000000</v>
+        <v>143860000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>138990000000</v>
+        <v>139450000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137440000000</v>
+        <v>137150000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,37 +1836,37 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>134360000000</v>
+        <v>133320000000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>S&amp;P Global Inc</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>132920000000</v>
+        <v>132460000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S&amp;P Global Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>132340000000</v>
+        <v>132100000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>131100000000</v>
+        <v>131130000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>129390000000</v>
+        <v>128110000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>125730000000</v>
+        <v>123730000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,7 +1926,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>122710000000</v>
+        <v>121870000000</v>
       </c>
     </row>
     <row r="97">
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>122580000000</v>
+        <v>121370000000</v>
       </c>
     </row>
     <row r="98">
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>120180000000</v>
+        <v>121240000000</v>
       </c>
     </row>
     <row r="99">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119040000000</v>
+        <v>119920000000</v>
       </c>
     </row>
     <row r="100">
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117470000000</v>
+        <v>117650000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116720000000</v>
+        <v>113490000000</v>
       </c>
     </row>
     <row r="102">
@@ -2016,97 +2016,97 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>116150000000</v>
+        <v>113080000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>114360000000</v>
+        <v>113010000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>112810000000</v>
+        <v>111310000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>111590000000</v>
+        <v>111160000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>111190000000</v>
+        <v>110850000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>108790000000</v>
+        <v>110260000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Airbnb Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>101090000000</v>
+        <v>100290000000</v>
       </c>
     </row>
     <row r="109">
@@ -2121,37 +2121,37 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>100840000000</v>
+        <v>99970000000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Airbnb Inc</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>98610000000</v>
+        <v>99430000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>97420000000</v>
+        <v>99430000000</v>
       </c>
     </row>
     <row r="112">
@@ -2166,37 +2166,37 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>96660000000</v>
+        <v>97210000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93080000000</v>
+        <v>93530000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>91070000000</v>
+        <v>92860000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>90670000000</v>
+        <v>91440000000</v>
       </c>
     </row>
     <row r="116">
@@ -2226,37 +2226,37 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>90260000000</v>
+        <v>89860000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>88660000000</v>
+        <v>89540000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>87950000000</v>
+        <v>89290000000</v>
       </c>
     </row>
     <row r="119">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87770000000</v>
+        <v>87700000000</v>
       </c>
     </row>
     <row r="120">
@@ -2286,127 +2286,127 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>87260000000</v>
+        <v>87560000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>85200000000</v>
+        <v>87000000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>84020000000</v>
+        <v>85500000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>83030000000</v>
+        <v>84820000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>80290000000</v>
+        <v>83730000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>80260000000</v>
+        <v>79780000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>79140000000</v>
+        <v>79770000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>78820000000</v>
+        <v>78530000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>78310000000</v>
+        <v>77950000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73480000000</v>
+        <v>73090000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>67940000000</v>
+        <v>69580000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67480000000</v>
+        <v>67670000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67240000000</v>
+        <v>67000000000</v>
       </c>
     </row>
     <row r="133">
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>62710000000</v>
+        <v>62840000000</v>
       </c>
     </row>
     <row r="134">
@@ -2496,37 +2496,37 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62090000000</v>
+        <v>62660000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NU</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Nu Holdings Ltd</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59900000000</v>
+        <v>61270000000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NU</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Nu Holdings Ltd</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>59680000000</v>
+        <v>57820000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55790000000</v>
+        <v>55180000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,67 +2556,67 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>52350000000</v>
+        <v>52900000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>50600000000</v>
+        <v>51560000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>49740000000</v>
+        <v>50660000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49520000000</v>
+        <v>49570000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49220000000</v>
+        <v>49250000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47980000000</v>
+        <v>48380000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>46690000000</v>
+        <v>47900000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46340000000</v>
+        <v>47650000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,52 +2676,52 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>44980000000</v>
+        <v>45190000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>43030000000</v>
+        <v>43610000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>42500000000</v>
+        <v>43250000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ZS</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Zscaler Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>42420000000</v>
+        <v>42830000000</v>
       </c>
     </row>
     <row r="150">
@@ -2736,22 +2736,22 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42370000000</v>
+        <v>42620000000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ZS</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Zscaler Inc</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>42200000000</v>
+        <v>41710000000</v>
       </c>
     </row>
     <row r="152">
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>39260000000</v>
+        <v>39610000000</v>
       </c>
     </row>
     <row r="153">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>39090000000</v>
+        <v>38970000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>37300000000</v>
+        <v>37730000000</v>
       </c>
     </row>
     <row r="155">
@@ -2811,37 +2811,37 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>35410000000</v>
+        <v>36360000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>34900000000</v>
+        <v>35260000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>32860000000</v>
+        <v>35070000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32330000000</v>
+        <v>32150000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30750000000</v>
+        <v>30610000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28420000000</v>
+        <v>29250000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>26250000000</v>
+        <v>25920000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25210000000</v>
+        <v>25450000000</v>
       </c>
     </row>
     <row r="163">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24640000000</v>
+        <v>24860000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23270000000</v>
+        <v>23530000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23050000000</v>
+        <v>23070000000</v>
       </c>
     </row>
     <row r="166">
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>21180000000</v>
+        <v>22140000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,7 +2991,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20810000000</v>
+        <v>20850000000</v>
       </c>
     </row>
     <row r="168">
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18900000000</v>
+        <v>18950000000</v>
       </c>
     </row>
     <row r="169">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18480000000</v>
+        <v>18560000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18480000000</v>
+        <v>18060000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>14150000000</v>
+        <v>13930000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>11650000000</v>
+        <v>11850000000</v>
       </c>
     </row>
     <row r="173">
@@ -3081,22 +3081,22 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11100000000</v>
+        <v>11670000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11090000000</v>
+        <v>11470000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,22 +3111,22 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11090000000</v>
+        <v>11220000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10940000000</v>
+        <v>11220000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9680000000</v>
+        <v>9410000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8930000000</v>
+        <v>8910000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,52 +3171,52 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7270000000</v>
+        <v>7500000000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>CELH</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Zillow Group Inc</t>
+          <t>Celsius Holdings Inc</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7250000000</v>
+        <v>7080000000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>PRMB</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Celsius Holdings Inc</t>
+          <t>Primo Brands Corp</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7080000000</v>
+        <v>6990000000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PRMB</t>
+          <t>Z</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Primo Brands Corp</t>
+          <t>Zillow Group Inc</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6950000000</v>
+        <v>6960000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6510000000</v>
+        <v>6840000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6440000000</v>
+        <v>6400000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5900000000</v>
+        <v>6170000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,37 +3276,37 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5840000000</v>
+        <v>6000000000</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OKLO</t>
+          <t>CRSP</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Oklo Inc</t>
+          <t>CRISPR Therapeutics AG</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5080000000</v>
+        <v>5230000000</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>CRSP</t>
+          <t>OKLO</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CRISPR Therapeutics AG</t>
+          <t>Oklo Inc</t>
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4980000000</v>
+        <v>5040000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4360000000</v>
+        <v>4310000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4150000000</v>
+        <v>4140000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3870000000</v>
+        <v>3990000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3550000000</v>
+        <v>3510000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2740000000</v>
+        <v>2840000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,37 +3396,37 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2450000000</v>
+        <v>2440000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2420000000</v>
+        <v>2350000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2310000000</v>
+        <v>2320000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,37 +3441,37 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2240000000</v>
+        <v>2290000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>C3.ai Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1990000000</v>
+        <v>1980000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>C3.ai Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1980000000</v>
+        <v>1970000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1550000000</v>
+        <v>1560000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1170000000</v>
+        <v>1250000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1110000000</v>
+        <v>1140000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>892730000</v>
+        <v>880230000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>662640000</v>
+        <v>665320000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>315810000</v>
+        <v>311220000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5017920000000</v>
+        <v>5092060000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,37 +576,37 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5190660000000</v>
+        <v>5149210000000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alphabet Inc</t>
+          <t>Microsoft Corp</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3962250000000</v>
+        <v>3937050000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Alphabet Inc</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3943510000000</v>
+        <v>3468420000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2746200000000</v>
+        <v>2629600000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2279510000000</v>
+        <v>2239570000000</v>
       </c>
     </row>
     <row r="11">
@@ -651,37 +651,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1679410000000</v>
+        <v>1646900000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Meta Platforms Inc</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1597780000000</v>
+        <v>1596420000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Meta Platforms Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1565670000000</v>
+        <v>1594150000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1212750000000</v>
+        <v>1293140000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1154580000000</v>
+        <v>1160880000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,37 +726,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1112450000000</v>
+        <v>1057050000000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>Walmart Inc</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>944290000000</v>
+        <v>961970000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Walmart Inc</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>942290000000</v>
+        <v>924670000000</v>
       </c>
     </row>
     <row r="19">
@@ -771,37 +771,37 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>901920000000</v>
+        <v>913300000000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ExxonMobil Holdings Corp</t>
+          <t>Visa Inc</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>748450000000</v>
+        <v>776650000000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Visa Inc</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>747940000000</v>
+        <v>753670000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>652480000000</v>
+        <v>662490000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>640900000000</v>
+        <v>645850000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>534640000000</v>
+        <v>556880000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>505380000000</v>
+        <v>513860000000</v>
       </c>
     </row>
     <row r="26">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>472950000000</v>
+        <v>472010000000</v>
       </c>
     </row>
     <row r="27">
@@ -891,52 +891,52 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>452850000000</v>
+        <v>457310000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>437050000000</v>
+        <v>441390000000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Cisco Systems Inc</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>435480000000</v>
+        <v>428130000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cisco Systems Inc</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>434830000000</v>
+        <v>421990000000</v>
       </c>
     </row>
     <row r="31">
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>394670000000</v>
+        <v>399360000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>366810000000</v>
+        <v>372210000000</v>
       </c>
     </row>
     <row r="33">
@@ -981,37 +981,37 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>365410000000</v>
+        <v>368830000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bank Of America Corp</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>352020000000</v>
+        <v>361020000000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Bank Of America Corp</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>347700000000</v>
+        <v>354030000000</v>
       </c>
     </row>
     <row r="36">
@@ -1026,142 +1026,142 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>330140000000</v>
+        <v>334630000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>327920000000</v>
+        <v>328220000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Palo Alto Networks Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>322690000000</v>
+        <v>324980000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>317060000000</v>
+        <v>323490000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>316830000000</v>
+        <v>317780000000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>Palo Alto Networks Inc</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>315850000000</v>
+        <v>311600000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>313960000000</v>
+        <v>305910000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>311170000000</v>
+        <v>302340000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>299030000000</v>
+        <v>298410000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>298610000000</v>
+        <v>297590000000</v>
       </c>
     </row>
     <row r="46">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>285710000000</v>
+        <v>294900000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,22 +1191,22 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>283110000000</v>
+        <v>285960000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>273040000000</v>
+        <v>270480000000</v>
       </c>
     </row>
     <row r="49">
@@ -1221,52 +1221,52 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>269380000000</v>
+        <v>270130000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>267490000000</v>
+        <v>269080000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>264270000000</v>
+        <v>267400000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>262890000000</v>
+        <v>264260000000</v>
       </c>
     </row>
     <row r="53">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>260360000000</v>
+        <v>262220000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,67 +1296,67 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>254550000000</v>
+        <v>254800000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>251940000000</v>
+        <v>254570000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BABA</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alibaba Group Holding Ltd ADR</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>251160000000</v>
+        <v>249090000000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>BABA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>Alibaba Group Holding Ltd ADR</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>251150000000</v>
+        <v>247630000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>244270000000</v>
+        <v>244330000000</v>
       </c>
     </row>
     <row r="59">
@@ -1371,67 +1371,67 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>239320000000</v>
+        <v>244110000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>234250000000</v>
+        <v>236460000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>233850000000</v>
+        <v>232850000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>230740000000</v>
+        <v>231940000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>216400000000</v>
+        <v>218500000000</v>
       </c>
     </row>
     <row r="64">
@@ -1446,37 +1446,37 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>213200000000</v>
+        <v>217060000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>208190000000</v>
+        <v>214690000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>207200000000</v>
+        <v>210950000000</v>
       </c>
     </row>
     <row r="67">
@@ -1491,97 +1491,97 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>206580000000</v>
+        <v>209140000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>203030000000</v>
+        <v>205350000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>199260000000</v>
+        <v>197990000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>197400000000</v>
+        <v>192230000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>195380000000</v>
+        <v>191510000000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>Blackrock Inc</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>188280000000</v>
+        <v>191110000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Blackrock Inc</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>188130000000</v>
+        <v>190030000000</v>
       </c>
     </row>
     <row r="74">
@@ -1596,52 +1596,52 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>180740000000</v>
+        <v>182320000000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>McDonald's Corp</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>179400000000</v>
+        <v>182130000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>177610000000</v>
+        <v>181400000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>McDonald's Corp</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>177260000000</v>
+        <v>180950000000</v>
       </c>
     </row>
     <row r="78">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>172740000000</v>
+        <v>177950000000</v>
       </c>
     </row>
     <row r="79">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>169920000000</v>
+        <v>172270000000</v>
       </c>
     </row>
     <row r="80">
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>164680000000</v>
+        <v>166720000000</v>
       </c>
     </row>
     <row r="81">
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>158840000000</v>
+        <v>157990000000</v>
       </c>
     </row>
     <row r="82">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>153970000000</v>
+        <v>155560000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,22 +1731,22 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>153500000000</v>
+        <v>154720000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>148390000000</v>
+        <v>148810000000</v>
       </c>
     </row>
     <row r="85">
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>145480000000</v>
+        <v>148670000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>144440000000</v>
+        <v>148010000000</v>
       </c>
     </row>
     <row r="87">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>143860000000</v>
+        <v>146120000000</v>
       </c>
     </row>
     <row r="88">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>139450000000</v>
+        <v>140930000000</v>
       </c>
     </row>
     <row r="89">
@@ -1821,22 +1821,22 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>137150000000</v>
+        <v>138580000000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Boeing Co</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>133320000000</v>
+        <v>136820000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,22 +1851,22 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>132460000000</v>
+        <v>135800000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Boeing Co</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>132100000000</v>
+        <v>134280000000</v>
       </c>
     </row>
     <row r="93">
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>131130000000</v>
+        <v>133760000000</v>
       </c>
     </row>
     <row r="94">
@@ -1896,202 +1896,202 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>128110000000</v>
+        <v>130960000000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>Altria Group Inc</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>123730000000</v>
+        <v>128150000000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Altria Group Inc</t>
+          <t>Bristol-Myers Squibb Co</t>
         </is>
       </c>
       <c r="L96" t="n">
-        <v>121870000000</v>
+        <v>125400000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>121370000000</v>
+        <v>124220000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>121240000000</v>
+        <v>124100000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>119920000000</v>
+        <v>120280000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>117650000000</v>
+        <v>116520000000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>Lowe's Cos. Inc</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>113490000000</v>
+        <v>116300000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>113080000000</v>
+        <v>114730000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GLW</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Corning Inc</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>113010000000</v>
+        <v>113360000000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lowe's Cos. Inc</t>
+          <t>Booking Holdings Inc</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>111310000000</v>
+        <v>113030000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Booking Holdings Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>111160000000</v>
+        <v>112850000000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>GLW</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Corning Inc</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>110850000000</v>
+        <v>111020000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>110260000000</v>
+        <v>110490000000</v>
       </c>
     </row>
     <row r="108">
@@ -2106,22 +2106,22 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>100290000000</v>
+        <v>103510000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>99970000000</v>
+        <v>102290000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,37 +2136,37 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99430000000</v>
+        <v>99670000000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Adobe Inc</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>99430000000</v>
+        <v>96570000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Adobe Inc</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>97210000000</v>
+        <v>95460000000</v>
       </c>
     </row>
     <row r="113">
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>93530000000</v>
+        <v>94680000000</v>
       </c>
     </row>
     <row r="114">
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>92860000000</v>
+        <v>94480000000</v>
       </c>
     </row>
     <row r="115">
@@ -2211,142 +2211,142 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>91440000000</v>
+        <v>93690000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>89860000000</v>
+        <v>91650000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>89540000000</v>
+        <v>91530000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>89290000000</v>
+        <v>91310000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>87700000000</v>
+        <v>91180000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>87560000000</v>
+        <v>88930000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>87000000000</v>
+        <v>88510000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>85500000000</v>
+        <v>85310000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>84820000000</v>
+        <v>84300000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>83730000000</v>
+        <v>84160000000</v>
       </c>
     </row>
     <row r="125">
@@ -2361,37 +2361,37 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>79780000000</v>
+        <v>83060000000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Northrop Grumman Corp</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>79770000000</v>
+        <v>79890000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Northrop Grumman Corp</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>78530000000</v>
+        <v>79420000000</v>
       </c>
     </row>
     <row r="128">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>77950000000</v>
+        <v>78850000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>73090000000</v>
+        <v>74260000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,67 +2436,67 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>69580000000</v>
+        <v>72310000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>67670000000</v>
+        <v>70010000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>67000000000</v>
+        <v>68970000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>62840000000</v>
+        <v>63670000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62660000000</v>
+        <v>62990000000</v>
       </c>
     </row>
     <row r="135">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>61270000000</v>
+        <v>59770000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>57820000000</v>
+        <v>58210000000</v>
       </c>
     </row>
     <row r="137">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>55180000000</v>
+        <v>57070000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,112 +2556,112 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>52900000000</v>
+        <v>54440000000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Autodesk Inc</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>51560000000</v>
+        <v>50520000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Autodesk Inc</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50660000000</v>
+        <v>50390000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49570000000</v>
+        <v>49290000000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>PayPal Holdings Inc</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>49250000000</v>
+        <v>47310000000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PayPal Holdings Inc</t>
+          <t>Vistra Corp</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>48380000000</v>
+        <v>47310000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vistra Corp</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47900000000</v>
+        <v>47110000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>47650000000</v>
+        <v>46760000000</v>
       </c>
     </row>
     <row r="146">
@@ -2676,67 +2676,67 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>45190000000</v>
+        <v>46230000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>43610000000</v>
+        <v>44230000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>43250000000</v>
+        <v>43800000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>42830000000</v>
+        <v>43400000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42620000000</v>
+        <v>42370000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,37 +2751,37 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>41710000000</v>
+        <v>40410000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>39610000000</v>
+        <v>39580000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>38970000000</v>
+        <v>39420000000</v>
       </c>
     </row>
     <row r="154">
@@ -2796,52 +2796,52 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>37730000000</v>
+        <v>38780000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>36360000000</v>
+        <v>37150000000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Rocket Lab Corp</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>35260000000</v>
+        <v>35370000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Rocket Lab Corp</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>35070000000</v>
+        <v>33500000000</v>
       </c>
     </row>
     <row r="158">
@@ -2856,7 +2856,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32150000000</v>
+        <v>32560000000</v>
       </c>
     </row>
     <row r="159">
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30610000000</v>
+        <v>30820000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,97 +2886,97 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>29250000000</v>
+        <v>28500000000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Fiserv Inc</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25920000000</v>
+        <v>25780000000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Fiserv Inc</t>
+          <t>Affirm Holdings Inc</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25450000000</v>
+        <v>25370000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Affirm Holdings Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24860000000</v>
+        <v>24930000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23530000000</v>
+        <v>23220000000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>SoFi Technologies Inc</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>23070000000</v>
+        <v>22740000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>SoFi Technologies Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22140000000</v>
+        <v>22620000000</v>
       </c>
     </row>
     <row r="167">
@@ -2991,37 +2991,37 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20850000000</v>
+        <v>20410000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>18950000000</v>
+        <v>19200000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>18560000000</v>
+        <v>19010000000</v>
       </c>
     </row>
     <row r="170">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18060000000</v>
+        <v>18430000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,52 +3051,52 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13930000000</v>
+        <v>13620000000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>TXRH</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Texas Roadhouse Inc</t>
         </is>
       </c>
       <c r="L172" t="n">
-        <v>11850000000</v>
+        <v>12010000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>IREN Ltd</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11670000000</v>
+        <v>11280000000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TXRH</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Texas Roadhouse Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11470000000</v>
+        <v>11260000000</v>
       </c>
     </row>
     <row r="175">
@@ -3111,22 +3111,22 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11220000000</v>
+        <v>11260000000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>IREN Ltd</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>11220000000</v>
+        <v>10620000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9410000000</v>
+        <v>9500000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8910000000</v>
+        <v>8950000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7500000000</v>
+        <v>7680000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7080000000</v>
+        <v>7130000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>6990000000</v>
+        <v>7050000000</v>
       </c>
     </row>
     <row r="182">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>6960000000</v>
+        <v>7010000000</v>
       </c>
     </row>
     <row r="183">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6840000000</v>
+        <v>6920000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6400000000</v>
+        <v>6850000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>6170000000</v>
+        <v>5870000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>6000000000</v>
+        <v>5450000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5230000000</v>
+        <v>5250000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>5040000000</v>
+        <v>4990000000</v>
       </c>
     </row>
     <row r="189">
@@ -3321,7 +3321,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4310000000</v>
+        <v>4080000000</v>
       </c>
     </row>
     <row r="190">
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4140000000</v>
+        <v>4030000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>3990000000</v>
+        <v>4010000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3510000000</v>
+        <v>3550000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2840000000</v>
+        <v>2770000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2440000000</v>
+        <v>2540000000</v>
       </c>
     </row>
     <row r="195">
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2350000000</v>
+        <v>2420000000</v>
       </c>
     </row>
     <row r="196">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2320000000</v>
+        <v>2330000000</v>
       </c>
     </row>
     <row r="197">
@@ -3441,67 +3441,67 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2290000000</v>
+        <v>2260000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>C3.ai Inc</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1980000000</v>
+        <v>2060000000</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>C3.ai Inc</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1970000000</v>
+        <v>1960000000</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>TDOC</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Quantum Computing Inc</t>
+          <t>Teladoc Health Inc</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1560000000</v>
+        <v>1590000000</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TDOC</t>
+          <t>QUBT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Teladoc Health Inc</t>
+          <t>Quantum Computing Inc</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1250000000</v>
+        <v>1540000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1140000000</v>
+        <v>1120000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>880230000</v>
+        <v>897030000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>665320000</v>
+        <v>655650000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>311220000</v>
+        <v>326550000</v>
       </c>
     </row>
     <row r="206">

--- a/data1/final_stock_data.xlsx
+++ b/data1/final_stock_data.xlsx
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5092060000000</v>
+        <v>5029590000000</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5149210000000</v>
+        <v>4931820000000</v>
       </c>
     </row>
     <row r="7">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3937050000000</v>
+        <v>3875800000000</v>
       </c>
     </row>
     <row r="8">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3468420000000</v>
+        <v>3410580000000</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2629600000000</v>
+        <v>2592490000000</v>
       </c>
     </row>
     <row r="10">
@@ -636,22 +636,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2239570000000</v>
+        <v>2106390000000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Broadcom Inc</t>
+          <t>Tesla Inc</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1646900000000</v>
+        <v>1580350000000</v>
       </c>
     </row>
     <row r="12">
@@ -666,22 +666,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1596420000000</v>
+        <v>1572060000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tesla Inc</t>
+          <t>Broadcom Inc</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1594150000000</v>
+        <v>1556590000000</v>
       </c>
     </row>
     <row r="14">
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1293140000000</v>
+        <v>1334410000000</v>
       </c>
     </row>
     <row r="15">
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1160880000000</v>
+        <v>1163540000000</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1057050000000</v>
+        <v>1001020000000</v>
       </c>
     </row>
     <row r="17">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>961970000000</v>
+        <v>979900000000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices Inc</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>924670000000</v>
+        <v>895920000000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Advanced Micro Devices Inc</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>913300000000</v>
+        <v>824070000000</v>
       </c>
     </row>
     <row r="20">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>776650000000</v>
+        <v>782420000000</v>
       </c>
     </row>
     <row r="21">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>753670000000</v>
+        <v>769960000000</v>
       </c>
     </row>
     <row r="22">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>662490000000</v>
+        <v>657680000000</v>
       </c>
     </row>
     <row r="23">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>645850000000</v>
+        <v>603530000000</v>
       </c>
     </row>
     <row r="24">
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>556880000000</v>
+        <v>559190000000</v>
       </c>
     </row>
     <row r="25">
@@ -861,52 +861,52 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>513860000000</v>
+        <v>521110000000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc</t>
+          <t>Chevron Corp</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>472010000000</v>
+        <v>465330000000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chevron Corp</t>
+          <t>Costco Wholesale Corp</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>457310000000</v>
+        <v>448570000000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corp</t>
+          <t>Palantir Technologies Inc</t>
         </is>
       </c>
       <c r="L28" t="n">
-        <v>441390000000</v>
+        <v>442430000000</v>
       </c>
     </row>
     <row r="29">
@@ -921,37 +921,37 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>428130000000</v>
+        <v>412040000000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORCL</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oracle Corp</t>
+          <t>Coca-Cola Co</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>421990000000</v>
+        <v>404720000000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>ORCL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Coca-Cola Co</t>
+          <t>Oracle Corp</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>399360000000</v>
+        <v>395110000000</v>
       </c>
     </row>
     <row r="32">
@@ -966,37 +966,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>372210000000</v>
+        <v>374480000000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Unitedhealth Group Inc</t>
+          <t>Merck &amp; Co Inc</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>368830000000</v>
+        <v>368890000000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Merck &amp; Co Inc</t>
+          <t>Unitedhealth Group Inc</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>361020000000</v>
+        <v>365290000000</v>
       </c>
     </row>
     <row r="35">
@@ -1011,82 +1011,82 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>354030000000</v>
+        <v>346200000000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Applied Materials Inc</t>
+          <t>Home Depot Inc</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>334630000000</v>
+        <v>328440000000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Home Depot Inc</t>
+          <t>Philip Morris International Inc</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>328220000000</v>
+        <v>325430000000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Philip Morris International Inc</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>324980000000</v>
+        <v>311870000000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Applied Materials Inc</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>323490000000</v>
+        <v>309570000000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SHEL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lam Research Corp</t>
+          <t>Shell Plc ADR</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>317780000000</v>
+        <v>308810000000</v>
       </c>
     </row>
     <row r="41">
@@ -1101,82 +1101,82 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>311600000000</v>
+        <v>299560000000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SHEL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shell Plc ADR</t>
+          <t>Lam Research Corp</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>305910000000</v>
+        <v>298690000000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dell Technologies Inc</t>
+          <t>Novartis AG ADR</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>302340000000</v>
+        <v>294330000000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>AZN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Astrazeneca plc</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>298410000000</v>
+        <v>289480000000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Caterpillar Inc</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="L45" t="n">
-        <v>297590000000</v>
+        <v>289460000000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Novartis AG ADR</t>
+          <t>Caterpillar Inc</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>294900000000</v>
+        <v>286260000000</v>
       </c>
     </row>
     <row r="47">
@@ -1191,97 +1191,97 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>285960000000</v>
+        <v>274900000000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Astrazeneca plc</t>
+          <t>Dell Technologies Inc</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>270480000000</v>
+        <v>269780000000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Goldman Sachs Group Inc</t>
+          <t>RTX Corp</t>
         </is>
       </c>
       <c r="L49" t="n">
-        <v>270130000000</v>
+        <v>269620000000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RTX Corp</t>
+          <t>Sap SE ADR</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>269080000000</v>
+        <v>265340000000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Crowdstrike Holdings Inc</t>
+          <t>Goldman Sachs Group Inc</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>267400000000</v>
+        <v>260470000000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>TMO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sap SE ADR</t>
+          <t>Thermo Fisher Scientific Inc</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>264260000000</v>
+        <v>257710000000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TMO</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific Inc</t>
+          <t>Crowdstrike Holdings Inc</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>262220000000</v>
+        <v>256420000000</v>
       </c>
     </row>
     <row r="54">
@@ -1296,37 +1296,37 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>254800000000</v>
+        <v>254920000000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wells Fargo &amp; Co</t>
+          <t>AMGEN Inc</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>254570000000</v>
+        <v>251940000000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMGEN Inc</t>
+          <t>Wells Fargo &amp; Co</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>249090000000</v>
+        <v>250350000000</v>
       </c>
     </row>
     <row r="57">
@@ -1341,217 +1341,217 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>247630000000</v>
+        <v>243900000000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Arm Holdings Plc ADR</t>
+          <t>International Business Machines Corp</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>244330000000</v>
+        <v>243660000000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>International Business Machines Corp</t>
+          <t>Linde Plc</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>244110000000</v>
+        <v>237050000000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GE Vernova Inc</t>
+          <t>Toyota Motor Corp ADR</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>236460000000</v>
+        <v>231760000000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Toyota Motor Corp ADR</t>
+          <t>GE Vernova Inc</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>232850000000</v>
+        <v>227060000000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Linde Plc</t>
+          <t>Arm Holdings Plc ADR</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>231940000000</v>
+        <v>219980000000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KLA Corp</t>
+          <t>American Express Co</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>218500000000</v>
+        <v>213980000000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>American Express Co</t>
+          <t>TotalEnergies SE</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>217060000000</v>
+        <v>212030000000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Shopify Inc</t>
+          <t>Gilead Sciences Inc</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>214690000000</v>
+        <v>211640000000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Citigroup Inc</t>
+          <t>KLA Corp</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>210950000000</v>
+        <v>206070000000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TotalEnergies SE</t>
+          <t>Citigroup Inc</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>209140000000</v>
+        <v>205720000000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Shopify Inc</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>205350000000</v>
+        <v>202600000000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qualcomm Inc</t>
+          <t>Walt Disney Co</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>197990000000</v>
+        <v>191560000000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sandisk Corp</t>
+          <t>Salesforce Inc</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>192230000000</v>
+        <v>188610000000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Walt Disney Co</t>
+          <t>PepsiCo Inc</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>191510000000</v>
+        <v>187160000000</v>
       </c>
     </row>
     <row r="72">
@@ -1566,37 +1566,37 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>191110000000</v>
+        <v>186450000000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Salesforce Inc</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>190030000000</v>
+        <v>185410000000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PepsiCo Inc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>182320000000</v>
+        <v>183770000000</v>
       </c>
     </row>
     <row r="75">
@@ -1611,112 +1611,112 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>182130000000</v>
+        <v>182660000000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Deere &amp; Co</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>181400000000</v>
+        <v>182130000000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Qualcomm Inc</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>180950000000</v>
+        <v>175970000000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deere &amp; Co</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>177950000000</v>
+        <v>175570000000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>Sandisk Corp</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>172270000000</v>
+        <v>166340000000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Danaher Corp</t>
+          <t>T-Mobile US Inc</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>166720000000</v>
+        <v>165710000000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T-Mobile US Inc</t>
+          <t>Danaher Corp</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>157990000000</v>
+        <v>163380000000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Intuitive Surgical Inc</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>155560000000</v>
+        <v>152630000000</v>
       </c>
     </row>
     <row r="83">
@@ -1731,97 +1731,97 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>154720000000</v>
+        <v>152270000000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Blackstone Inc</t>
+          <t>Intuitive Surgical Inc</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>148810000000</v>
+        <v>149750000000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lockheed Martin Corp</t>
+          <t>Blackstone Inc</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>148670000000</v>
+        <v>147360000000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Western Digital Corp</t>
+          <t>Lockheed Martin Corp</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>148010000000</v>
+        <v>147140000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>AT&amp;T Inc</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>146120000000</v>
+        <v>144230000000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AT&amp;T Inc</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>140930000000</v>
+        <v>139120000000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Western Digital Corp</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>138580000000</v>
+        <v>137040000000</v>
       </c>
     </row>
     <row r="90">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>136820000000</v>
+        <v>135940000000</v>
       </c>
     </row>
     <row r="91">
@@ -1851,52 +1851,52 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>135800000000</v>
+        <v>135250000000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Uber Technologies Inc</t>
+          <t>Progressive Corp</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>134280000000</v>
+        <v>134400000000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>NVO</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Progressive Corp</t>
+          <t>Novo Nordisk ADR</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>133760000000</v>
+        <v>133840000000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>NVO</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Novo Nordisk ADR</t>
+          <t>Uber Technologies Inc</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>130960000000</v>
+        <v>133280000000</v>
       </c>
     </row>
     <row r="95">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>128150000000</v>
+        <v>130290000000</v>
       </c>
     </row>
     <row r="96">
@@ -1926,67 +1926,67 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>125400000000</v>
+        <v>127630000000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Medtronic Plc</t>
+          <t>Prologis Inc</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>124220000000</v>
+        <v>124090000000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Prologis Inc</t>
+          <t>Medtronic Plc</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>124100000000</v>
+        <v>123490000000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>SPOT</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Starbucks Corp</t>
+          <t>Spotify Technology SA</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>120280000000</v>
+        <v>122180000000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SNOW</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Snowflake Inc</t>
+          <t>Starbucks Corp</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>116520000000</v>
+        <v>118180000000</v>
       </c>
     </row>
     <row r="101">
@@ -2001,37 +2001,37 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>116300000000</v>
+        <v>117300000000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SPOT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Spotify Technology SA</t>
+          <t>Automatic Data Processing Inc</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>114730000000</v>
+        <v>116430000000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>PDD</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Automatic Data Processing Inc</t>
+          <t>PDD Holdings Inc ADR</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>113360000000</v>
+        <v>111890000000</v>
       </c>
     </row>
     <row r="104">
@@ -2046,22 +2046,22 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>113030000000</v>
+        <v>111300000000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PDD</t>
+          <t>SNOW</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PDD Holdings Inc ADR</t>
+          <t>Snowflake Inc</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>112850000000</v>
+        <v>107990000000</v>
       </c>
     </row>
     <row r="106">
@@ -2076,52 +2076,52 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>111020000000</v>
+        <v>106220000000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NET</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cloudflare Inc</t>
+          <t>HCA Healthcare Inc</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>110490000000</v>
+        <v>102450000000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HCA Healthcare Inc</t>
+          <t>Equinix Inc</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>103510000000</v>
+        <v>100340000000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>NET</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Equinix Inc</t>
+          <t>Cloudflare Inc</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>102290000000</v>
+        <v>99950000000</v>
       </c>
     </row>
     <row r="110">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>99670000000</v>
+        <v>98430000000</v>
       </c>
     </row>
     <row r="111">
@@ -2151,217 +2151,217 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>96570000000</v>
+        <v>97390000000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Datadog Inc</t>
+          <t>Regeneron Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>95460000000</v>
+        <v>95530000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>MMC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>94680000000</v>
+        <v>95400000000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Intercontinental Exchange Inc</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>94480000000</v>
+        <v>94360000000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MMC</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>93690000000</v>
+        <v>92630000000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3M Co</t>
+          <t>United Parcel Service Inc</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>91650000000</v>
+        <v>92100000000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange Inc</t>
+          <t>Intuit Inc</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>91530000000</v>
+        <v>91150000000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>United Parcel Service Inc</t>
+          <t>Elevance Health Inc</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>91310000000</v>
+        <v>90760000000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Elevance Health Inc</t>
+          <t>3M Co</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>91180000000</v>
+        <v>90090000000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>88930000000</v>
+        <v>89530000000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Intuit Inc</t>
+          <t>Moderna Inc</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>88510000000</v>
+        <v>88520000000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>APP</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Applovin Corp</t>
+          <t>Datadog Inc</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>85310000000</v>
+        <v>84480000000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>MELI</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals Inc</t>
+          <t>MercadoLibre Inc</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>84300000000</v>
+        <v>82360000000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>MercadoLibre Inc</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>84160000000</v>
+        <v>82160000000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>SLB Ltd</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>83060000000</v>
+        <v>79320000000</v>
       </c>
     </row>
     <row r="126">
@@ -2376,37 +2376,37 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>79890000000</v>
+        <v>79210000000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SLB Ltd</t>
+          <t>Cigna Group</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>79420000000</v>
+        <v>78800000000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>APP</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cigna Group</t>
+          <t>Applovin Corp</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>78850000000</v>
+        <v>76470000000</v>
       </c>
     </row>
     <row r="129">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>74260000000</v>
+        <v>75960000000</v>
       </c>
     </row>
     <row r="130">
@@ -2436,82 +2436,82 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>72310000000</v>
+        <v>73730000000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Apollo Global Management Inc</t>
+          <t>Target Corp</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>70010000000</v>
+        <v>70130000000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Target Corp</t>
+          <t>Apollo Global Management Inc</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>68970000000</v>
+        <v>68410000000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ferrari NV</t>
+          <t>Occidental Petroleum Corp</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>63670000000</v>
+        <v>63980000000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Occidental Petroleum Corp</t>
+          <t>Ferrari NV</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>62990000000</v>
+        <v>63070000000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MSTR</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Strategy Inc</t>
+          <t>Nike Inc</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>59770000000</v>
+        <v>57440000000</v>
       </c>
     </row>
     <row r="136">
@@ -2526,22 +2526,22 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>58210000000</v>
+        <v>56080000000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>MSTR</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Nike Inc</t>
+          <t>Strategy Inc</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>57070000000</v>
+        <v>55080000000</v>
       </c>
     </row>
     <row r="138">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>54440000000</v>
+        <v>53030000000</v>
       </c>
     </row>
     <row r="139">
@@ -2571,37 +2571,37 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>50520000000</v>
+        <v>52170000000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Astera Labs Inc</t>
+          <t>Ford Motor Co</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>50390000000</v>
+        <v>48850000000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ford Motor Co</t>
+          <t>Workday Inc</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>49290000000</v>
+        <v>47670000000</v>
       </c>
     </row>
     <row r="142">
@@ -2616,7 +2616,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>47310000000</v>
+        <v>47360000000</v>
       </c>
     </row>
     <row r="143">
@@ -2631,112 +2631,112 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>47310000000</v>
+        <v>46440000000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Workday Inc</t>
+          <t>Block Inc</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>47110000000</v>
+        <v>45790000000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Nebius Group NV</t>
+          <t>Astera Labs Inc</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>46760000000</v>
+        <v>44880000000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Block Inc</t>
+          <t>MSCI Inc</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>46230000000</v>
+        <v>44570000000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>MSCI Inc</t>
+          <t>Sea Ltd ADR</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>44230000000</v>
+        <v>42090000000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Illumina Inc</t>
+          <t>Nebius Group NV</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>43800000000</v>
+        <v>41900000000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sea Ltd ADR</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>43400000000</v>
+        <v>40350000000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Coinbase Global Inc</t>
+          <t>Estee Lauder Cos. Inc</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>42370000000</v>
+        <v>39580000000</v>
       </c>
     </row>
     <row r="151">
@@ -2751,67 +2751,67 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40410000000</v>
+        <v>38780000000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Carnival Corp Ltd</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>39580000000</v>
+        <v>38770000000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Estee Lauder Cos. Inc</t>
+          <t>Coinbase Global Inc</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>39420000000</v>
+        <v>37870000000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Carnival Corp Ltd</t>
+          <t>Illumina Inc</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>38780000000</v>
+        <v>35630000000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>TWLO</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Twilio Inc</t>
+          <t>Zoetis Inc</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>37150000000</v>
+        <v>32940000000</v>
       </c>
     </row>
     <row r="156">
@@ -2826,52 +2826,52 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>35370000000</v>
+        <v>32750000000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CRWV</t>
+          <t>TWLO</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>Twilio Inc</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>33500000000</v>
+        <v>31490000000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Zoetis Inc</t>
+          <t>JD.com Inc ADR</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>32560000000</v>
+        <v>30880000000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>CRWV</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JD.com Inc ADR</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>30820000000</v>
+        <v>30260000000</v>
       </c>
     </row>
     <row r="160">
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>28500000000</v>
+        <v>27870000000</v>
       </c>
     </row>
     <row r="161">
@@ -2901,7 +2901,7 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>25780000000</v>
+        <v>26600000000</v>
       </c>
     </row>
     <row r="162">
@@ -2916,37 +2916,37 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>25370000000</v>
+        <v>24910000000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>ROKU</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Reddit Inc</t>
+          <t>Roku Inc</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>24930000000</v>
+        <v>23040000000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ROKU</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Roku Inc</t>
+          <t>Super Micro Computer Inc</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>23220000000</v>
+        <v>21650000000</v>
       </c>
     </row>
     <row r="165">
@@ -2961,82 +2961,82 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>22740000000</v>
+        <v>21650000000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Super Micro Computer Inc</t>
+          <t>Charter Communications Inc</t>
         </is>
       </c>
       <c r="L166" t="n">
-        <v>22620000000</v>
+        <v>19640000000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CRCL</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Circle Internet Group Inc</t>
+          <t>First Solar Inc</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>20410000000</v>
+        <v>18740000000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>DKNG</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Charter Communications Inc</t>
+          <t>DraftKings Inc</t>
         </is>
       </c>
       <c r="L168" t="n">
-        <v>19200000000</v>
+        <v>18600000000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>CRCL</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>First Solar Inc</t>
+          <t>Circle Internet Group Inc</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>19010000000</v>
+        <v>18510000000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>DKNG</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>DraftKings Inc</t>
+          <t>Reddit Inc</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>18430000000</v>
+        <v>17650000000</v>
       </c>
     </row>
     <row r="171">
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>13620000000</v>
+        <v>12900000000</v>
       </c>
     </row>
     <row r="172">
@@ -3066,22 +3066,22 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>12010000000</v>
+        <v>11980000000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PINS</t>
+          <t>GRAB</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Pinterest Inc</t>
+          <t>Grab Holdings Limited</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>11280000000</v>
+        <v>11050000000</v>
       </c>
     </row>
     <row r="174">
@@ -3096,22 +3096,22 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>11260000000</v>
+        <v>11050000000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GRAB</t>
+          <t>PINS</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Grab Holdings Limited</t>
+          <t>Pinterest Inc</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>11260000000</v>
+        <v>10960000000</v>
       </c>
     </row>
     <row r="176">
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>10620000000</v>
+        <v>9690000000</v>
       </c>
     </row>
     <row r="177">
@@ -3141,7 +3141,7 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>9500000000</v>
+        <v>9380000000</v>
       </c>
     </row>
     <row r="178">
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>8950000000</v>
+        <v>8750000000</v>
       </c>
     </row>
     <row r="179">
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>7680000000</v>
+        <v>7490000000</v>
       </c>
     </row>
     <row r="180">
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>7130000000</v>
+        <v>7370000000</v>
       </c>
     </row>
     <row r="181">
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>7050000000</v>
+        <v>7140000000</v>
       </c>
     </row>
     <row r="182">
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>6920000000</v>
+        <v>6460000000</v>
       </c>
     </row>
     <row r="184">
@@ -3246,7 +3246,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>6850000000</v>
+        <v>6410000000</v>
       </c>
     </row>
     <row r="185">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>5870000000</v>
+        <v>5390000000</v>
       </c>
     </row>
     <row r="186">
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>5450000000</v>
+        <v>5070000000</v>
       </c>
     </row>
     <row r="187">
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>5250000000</v>
+        <v>4970000000</v>
       </c>
     </row>
     <row r="188">
@@ -3306,37 +3306,37 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4990000000</v>
+        <v>4700000000</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FSLY</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Fastly Inc</t>
+          <t>Rigetti Computing Inc</t>
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4080000000</v>
+        <v>3750000000</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>FSLY</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Rigetti Computing Inc</t>
+          <t>Fastly Inc</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4030000000</v>
+        <v>3680000000</v>
       </c>
     </row>
     <row r="191">
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4010000000</v>
+        <v>3680000000</v>
       </c>
     </row>
     <row r="192">
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>3550000000</v>
+        <v>3320000000</v>
       </c>
     </row>
     <row r="193">
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2770000000</v>
+        <v>2620000000</v>
       </c>
     </row>
     <row r="194">
@@ -3396,67 +3396,67 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2540000000</v>
+        <v>2420000000</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>TMDX</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Upstart Holdings Inc</t>
+          <t>Transmedics Group Inc</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>2420000000</v>
+        <v>2290000000</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TMDX</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Transmedics Group Inc</t>
+          <t>Upstart Holdings Inc</t>
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2330000000</v>
+        <v>2240000000</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>LEU</t>
+          <t>PENN</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Centrus Energy Corp</t>
+          <t>PENN Entertainment Inc</t>
         </is>
       </c>
       <c r="L197" t="n">
-        <v>2260000000</v>
+        <v>2130000000</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PENN</t>
+          <t>LEU</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PENN Entertainment Inc</t>
+          <t>Centrus Energy Corp</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2060000000</v>
+        <v>2110000000</v>
       </c>
     </row>
     <row r="199">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1960000000</v>
+        <v>1910000000</v>
       </c>
     </row>
     <row r="200">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1590000000</v>
+        <v>1550000000</v>
       </c>
     </row>
     <row r="201">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1540000000</v>
+        <v>1490000000</v>
       </c>
     </row>
     <row r="202">
@@ -3516,7 +3516,7 @@
         </is>
       </c>
       <c r="L202" t="n">
-        <v>1120000000</v>
+        <v>1060000000</v>
       </c>
     </row>
     <row r="203">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>897030000</v>
+        <v>806180000</v>
       </c>
     </row>
     <row r="204">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>655650000</v>
+        <v>625580000</v>
       </c>
     </row>
     <row r="205">
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>326550000</v>
+        <v>309690000</v>
       </c>
     </row>
     <row r="206">
